--- a/Planilhas em tratamento/medicao_energia_2025.xlsx
+++ b/Planilhas em tratamento/medicao_energia_2025.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sgt.marquezzini\Documents\GitHub\Dashboardenergia\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sgt.marquezzini\Documents\GitHub\Dashboardenergia\Planilhas em tratamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC02BD70-98DC-4951-9D9D-6946BF8C6E59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E132C71-4A19-4E06-A15C-06984F5D19F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19080" yWindow="-120" windowWidth="19440" windowHeight="15000" tabRatio="500" firstSheet="5" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19080" yWindow="-120" windowWidth="19440" windowHeight="15000" tabRatio="500" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DEZEMBRO" sheetId="1" r:id="rId1"/>
@@ -467,13 +467,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -489,6 +482,13 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
@@ -3366,14 +3366,14 @@
     </row>
     <row r="35" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="1"/>
-      <c r="B35" s="34"/>
-      <c r="C35" s="34"/>
-      <c r="D35" s="34"/>
-      <c r="E35" s="34"/>
-      <c r="F35" s="34"/>
-      <c r="G35" s="34"/>
-      <c r="H35" s="34"/>
-      <c r="I35" s="34"/>
+      <c r="B35" s="39"/>
+      <c r="C35" s="39"/>
+      <c r="D35" s="39"/>
+      <c r="E35" s="39"/>
+      <c r="F35" s="39"/>
+      <c r="G35" s="39"/>
+      <c r="H35" s="39"/>
+      <c r="I35" s="39"/>
     </row>
     <row r="36" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
@@ -3751,15 +3751,15 @@
       <c r="I69" s="1"/>
     </row>
     <row r="70" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A70" s="34"/>
-      <c r="B70" s="34"/>
-      <c r="C70" s="34"/>
-      <c r="D70" s="34"/>
-      <c r="E70" s="34"/>
-      <c r="F70" s="34"/>
-      <c r="G70" s="34"/>
-      <c r="H70" s="34"/>
-      <c r="I70" s="34"/>
+      <c r="A70" s="39"/>
+      <c r="B70" s="39"/>
+      <c r="C70" s="39"/>
+      <c r="D70" s="39"/>
+      <c r="E70" s="39"/>
+      <c r="F70" s="39"/>
+      <c r="G70" s="39"/>
+      <c r="H70" s="39"/>
+      <c r="I70" s="39"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="1"/>
@@ -3784,15 +3784,15 @@
       <c r="I72" s="21"/>
     </row>
     <row r="75" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A75" s="35"/>
-      <c r="B75" s="35"/>
-      <c r="C75" s="35"/>
-      <c r="D75" s="35"/>
-      <c r="E75" s="35"/>
-      <c r="F75" s="35"/>
-      <c r="G75" s="35"/>
-      <c r="H75" s="35"/>
-      <c r="I75" s="35"/>
+      <c r="A75" s="40"/>
+      <c r="B75" s="40"/>
+      <c r="C75" s="40"/>
+      <c r="D75" s="40"/>
+      <c r="E75" s="40"/>
+      <c r="F75" s="40"/>
+      <c r="G75" s="40"/>
+      <c r="H75" s="40"/>
+      <c r="I75" s="40"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="1"/>
@@ -3828,15 +3828,15 @@
       <c r="I78" s="23"/>
     </row>
     <row r="79" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A79" s="36"/>
-      <c r="B79" s="36"/>
-      <c r="C79" s="36"/>
-      <c r="D79" s="36"/>
-      <c r="E79" s="36"/>
-      <c r="F79" s="36"/>
-      <c r="G79" s="36"/>
-      <c r="H79" s="36"/>
-      <c r="I79" s="36"/>
+      <c r="A79" s="41"/>
+      <c r="B79" s="41"/>
+      <c r="C79" s="41"/>
+      <c r="D79" s="41"/>
+      <c r="E79" s="41"/>
+      <c r="F79" s="41"/>
+      <c r="G79" s="41"/>
+      <c r="H79" s="41"/>
+      <c r="I79" s="41"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="1"/>
@@ -3872,15 +3872,15 @@
       <c r="B85" s="21"/>
     </row>
     <row r="87" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A87" s="35"/>
-      <c r="B87" s="35"/>
-      <c r="C87" s="35"/>
-      <c r="D87" s="35"/>
-      <c r="E87" s="35"/>
-      <c r="F87" s="35"/>
-      <c r="G87" s="35"/>
-      <c r="H87" s="35"/>
-      <c r="I87" s="35"/>
+      <c r="A87" s="40"/>
+      <c r="B87" s="40"/>
+      <c r="C87" s="40"/>
+      <c r="D87" s="40"/>
+      <c r="E87" s="40"/>
+      <c r="F87" s="40"/>
+      <c r="G87" s="40"/>
+      <c r="H87" s="40"/>
+      <c r="I87" s="40"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="1"/>
@@ -3983,15 +3983,15 @@
       <c r="B98" s="24"/>
     </row>
     <row r="100" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A100" s="34"/>
-      <c r="B100" s="34"/>
-      <c r="C100" s="34"/>
-      <c r="D100" s="34"/>
-      <c r="E100" s="34"/>
-      <c r="F100" s="34"/>
-      <c r="G100" s="34"/>
-      <c r="H100" s="34"/>
-      <c r="I100" s="34"/>
+      <c r="A100" s="39"/>
+      <c r="B100" s="39"/>
+      <c r="C100" s="39"/>
+      <c r="D100" s="39"/>
+      <c r="E100" s="39"/>
+      <c r="F100" s="39"/>
+      <c r="G100" s="39"/>
+      <c r="H100" s="39"/>
+      <c r="I100" s="39"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="1"/>
@@ -4224,28 +4224,28 @@
       <c r="U2" s="7">
         <v>0</v>
       </c>
-      <c r="V2" s="37">
+      <c r="V2" s="34">
         <v>594</v>
       </c>
-      <c r="W2" s="37">
+      <c r="W2" s="34">
         <v>1193</v>
       </c>
-      <c r="X2" s="37">
+      <c r="X2" s="34">
         <v>8925</v>
       </c>
-      <c r="Y2" s="37">
+      <c r="Y2" s="34">
         <v>10736</v>
       </c>
-      <c r="Z2" s="37">
+      <c r="Z2" s="34">
         <v>1256</v>
       </c>
-      <c r="AA2" s="37">
+      <c r="AA2" s="34">
         <v>3235</v>
       </c>
-      <c r="AB2" s="37">
+      <c r="AB2" s="34">
         <v>321</v>
       </c>
-      <c r="AC2" s="37">
+      <c r="AC2" s="34">
         <v>2913</v>
       </c>
       <c r="AE2" s="9" t="s">
@@ -4326,28 +4326,28 @@
       <c r="U3" s="15">
         <v>1</v>
       </c>
-      <c r="V3" s="37">
+      <c r="V3" s="34">
         <v>594</v>
       </c>
-      <c r="W3" s="37">
+      <c r="W3" s="34">
         <v>1193</v>
       </c>
-      <c r="X3" s="37">
+      <c r="X3" s="34">
         <v>8925</v>
       </c>
-      <c r="Y3" s="37">
+      <c r="Y3" s="34">
         <v>10736</v>
       </c>
-      <c r="Z3" s="37">
+      <c r="Z3" s="34">
         <v>1256</v>
       </c>
-      <c r="AA3" s="37">
+      <c r="AA3" s="34">
         <v>3235</v>
       </c>
-      <c r="AB3" s="37">
+      <c r="AB3" s="34">
         <v>321</v>
       </c>
-      <c r="AC3" s="37">
+      <c r="AC3" s="34">
         <v>2913</v>
       </c>
     </row>
@@ -4422,28 +4422,28 @@
         <f t="shared" ref="U4:U33" si="8">U3+1</f>
         <v>2</v>
       </c>
-      <c r="V4" s="37">
+      <c r="V4" s="34">
         <v>671</v>
       </c>
-      <c r="W4" s="37">
+      <c r="W4" s="34">
         <v>1289</v>
       </c>
-      <c r="X4" s="37">
+      <c r="X4" s="34">
         <v>8928</v>
       </c>
-      <c r="Y4" s="37">
+      <c r="Y4" s="34">
         <v>10736</v>
       </c>
-      <c r="Z4" s="37">
+      <c r="Z4" s="34">
         <v>1256</v>
       </c>
-      <c r="AA4" s="37">
+      <c r="AA4" s="34">
         <v>3238</v>
       </c>
-      <c r="AB4" s="37">
+      <c r="AB4" s="34">
         <v>321</v>
       </c>
-      <c r="AC4" s="37">
+      <c r="AC4" s="34">
         <v>2917</v>
       </c>
     </row>
@@ -4518,28 +4518,28 @@
         <f t="shared" si="8"/>
         <v>3</v>
       </c>
-      <c r="V5" s="37">
+      <c r="V5" s="34">
         <v>692</v>
       </c>
-      <c r="W5" s="37">
+      <c r="W5" s="34">
         <v>1453</v>
       </c>
-      <c r="X5" s="37">
+      <c r="X5" s="34">
         <v>8931</v>
       </c>
-      <c r="Y5" s="37">
+      <c r="Y5" s="34">
         <v>10736</v>
       </c>
-      <c r="Z5" s="37">
+      <c r="Z5" s="34">
         <v>1256</v>
       </c>
-      <c r="AA5" s="37">
+      <c r="AA5" s="34">
         <v>3243</v>
       </c>
-      <c r="AB5" s="37">
+      <c r="AB5" s="34">
         <v>321</v>
       </c>
-      <c r="AC5" s="37">
+      <c r="AC5" s="34">
         <v>2922</v>
       </c>
     </row>
@@ -4614,28 +4614,28 @@
         <f t="shared" si="8"/>
         <v>4</v>
       </c>
-      <c r="V6" s="37">
+      <c r="V6" s="34">
         <v>728</v>
       </c>
-      <c r="W6" s="37">
+      <c r="W6" s="34">
         <v>1501</v>
       </c>
-      <c r="X6" s="37">
+      <c r="X6" s="34">
         <v>8935</v>
       </c>
-      <c r="Y6" s="37">
+      <c r="Y6" s="34">
         <v>10738</v>
       </c>
-      <c r="Z6" s="37">
+      <c r="Z6" s="34">
         <v>1256</v>
       </c>
-      <c r="AA6" s="37">
+      <c r="AA6" s="34">
         <v>3251</v>
       </c>
-      <c r="AB6" s="37">
+      <c r="AB6" s="34">
         <v>322</v>
       </c>
-      <c r="AC6" s="37">
+      <c r="AC6" s="34">
         <v>2928</v>
       </c>
     </row>
@@ -4710,28 +4710,28 @@
         <f t="shared" si="8"/>
         <v>5</v>
       </c>
-      <c r="V7" s="37">
+      <c r="V7" s="34">
         <v>728</v>
       </c>
-      <c r="W7" s="37">
+      <c r="W7" s="34">
         <v>1501</v>
       </c>
-      <c r="X7" s="37">
+      <c r="X7" s="34">
         <v>8935</v>
       </c>
-      <c r="Y7" s="37">
+      <c r="Y7" s="34">
         <v>10738</v>
       </c>
-      <c r="Z7" s="37">
+      <c r="Z7" s="34">
         <v>1256</v>
       </c>
-      <c r="AA7" s="37">
+      <c r="AA7" s="34">
         <v>3251</v>
       </c>
-      <c r="AB7" s="37">
+      <c r="AB7" s="34">
         <v>322</v>
       </c>
-      <c r="AC7" s="37">
+      <c r="AC7" s="34">
         <v>2928</v>
       </c>
     </row>
@@ -4806,28 +4806,28 @@
         <f t="shared" si="8"/>
         <v>6</v>
       </c>
-      <c r="V8" s="37">
+      <c r="V8" s="34">
         <v>882</v>
       </c>
-      <c r="W8" s="37">
+      <c r="W8" s="34">
         <v>1705</v>
       </c>
-      <c r="X8" s="37">
+      <c r="X8" s="34">
         <v>8946</v>
       </c>
-      <c r="Y8" s="37">
+      <c r="Y8" s="34">
         <v>10739</v>
       </c>
-      <c r="Z8" s="37">
+      <c r="Z8" s="34">
         <v>1256</v>
       </c>
-      <c r="AA8" s="37">
+      <c r="AA8" s="34">
         <v>3263</v>
       </c>
-      <c r="AB8" s="37">
+      <c r="AB8" s="34">
         <v>322</v>
       </c>
-      <c r="AC8" s="37">
+      <c r="AC8" s="34">
         <v>2928</v>
       </c>
     </row>
@@ -4902,28 +4902,28 @@
         <f t="shared" si="8"/>
         <v>7</v>
       </c>
-      <c r="V9" s="37">
+      <c r="V9" s="34">
         <v>882</v>
       </c>
-      <c r="W9" s="37">
+      <c r="W9" s="34">
         <v>1705</v>
       </c>
-      <c r="X9" s="37">
+      <c r="X9" s="34">
         <v>8946</v>
       </c>
-      <c r="Y9" s="37">
+      <c r="Y9" s="34">
         <v>10739</v>
       </c>
-      <c r="Z9" s="37">
+      <c r="Z9" s="34">
         <v>1256</v>
       </c>
-      <c r="AA9" s="37">
+      <c r="AA9" s="34">
         <v>3263</v>
       </c>
-      <c r="AB9" s="37">
+      <c r="AB9" s="34">
         <v>322</v>
       </c>
-      <c r="AC9" s="37">
+      <c r="AC9" s="34">
         <v>2928</v>
       </c>
     </row>
@@ -4998,28 +4998,28 @@
         <f t="shared" si="8"/>
         <v>8</v>
       </c>
-      <c r="V10" s="37">
+      <c r="V10" s="34">
         <v>1058</v>
       </c>
-      <c r="W10" s="37">
+      <c r="W10" s="34">
         <v>1995</v>
       </c>
-      <c r="X10" s="37">
+      <c r="X10" s="34">
         <v>8952</v>
       </c>
-      <c r="Y10" s="37">
+      <c r="Y10" s="34">
         <v>10741</v>
       </c>
-      <c r="Z10" s="37">
+      <c r="Z10" s="34">
         <v>1257</v>
       </c>
-      <c r="AA10" s="37">
+      <c r="AA10" s="34">
         <v>3274</v>
       </c>
-      <c r="AB10" s="37">
+      <c r="AB10" s="34">
         <v>325</v>
       </c>
-      <c r="AC10" s="37">
+      <c r="AC10" s="34">
         <v>2948</v>
       </c>
     </row>
@@ -5094,28 +5094,28 @@
         <f t="shared" si="8"/>
         <v>9</v>
       </c>
-      <c r="V11" s="37">
+      <c r="V11" s="34">
         <v>1080</v>
       </c>
-      <c r="W11" s="37">
+      <c r="W11" s="34">
         <v>2125</v>
       </c>
-      <c r="X11" s="37">
+      <c r="X11" s="34">
         <v>8952</v>
       </c>
-      <c r="Y11" s="37">
+      <c r="Y11" s="34">
         <v>10741</v>
       </c>
-      <c r="Z11" s="37">
+      <c r="Z11" s="34">
         <v>1257</v>
       </c>
-      <c r="AA11" s="37">
+      <c r="AA11" s="34">
         <v>3280</v>
       </c>
-      <c r="AB11" s="37">
+      <c r="AB11" s="34">
         <v>325</v>
       </c>
-      <c r="AC11" s="37">
+      <c r="AC11" s="34">
         <v>2955</v>
       </c>
     </row>
@@ -5190,28 +5190,28 @@
         <f t="shared" si="8"/>
         <v>10</v>
       </c>
-      <c r="V12" s="37">
+      <c r="V12" s="34">
         <v>1135</v>
       </c>
-      <c r="W12" s="37">
+      <c r="W12" s="34">
         <v>2301</v>
       </c>
-      <c r="X12" s="37">
+      <c r="X12" s="34">
         <v>8960</v>
       </c>
-      <c r="Y12" s="37">
+      <c r="Y12" s="34">
         <v>10742</v>
       </c>
-      <c r="Z12" s="37">
+      <c r="Z12" s="34">
         <v>1257</v>
       </c>
-      <c r="AA12" s="37">
+      <c r="AA12" s="34">
         <v>3287</v>
       </c>
-      <c r="AB12" s="37">
+      <c r="AB12" s="34">
         <v>325</v>
       </c>
-      <c r="AC12" s="37">
+      <c r="AC12" s="34">
         <v>2962</v>
       </c>
     </row>
@@ -5286,28 +5286,28 @@
         <f t="shared" si="8"/>
         <v>11</v>
       </c>
-      <c r="V13" s="37">
+      <c r="V13" s="34">
         <v>1230</v>
       </c>
-      <c r="W13" s="37">
+      <c r="W13" s="34">
         <v>2418</v>
       </c>
-      <c r="X13" s="37">
+      <c r="X13" s="34">
         <v>8964</v>
       </c>
-      <c r="Y13" s="37">
+      <c r="Y13" s="34">
         <v>10743</v>
       </c>
-      <c r="Z13" s="37">
+      <c r="Z13" s="34">
         <v>1257</v>
       </c>
-      <c r="AA13" s="37">
+      <c r="AA13" s="34">
         <v>3287</v>
       </c>
-      <c r="AB13" s="37">
+      <c r="AB13" s="34">
         <v>325</v>
       </c>
-      <c r="AC13" s="37">
+      <c r="AC13" s="34">
         <v>2962</v>
       </c>
     </row>
@@ -5382,28 +5382,28 @@
         <f t="shared" si="8"/>
         <v>12</v>
       </c>
-      <c r="V14" s="37">
+      <c r="V14" s="34">
         <v>1347</v>
       </c>
-      <c r="W14" s="37">
+      <c r="W14" s="34">
         <v>2611</v>
       </c>
-      <c r="X14" s="37">
+      <c r="X14" s="34">
         <v>8967</v>
       </c>
-      <c r="Y14" s="37">
+      <c r="Y14" s="34">
         <v>10744</v>
       </c>
-      <c r="Z14" s="37">
+      <c r="Z14" s="34">
         <v>1257</v>
       </c>
-      <c r="AA14" s="37">
+      <c r="AA14" s="34">
         <v>3300</v>
       </c>
-      <c r="AB14" s="37">
+      <c r="AB14" s="34">
         <v>327</v>
       </c>
-      <c r="AC14" s="37">
+      <c r="AC14" s="34">
         <v>2973</v>
       </c>
     </row>
@@ -5477,28 +5477,28 @@
         <f t="shared" si="8"/>
         <v>13</v>
       </c>
-      <c r="V15" s="37">
+      <c r="V15" s="34">
         <v>1470</v>
       </c>
-      <c r="W15" s="37">
+      <c r="W15" s="34">
         <v>2681</v>
       </c>
-      <c r="X15" s="37">
+      <c r="X15" s="34">
         <v>8971</v>
       </c>
-      <c r="Y15" s="37">
+      <c r="Y15" s="34">
         <v>10744</v>
       </c>
-      <c r="Z15" s="37">
+      <c r="Z15" s="34">
         <v>1258</v>
       </c>
-      <c r="AA15" s="37">
+      <c r="AA15" s="34">
         <v>3306</v>
       </c>
-      <c r="AB15" s="37">
+      <c r="AB15" s="34">
         <v>328</v>
       </c>
-      <c r="AC15" s="37">
+      <c r="AC15" s="34">
         <v>2977</v>
       </c>
     </row>
@@ -5573,28 +5573,28 @@
         <f t="shared" si="8"/>
         <v>14</v>
       </c>
-      <c r="V16" s="37">
+      <c r="V16" s="34">
         <v>1470</v>
       </c>
-      <c r="W16" s="37">
+      <c r="W16" s="34">
         <v>2681</v>
       </c>
-      <c r="X16" s="37">
+      <c r="X16" s="34">
         <v>8971</v>
       </c>
-      <c r="Y16" s="37">
+      <c r="Y16" s="34">
         <v>10744</v>
       </c>
-      <c r="Z16" s="37">
+      <c r="Z16" s="34">
         <v>1258</v>
       </c>
-      <c r="AA16" s="37">
+      <c r="AA16" s="34">
         <v>3306</v>
       </c>
-      <c r="AB16" s="37">
+      <c r="AB16" s="34">
         <v>328</v>
       </c>
-      <c r="AC16" s="37">
+      <c r="AC16" s="34">
         <v>2977</v>
       </c>
     </row>
@@ -5669,28 +5669,28 @@
         <f t="shared" si="8"/>
         <v>15</v>
       </c>
-      <c r="V17" s="37">
+      <c r="V17" s="34">
         <v>1674</v>
       </c>
-      <c r="W17" s="37">
+      <c r="W17" s="34">
         <v>2914</v>
       </c>
-      <c r="X17" s="37">
+      <c r="X17" s="34">
         <v>8979</v>
       </c>
-      <c r="Y17" s="37">
+      <c r="Y17" s="34">
         <v>10745</v>
       </c>
-      <c r="Z17" s="37">
+      <c r="Z17" s="34">
         <v>1258</v>
       </c>
-      <c r="AA17" s="37">
+      <c r="AA17" s="34">
         <v>3317</v>
       </c>
-      <c r="AB17" s="37">
+      <c r="AB17" s="34">
         <v>329</v>
       </c>
-      <c r="AC17" s="37">
+      <c r="AC17" s="34">
         <v>2988</v>
       </c>
     </row>
@@ -5765,28 +5765,28 @@
         <f t="shared" si="8"/>
         <v>16</v>
       </c>
-      <c r="V18" s="37">
+      <c r="V18" s="34">
         <v>1690</v>
       </c>
-      <c r="W18" s="37">
+      <c r="W18" s="34">
         <v>2986</v>
       </c>
-      <c r="X18" s="37">
+      <c r="X18" s="34">
         <v>8979</v>
       </c>
-      <c r="Y18" s="37">
+      <c r="Y18" s="34">
         <v>10747</v>
       </c>
-      <c r="Z18" s="37">
+      <c r="Z18" s="34">
         <v>1258</v>
       </c>
-      <c r="AA18" s="37">
+      <c r="AA18" s="34">
         <v>3324</v>
       </c>
-      <c r="AB18" s="37">
+      <c r="AB18" s="34">
         <v>329</v>
       </c>
-      <c r="AC18" s="37">
+      <c r="AC18" s="34">
         <v>2994</v>
       </c>
     </row>
@@ -5861,28 +5861,28 @@
         <f t="shared" si="8"/>
         <v>17</v>
       </c>
-      <c r="V19" s="37">
+      <c r="V19" s="34">
         <v>1733</v>
       </c>
-      <c r="W19" s="37">
+      <c r="W19" s="34">
         <v>3061</v>
       </c>
-      <c r="X19" s="37">
+      <c r="X19" s="34">
         <v>8985</v>
       </c>
-      <c r="Y19" s="37">
+      <c r="Y19" s="34">
         <v>10747</v>
       </c>
-      <c r="Z19" s="37">
+      <c r="Z19" s="34">
         <v>1258</v>
       </c>
-      <c r="AA19" s="37">
+      <c r="AA19" s="34">
         <v>3330</v>
       </c>
-      <c r="AB19" s="37">
+      <c r="AB19" s="34">
         <v>329</v>
       </c>
-      <c r="AC19" s="37">
+      <c r="AC19" s="34">
         <v>3000</v>
       </c>
     </row>
@@ -5957,28 +5957,28 @@
         <f t="shared" si="8"/>
         <v>18</v>
       </c>
-      <c r="V20" s="37">
+      <c r="V20" s="34">
         <v>1859</v>
       </c>
-      <c r="W20" s="37">
+      <c r="W20" s="34">
         <v>3301</v>
       </c>
-      <c r="X20" s="37">
+      <c r="X20" s="34">
         <v>8988</v>
       </c>
-      <c r="Y20" s="37">
+      <c r="Y20" s="34">
         <v>10748</v>
       </c>
-      <c r="Z20" s="37">
+      <c r="Z20" s="34">
         <v>1258</v>
       </c>
-      <c r="AA20" s="37">
+      <c r="AA20" s="34">
         <v>3336</v>
       </c>
-      <c r="AB20" s="37">
+      <c r="AB20" s="34">
         <v>330</v>
       </c>
-      <c r="AC20" s="37">
+      <c r="AC20" s="34">
         <v>3005</v>
       </c>
     </row>
@@ -6053,28 +6053,28 @@
         <f t="shared" si="8"/>
         <v>19</v>
       </c>
-      <c r="V21" s="37">
+      <c r="V21" s="34">
         <v>1951</v>
       </c>
-      <c r="W21" s="37">
+      <c r="W21" s="34">
         <v>3368</v>
       </c>
-      <c r="X21" s="37">
+      <c r="X21" s="34">
         <v>8992</v>
       </c>
-      <c r="Y21" s="37">
+      <c r="Y21" s="34">
         <v>10749</v>
       </c>
-      <c r="Z21" s="37">
+      <c r="Z21" s="34">
         <v>1258</v>
       </c>
-      <c r="AA21" s="37">
+      <c r="AA21" s="34">
         <v>3342</v>
       </c>
-      <c r="AB21" s="37">
+      <c r="AB21" s="34">
         <v>331</v>
       </c>
-      <c r="AC21" s="37">
+      <c r="AC21" s="34">
         <v>3010</v>
       </c>
     </row>
@@ -6149,28 +6149,28 @@
         <f t="shared" si="8"/>
         <v>20</v>
       </c>
-      <c r="V22" s="37">
+      <c r="V22" s="34">
         <v>2048</v>
       </c>
-      <c r="W22" s="37">
+      <c r="W22" s="34">
         <v>3506</v>
       </c>
-      <c r="X22" s="37">
+      <c r="X22" s="34">
         <v>8995</v>
       </c>
-      <c r="Y22" s="37">
+      <c r="Y22" s="34">
         <v>10749</v>
       </c>
-      <c r="Z22" s="37">
+      <c r="Z22" s="34">
         <v>1258</v>
       </c>
-      <c r="AA22" s="37">
+      <c r="AA22" s="34">
         <v>3347</v>
       </c>
-      <c r="AB22" s="37">
+      <c r="AB22" s="34">
         <v>332</v>
       </c>
-      <c r="AC22" s="37">
+      <c r="AC22" s="34">
         <v>3015</v>
       </c>
     </row>
@@ -6245,28 +6245,28 @@
         <f t="shared" si="8"/>
         <v>21</v>
       </c>
-      <c r="V23" s="37">
+      <c r="V23" s="34">
         <v>2170</v>
       </c>
-      <c r="W23" s="37">
+      <c r="W23" s="34">
         <v>3628</v>
       </c>
-      <c r="X23" s="37">
+      <c r="X23" s="34">
         <v>8985</v>
       </c>
-      <c r="Y23" s="37">
+      <c r="Y23" s="34">
         <v>10749</v>
       </c>
-      <c r="Z23" s="37">
+      <c r="Z23" s="34">
         <v>1258</v>
       </c>
-      <c r="AA23" s="37">
+      <c r="AA23" s="34">
         <v>3350</v>
       </c>
-      <c r="AB23" s="37">
+      <c r="AB23" s="34">
         <v>333</v>
       </c>
-      <c r="AC23" s="37">
+      <c r="AC23" s="34">
         <v>3017</v>
       </c>
     </row>
@@ -6341,28 +6341,28 @@
         <f t="shared" si="8"/>
         <v>22</v>
       </c>
-      <c r="V24" s="37">
+      <c r="V24" s="34">
         <v>2199</v>
       </c>
-      <c r="W24" s="37">
+      <c r="W24" s="34">
         <v>3713</v>
       </c>
-      <c r="X24" s="37">
+      <c r="X24" s="34">
         <v>8999</v>
       </c>
-      <c r="Y24" s="37">
+      <c r="Y24" s="34">
         <v>10752</v>
       </c>
-      <c r="Z24" s="37">
+      <c r="Z24" s="34">
         <v>1259</v>
       </c>
-      <c r="AA24" s="37">
+      <c r="AA24" s="34">
         <v>3356</v>
       </c>
-      <c r="AB24" s="37">
+      <c r="AB24" s="34">
         <v>334</v>
       </c>
-      <c r="AC24" s="37">
+      <c r="AC24" s="34">
         <v>3021</v>
       </c>
     </row>
@@ -6437,28 +6437,28 @@
         <f t="shared" si="8"/>
         <v>23</v>
       </c>
-      <c r="V25" s="37">
+      <c r="V25" s="34">
         <v>2248</v>
       </c>
-      <c r="W25" s="37">
+      <c r="W25" s="34">
         <v>3790</v>
       </c>
-      <c r="X25" s="37">
+      <c r="X25" s="34">
         <v>9004</v>
       </c>
-      <c r="Y25" s="37">
+      <c r="Y25" s="34">
         <v>10752</v>
       </c>
-      <c r="Z25" s="37">
+      <c r="Z25" s="34">
         <v>1259</v>
       </c>
-      <c r="AA25" s="37">
+      <c r="AA25" s="34">
         <v>3364</v>
       </c>
-      <c r="AB25" s="37">
+      <c r="AB25" s="34">
         <v>334</v>
       </c>
-      <c r="AC25" s="37">
+      <c r="AC25" s="34">
         <v>3023</v>
       </c>
     </row>
@@ -6533,28 +6533,28 @@
         <f t="shared" si="8"/>
         <v>24</v>
       </c>
-      <c r="V26" s="37">
+      <c r="V26" s="34">
         <v>2286</v>
       </c>
-      <c r="W26" s="37">
+      <c r="W26" s="34">
         <v>3790</v>
       </c>
-      <c r="X26" s="37">
+      <c r="X26" s="34">
         <v>9009</v>
       </c>
-      <c r="Y26" s="37">
+      <c r="Y26" s="34">
         <v>10753</v>
       </c>
-      <c r="Z26" s="37">
+      <c r="Z26" s="34">
         <v>1259</v>
       </c>
-      <c r="AA26" s="37">
+      <c r="AA26" s="34">
         <v>3369</v>
       </c>
-      <c r="AB26" s="37">
+      <c r="AB26" s="34">
         <v>334</v>
       </c>
-      <c r="AC26" s="37">
+      <c r="AC26" s="34">
         <v>3035</v>
       </c>
     </row>
@@ -6629,28 +6629,28 @@
         <f t="shared" si="8"/>
         <v>25</v>
       </c>
-      <c r="V27" s="37">
+      <c r="V27" s="34">
         <v>2384</v>
       </c>
-      <c r="W27" s="37">
+      <c r="W27" s="34">
         <v>3934</v>
       </c>
-      <c r="X27" s="37">
+      <c r="X27" s="34">
         <v>9011</v>
       </c>
-      <c r="Y27" s="37">
+      <c r="Y27" s="34">
         <v>10753</v>
       </c>
-      <c r="Z27" s="37">
+      <c r="Z27" s="34">
         <v>1259</v>
       </c>
-      <c r="AA27" s="37">
+      <c r="AA27" s="34">
         <v>3371</v>
       </c>
-      <c r="AB27" s="37">
+      <c r="AB27" s="34">
         <v>334</v>
       </c>
-      <c r="AC27" s="37">
+      <c r="AC27" s="34">
         <v>3036</v>
       </c>
     </row>
@@ -6725,28 +6725,28 @@
         <f t="shared" si="8"/>
         <v>26</v>
       </c>
-      <c r="V28" s="37">
+      <c r="V28" s="34">
         <v>2452</v>
       </c>
-      <c r="W28" s="37">
+      <c r="W28" s="34">
         <v>4054</v>
       </c>
-      <c r="X28" s="37">
+      <c r="X28" s="34">
         <v>9015</v>
       </c>
-      <c r="Y28" s="37">
+      <c r="Y28" s="34">
         <v>10755</v>
       </c>
-      <c r="Z28" s="37">
+      <c r="Z28" s="34">
         <v>1259</v>
       </c>
-      <c r="AA28" s="37">
+      <c r="AA28" s="34">
         <v>3379</v>
       </c>
-      <c r="AB28" s="37">
+      <c r="AB28" s="34">
         <v>336</v>
       </c>
-      <c r="AC28" s="37">
+      <c r="AC28" s="34">
         <v>3043</v>
       </c>
     </row>
@@ -6821,28 +6821,28 @@
         <f t="shared" si="8"/>
         <v>27</v>
       </c>
-      <c r="V29" s="37">
+      <c r="V29" s="34">
         <v>2601</v>
       </c>
-      <c r="W29" s="37">
+      <c r="W29" s="34">
         <v>4174</v>
       </c>
-      <c r="X29" s="37">
+      <c r="X29" s="34">
         <v>9017</v>
       </c>
-      <c r="Y29" s="37">
+      <c r="Y29" s="34">
         <v>10755</v>
       </c>
-      <c r="Z29" s="37">
+      <c r="Z29" s="34">
         <v>1259</v>
       </c>
-      <c r="AA29" s="37">
+      <c r="AA29" s="34">
         <v>3384</v>
       </c>
-      <c r="AB29" s="37">
+      <c r="AB29" s="34">
         <v>336</v>
       </c>
-      <c r="AC29" s="37">
+      <c r="AC29" s="34">
         <v>3048</v>
       </c>
     </row>
@@ -6917,28 +6917,28 @@
         <f t="shared" si="8"/>
         <v>28</v>
       </c>
-      <c r="V30" s="37">
+      <c r="V30" s="34">
         <v>2674</v>
       </c>
-      <c r="W30" s="37">
+      <c r="W30" s="34">
         <v>4247</v>
       </c>
-      <c r="X30" s="37">
+      <c r="X30" s="34">
         <v>9020</v>
       </c>
-      <c r="Y30" s="37">
+      <c r="Y30" s="34">
         <v>10756</v>
       </c>
-      <c r="Z30" s="37">
+      <c r="Z30" s="34">
         <v>1260</v>
       </c>
-      <c r="AA30" s="37">
+      <c r="AA30" s="34">
         <v>3390</v>
       </c>
-      <c r="AB30" s="37">
+      <c r="AB30" s="34">
         <v>337</v>
       </c>
-      <c r="AC30" s="37">
+      <c r="AC30" s="34">
         <v>3052</v>
       </c>
     </row>
@@ -7013,28 +7013,28 @@
         <f t="shared" si="8"/>
         <v>29</v>
       </c>
-      <c r="V31" s="37">
+      <c r="V31" s="34">
         <v>2742</v>
       </c>
-      <c r="W31" s="37">
+      <c r="W31" s="34">
         <v>4306</v>
       </c>
-      <c r="X31" s="37">
+      <c r="X31" s="34">
         <v>9020</v>
       </c>
-      <c r="Y31" s="37">
+      <c r="Y31" s="34">
         <v>10757</v>
       </c>
-      <c r="Z31" s="37">
+      <c r="Z31" s="34">
         <v>1260</v>
       </c>
-      <c r="AA31" s="37">
+      <c r="AA31" s="34">
         <v>3395</v>
       </c>
-      <c r="AB31" s="37">
+      <c r="AB31" s="34">
         <v>338</v>
       </c>
-      <c r="AC31" s="37">
+      <c r="AC31" s="34">
         <v>3057</v>
       </c>
     </row>
@@ -7109,28 +7109,28 @@
         <f t="shared" si="8"/>
         <v>30</v>
       </c>
-      <c r="V32" s="37">
+      <c r="V32" s="34">
         <v>2801</v>
       </c>
-      <c r="W32" s="37">
+      <c r="W32" s="34">
         <v>4403</v>
       </c>
-      <c r="X32" s="37">
+      <c r="X32" s="34">
         <v>9034</v>
       </c>
-      <c r="Y32" s="37">
+      <c r="Y32" s="34">
         <v>10757</v>
       </c>
-      <c r="Z32" s="37">
+      <c r="Z32" s="34">
         <v>1260</v>
       </c>
-      <c r="AA32" s="37">
+      <c r="AA32" s="34">
         <v>3402</v>
       </c>
-      <c r="AB32" s="37">
+      <c r="AB32" s="34">
         <v>338</v>
       </c>
-      <c r="AC32" s="37">
+      <c r="AC32" s="34">
         <v>3063</v>
       </c>
     </row>
@@ -7157,42 +7157,42 @@
         <f t="shared" si="8"/>
         <v>31</v>
       </c>
-      <c r="V33" s="37">
+      <c r="V33" s="34">
         <v>2812</v>
       </c>
-      <c r="W33" s="37">
+      <c r="W33" s="34">
         <v>4489</v>
       </c>
-      <c r="X33" s="37">
+      <c r="X33" s="34">
         <v>9036</v>
       </c>
-      <c r="Y33" s="37">
+      <c r="Y33" s="34">
         <v>10758</v>
       </c>
-      <c r="Z33" s="37">
+      <c r="Z33" s="34">
         <v>1260</v>
       </c>
-      <c r="AA33" s="37">
+      <c r="AA33" s="34">
         <v>3408</v>
       </c>
-      <c r="AB33" s="37">
+      <c r="AB33" s="34">
         <v>338</v>
       </c>
-      <c r="AC33" s="37">
+      <c r="AC33" s="34">
         <v>3069</v>
       </c>
     </row>
     <row r="34" spans="1:29" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="36" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
-      <c r="B36" s="34"/>
-      <c r="C36" s="34"/>
-      <c r="D36" s="34"/>
-      <c r="E36" s="34"/>
-      <c r="F36" s="34"/>
-      <c r="G36" s="34"/>
-      <c r="H36" s="34"/>
-      <c r="I36" s="34"/>
+      <c r="B36" s="39"/>
+      <c r="C36" s="39"/>
+      <c r="D36" s="39"/>
+      <c r="E36" s="39"/>
+      <c r="F36" s="39"/>
+      <c r="G36" s="39"/>
+      <c r="H36" s="39"/>
+      <c r="I36" s="39"/>
     </row>
     <row r="37" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="1"/>
@@ -7569,15 +7569,15 @@
       <c r="I70" s="1"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A71" s="34"/>
-      <c r="B71" s="34"/>
-      <c r="C71" s="34"/>
-      <c r="D71" s="34"/>
-      <c r="E71" s="34"/>
-      <c r="F71" s="34"/>
-      <c r="G71" s="34"/>
-      <c r="H71" s="34"/>
-      <c r="I71" s="34"/>
+      <c r="A71" s="39"/>
+      <c r="B71" s="39"/>
+      <c r="C71" s="39"/>
+      <c r="D71" s="39"/>
+      <c r="E71" s="39"/>
+      <c r="F71" s="39"/>
+      <c r="G71" s="39"/>
+      <c r="H71" s="39"/>
+      <c r="I71" s="39"/>
     </row>
     <row r="72" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A72" s="1"/>
@@ -7602,15 +7602,15 @@
       <c r="I73" s="21"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A76" s="35"/>
-      <c r="B76" s="35"/>
-      <c r="C76" s="35"/>
-      <c r="D76" s="35"/>
-      <c r="E76" s="35"/>
-      <c r="F76" s="35"/>
-      <c r="G76" s="35"/>
-      <c r="H76" s="35"/>
-      <c r="I76" s="35"/>
+      <c r="A76" s="40"/>
+      <c r="B76" s="40"/>
+      <c r="C76" s="40"/>
+      <c r="D76" s="40"/>
+      <c r="E76" s="40"/>
+      <c r="F76" s="40"/>
+      <c r="G76" s="40"/>
+      <c r="H76" s="40"/>
+      <c r="I76" s="40"/>
     </row>
     <row r="77" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="1"/>
@@ -7646,15 +7646,15 @@
       <c r="I79" s="23"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A80" s="36"/>
-      <c r="B80" s="36"/>
-      <c r="C80" s="36"/>
-      <c r="D80" s="36"/>
-      <c r="E80" s="36"/>
-      <c r="F80" s="36"/>
-      <c r="G80" s="36"/>
-      <c r="H80" s="36"/>
-      <c r="I80" s="36"/>
+      <c r="A80" s="41"/>
+      <c r="B80" s="41"/>
+      <c r="C80" s="41"/>
+      <c r="D80" s="41"/>
+      <c r="E80" s="41"/>
+      <c r="F80" s="41"/>
+      <c r="G80" s="41"/>
+      <c r="H80" s="41"/>
+      <c r="I80" s="41"/>
     </row>
     <row r="81" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="1"/>
@@ -7690,15 +7690,15 @@
       <c r="B86" s="21"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A88" s="35"/>
-      <c r="B88" s="35"/>
-      <c r="C88" s="35"/>
-      <c r="D88" s="35"/>
-      <c r="E88" s="35"/>
-      <c r="F88" s="35"/>
-      <c r="G88" s="35"/>
-      <c r="H88" s="35"/>
-      <c r="I88" s="35"/>
+      <c r="A88" s="40"/>
+      <c r="B88" s="40"/>
+      <c r="C88" s="40"/>
+      <c r="D88" s="40"/>
+      <c r="E88" s="40"/>
+      <c r="F88" s="40"/>
+      <c r="G88" s="40"/>
+      <c r="H88" s="40"/>
+      <c r="I88" s="40"/>
     </row>
     <row r="89" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="1"/>
@@ -7801,15 +7801,15 @@
       <c r="B99" s="24"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A101" s="34"/>
-      <c r="B101" s="34"/>
-      <c r="C101" s="34"/>
-      <c r="D101" s="34"/>
-      <c r="E101" s="34"/>
-      <c r="F101" s="34"/>
-      <c r="G101" s="34"/>
-      <c r="H101" s="34"/>
-      <c r="I101" s="34"/>
+      <c r="A101" s="39"/>
+      <c r="B101" s="39"/>
+      <c r="C101" s="39"/>
+      <c r="D101" s="39"/>
+      <c r="E101" s="39"/>
+      <c r="F101" s="39"/>
+      <c r="G101" s="39"/>
+      <c r="H101" s="39"/>
+      <c r="I101" s="39"/>
     </row>
     <row r="102" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A102" s="1"/>
@@ -10286,14 +10286,14 @@
     </row>
     <row r="32" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A32" s="1"/>
-      <c r="B32" s="34"/>
-      <c r="C32" s="34"/>
-      <c r="D32" s="34"/>
-      <c r="E32" s="34"/>
-      <c r="F32" s="34"/>
-      <c r="G32" s="34"/>
-      <c r="H32" s="34"/>
-      <c r="I32" s="34"/>
+      <c r="B32" s="39"/>
+      <c r="C32" s="39"/>
+      <c r="D32" s="39"/>
+      <c r="E32" s="39"/>
+      <c r="F32" s="39"/>
+      <c r="G32" s="39"/>
+      <c r="H32" s="39"/>
+      <c r="I32" s="39"/>
     </row>
     <row r="33" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A33" s="1"/>
@@ -10670,15 +10670,15 @@
       <c r="I66" s="1"/>
     </row>
     <row r="67" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A67" s="34"/>
-      <c r="B67" s="34"/>
-      <c r="C67" s="34"/>
-      <c r="D67" s="34"/>
-      <c r="E67" s="34"/>
-      <c r="F67" s="34"/>
-      <c r="G67" s="34"/>
-      <c r="H67" s="34"/>
-      <c r="I67" s="34"/>
+      <c r="A67" s="39"/>
+      <c r="B67" s="39"/>
+      <c r="C67" s="39"/>
+      <c r="D67" s="39"/>
+      <c r="E67" s="39"/>
+      <c r="F67" s="39"/>
+      <c r="G67" s="39"/>
+      <c r="H67" s="39"/>
+      <c r="I67" s="39"/>
     </row>
     <row r="68" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A68" s="1"/>
@@ -10703,15 +10703,15 @@
       <c r="I69" s="21"/>
     </row>
     <row r="72" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A72" s="35"/>
-      <c r="B72" s="35"/>
-      <c r="C72" s="35"/>
-      <c r="D72" s="35"/>
-      <c r="E72" s="35"/>
-      <c r="F72" s="35"/>
-      <c r="G72" s="35"/>
-      <c r="H72" s="35"/>
-      <c r="I72" s="35"/>
+      <c r="A72" s="40"/>
+      <c r="B72" s="40"/>
+      <c r="C72" s="40"/>
+      <c r="D72" s="40"/>
+      <c r="E72" s="40"/>
+      <c r="F72" s="40"/>
+      <c r="G72" s="40"/>
+      <c r="H72" s="40"/>
+      <c r="I72" s="40"/>
     </row>
     <row r="73" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A73" s="1"/>
@@ -10747,15 +10747,15 @@
       <c r="I75" s="23"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A76" s="36"/>
-      <c r="B76" s="36"/>
-      <c r="C76" s="36"/>
-      <c r="D76" s="36"/>
-      <c r="E76" s="36"/>
-      <c r="F76" s="36"/>
-      <c r="G76" s="36"/>
-      <c r="H76" s="36"/>
-      <c r="I76" s="36"/>
+      <c r="A76" s="41"/>
+      <c r="B76" s="41"/>
+      <c r="C76" s="41"/>
+      <c r="D76" s="41"/>
+      <c r="E76" s="41"/>
+      <c r="F76" s="41"/>
+      <c r="G76" s="41"/>
+      <c r="H76" s="41"/>
+      <c r="I76" s="41"/>
     </row>
     <row r="77" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="1"/>
@@ -10791,15 +10791,15 @@
       <c r="B82" s="21"/>
     </row>
     <row r="84" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A84" s="35"/>
-      <c r="B84" s="35"/>
-      <c r="C84" s="35"/>
-      <c r="D84" s="35"/>
-      <c r="E84" s="35"/>
-      <c r="F84" s="35"/>
-      <c r="G84" s="35"/>
-      <c r="H84" s="35"/>
-      <c r="I84" s="35"/>
+      <c r="A84" s="40"/>
+      <c r="B84" s="40"/>
+      <c r="C84" s="40"/>
+      <c r="D84" s="40"/>
+      <c r="E84" s="40"/>
+      <c r="F84" s="40"/>
+      <c r="G84" s="40"/>
+      <c r="H84" s="40"/>
+      <c r="I84" s="40"/>
     </row>
     <row r="85" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A85" s="1"/>
@@ -10902,15 +10902,15 @@
       <c r="B95" s="24"/>
     </row>
     <row r="97" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A97" s="34"/>
-      <c r="B97" s="34"/>
-      <c r="C97" s="34"/>
-      <c r="D97" s="34"/>
-      <c r="E97" s="34"/>
-      <c r="F97" s="34"/>
-      <c r="G97" s="34"/>
-      <c r="H97" s="34"/>
-      <c r="I97" s="34"/>
+      <c r="A97" s="39"/>
+      <c r="B97" s="39"/>
+      <c r="C97" s="39"/>
+      <c r="D97" s="39"/>
+      <c r="E97" s="39"/>
+      <c r="F97" s="39"/>
+      <c r="G97" s="39"/>
+      <c r="H97" s="39"/>
+      <c r="I97" s="39"/>
     </row>
     <row r="98" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A98" s="1"/>
@@ -13580,14 +13580,14 @@
     <row r="34" spans="1:20" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="36" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
-      <c r="B36" s="34"/>
-      <c r="C36" s="34"/>
-      <c r="D36" s="34"/>
-      <c r="E36" s="34"/>
-      <c r="F36" s="34"/>
-      <c r="G36" s="34"/>
-      <c r="H36" s="34"/>
-      <c r="I36" s="34"/>
+      <c r="B36" s="39"/>
+      <c r="C36" s="39"/>
+      <c r="D36" s="39"/>
+      <c r="E36" s="39"/>
+      <c r="F36" s="39"/>
+      <c r="G36" s="39"/>
+      <c r="H36" s="39"/>
+      <c r="I36" s="39"/>
     </row>
     <row r="37" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="1"/>
@@ -13964,15 +13964,15 @@
       <c r="I70" s="1"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A71" s="34"/>
-      <c r="B71" s="34"/>
-      <c r="C71" s="34"/>
-      <c r="D71" s="34"/>
-      <c r="E71" s="34"/>
-      <c r="F71" s="34"/>
-      <c r="G71" s="34"/>
-      <c r="H71" s="34"/>
-      <c r="I71" s="34"/>
+      <c r="A71" s="39"/>
+      <c r="B71" s="39"/>
+      <c r="C71" s="39"/>
+      <c r="D71" s="39"/>
+      <c r="E71" s="39"/>
+      <c r="F71" s="39"/>
+      <c r="G71" s="39"/>
+      <c r="H71" s="39"/>
+      <c r="I71" s="39"/>
     </row>
     <row r="72" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A72" s="1"/>
@@ -13997,15 +13997,15 @@
       <c r="I73" s="21"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A76" s="35"/>
-      <c r="B76" s="35"/>
-      <c r="C76" s="35"/>
-      <c r="D76" s="35"/>
-      <c r="E76" s="35"/>
-      <c r="F76" s="35"/>
-      <c r="G76" s="35"/>
-      <c r="H76" s="35"/>
-      <c r="I76" s="35"/>
+      <c r="A76" s="40"/>
+      <c r="B76" s="40"/>
+      <c r="C76" s="40"/>
+      <c r="D76" s="40"/>
+      <c r="E76" s="40"/>
+      <c r="F76" s="40"/>
+      <c r="G76" s="40"/>
+      <c r="H76" s="40"/>
+      <c r="I76" s="40"/>
     </row>
     <row r="77" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="1"/>
@@ -14041,15 +14041,15 @@
       <c r="I79" s="23"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A80" s="36"/>
-      <c r="B80" s="36"/>
-      <c r="C80" s="36"/>
-      <c r="D80" s="36"/>
-      <c r="E80" s="36"/>
-      <c r="F80" s="36"/>
-      <c r="G80" s="36"/>
-      <c r="H80" s="36"/>
-      <c r="I80" s="36"/>
+      <c r="A80" s="41"/>
+      <c r="B80" s="41"/>
+      <c r="C80" s="41"/>
+      <c r="D80" s="41"/>
+      <c r="E80" s="41"/>
+      <c r="F80" s="41"/>
+      <c r="G80" s="41"/>
+      <c r="H80" s="41"/>
+      <c r="I80" s="41"/>
     </row>
     <row r="81" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="1"/>
@@ -14085,15 +14085,15 @@
       <c r="B86" s="21"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A88" s="35"/>
-      <c r="B88" s="35"/>
-      <c r="C88" s="35"/>
-      <c r="D88" s="35"/>
-      <c r="E88" s="35"/>
-      <c r="F88" s="35"/>
-      <c r="G88" s="35"/>
-      <c r="H88" s="35"/>
-      <c r="I88" s="35"/>
+      <c r="A88" s="40"/>
+      <c r="B88" s="40"/>
+      <c r="C88" s="40"/>
+      <c r="D88" s="40"/>
+      <c r="E88" s="40"/>
+      <c r="F88" s="40"/>
+      <c r="G88" s="40"/>
+      <c r="H88" s="40"/>
+      <c r="I88" s="40"/>
     </row>
     <row r="89" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="1"/>
@@ -14196,15 +14196,15 @@
       <c r="B99" s="24"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A101" s="34"/>
-      <c r="B101" s="34"/>
-      <c r="C101" s="34"/>
-      <c r="D101" s="34"/>
-      <c r="E101" s="34"/>
-      <c r="F101" s="34"/>
-      <c r="G101" s="34"/>
-      <c r="H101" s="34"/>
-      <c r="I101" s="34"/>
+      <c r="A101" s="39"/>
+      <c r="B101" s="39"/>
+      <c r="C101" s="39"/>
+      <c r="D101" s="39"/>
+      <c r="E101" s="39"/>
+      <c r="F101" s="39"/>
+      <c r="G101" s="39"/>
+      <c r="H101" s="39"/>
+      <c r="I101" s="39"/>
     </row>
     <row r="102" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A102" s="1"/>
@@ -16881,14 +16881,14 @@
     <row r="33" spans="1:9" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="35" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="1"/>
-      <c r="B35" s="34"/>
-      <c r="C35" s="34"/>
-      <c r="D35" s="34"/>
-      <c r="E35" s="34"/>
-      <c r="F35" s="34"/>
-      <c r="G35" s="34"/>
-      <c r="H35" s="34"/>
-      <c r="I35" s="34"/>
+      <c r="B35" s="39"/>
+      <c r="C35" s="39"/>
+      <c r="D35" s="39"/>
+      <c r="E35" s="39"/>
+      <c r="F35" s="39"/>
+      <c r="G35" s="39"/>
+      <c r="H35" s="39"/>
+      <c r="I35" s="39"/>
     </row>
     <row r="36" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
@@ -17266,15 +17266,15 @@
       <c r="I69" s="1"/>
     </row>
     <row r="70" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A70" s="34"/>
-      <c r="B70" s="34"/>
-      <c r="C70" s="34"/>
-      <c r="D70" s="34"/>
-      <c r="E70" s="34"/>
-      <c r="F70" s="34"/>
-      <c r="G70" s="34"/>
-      <c r="H70" s="34"/>
-      <c r="I70" s="34"/>
+      <c r="A70" s="39"/>
+      <c r="B70" s="39"/>
+      <c r="C70" s="39"/>
+      <c r="D70" s="39"/>
+      <c r="E70" s="39"/>
+      <c r="F70" s="39"/>
+      <c r="G70" s="39"/>
+      <c r="H70" s="39"/>
+      <c r="I70" s="39"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="1"/>
@@ -17299,15 +17299,15 @@
       <c r="I72" s="21"/>
     </row>
     <row r="75" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A75" s="35"/>
-      <c r="B75" s="35"/>
-      <c r="C75" s="35"/>
-      <c r="D75" s="35"/>
-      <c r="E75" s="35"/>
-      <c r="F75" s="35"/>
-      <c r="G75" s="35"/>
-      <c r="H75" s="35"/>
-      <c r="I75" s="35"/>
+      <c r="A75" s="40"/>
+      <c r="B75" s="40"/>
+      <c r="C75" s="40"/>
+      <c r="D75" s="40"/>
+      <c r="E75" s="40"/>
+      <c r="F75" s="40"/>
+      <c r="G75" s="40"/>
+      <c r="H75" s="40"/>
+      <c r="I75" s="40"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="1"/>
@@ -17343,15 +17343,15 @@
       <c r="I78" s="23"/>
     </row>
     <row r="79" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A79" s="36"/>
-      <c r="B79" s="36"/>
-      <c r="C79" s="36"/>
-      <c r="D79" s="36"/>
-      <c r="E79" s="36"/>
-      <c r="F79" s="36"/>
-      <c r="G79" s="36"/>
-      <c r="H79" s="36"/>
-      <c r="I79" s="36"/>
+      <c r="A79" s="41"/>
+      <c r="B79" s="41"/>
+      <c r="C79" s="41"/>
+      <c r="D79" s="41"/>
+      <c r="E79" s="41"/>
+      <c r="F79" s="41"/>
+      <c r="G79" s="41"/>
+      <c r="H79" s="41"/>
+      <c r="I79" s="41"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="1"/>
@@ -17387,15 +17387,15 @@
       <c r="B85" s="21"/>
     </row>
     <row r="87" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A87" s="35"/>
-      <c r="B87" s="35"/>
-      <c r="C87" s="35"/>
-      <c r="D87" s="35"/>
-      <c r="E87" s="35"/>
-      <c r="F87" s="35"/>
-      <c r="G87" s="35"/>
-      <c r="H87" s="35"/>
-      <c r="I87" s="35"/>
+      <c r="A87" s="40"/>
+      <c r="B87" s="40"/>
+      <c r="C87" s="40"/>
+      <c r="D87" s="40"/>
+      <c r="E87" s="40"/>
+      <c r="F87" s="40"/>
+      <c r="G87" s="40"/>
+      <c r="H87" s="40"/>
+      <c r="I87" s="40"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="1"/>
@@ -17498,15 +17498,15 @@
       <c r="B98" s="24"/>
     </row>
     <row r="100" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A100" s="34"/>
-      <c r="B100" s="34"/>
-      <c r="C100" s="34"/>
-      <c r="D100" s="34"/>
-      <c r="E100" s="34"/>
-      <c r="F100" s="34"/>
-      <c r="G100" s="34"/>
-      <c r="H100" s="34"/>
-      <c r="I100" s="34"/>
+      <c r="A100" s="39"/>
+      <c r="B100" s="39"/>
+      <c r="C100" s="39"/>
+      <c r="D100" s="39"/>
+      <c r="E100" s="39"/>
+      <c r="F100" s="39"/>
+      <c r="G100" s="39"/>
+      <c r="H100" s="39"/>
+      <c r="I100" s="39"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="1"/>
@@ -20205,14 +20205,14 @@
     <row r="34" spans="1:29" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="36" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
-      <c r="B36" s="34"/>
-      <c r="C36" s="34"/>
-      <c r="D36" s="34"/>
-      <c r="E36" s="34"/>
-      <c r="F36" s="34"/>
-      <c r="G36" s="34"/>
-      <c r="H36" s="34"/>
-      <c r="I36" s="34"/>
+      <c r="B36" s="39"/>
+      <c r="C36" s="39"/>
+      <c r="D36" s="39"/>
+      <c r="E36" s="39"/>
+      <c r="F36" s="39"/>
+      <c r="G36" s="39"/>
+      <c r="H36" s="39"/>
+      <c r="I36" s="39"/>
     </row>
     <row r="37" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="1"/>
@@ -20590,15 +20590,15 @@
       <c r="I70" s="1"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A71" s="34"/>
-      <c r="B71" s="34"/>
-      <c r="C71" s="34"/>
-      <c r="D71" s="34"/>
-      <c r="E71" s="34"/>
-      <c r="F71" s="34"/>
-      <c r="G71" s="34"/>
-      <c r="H71" s="34"/>
-      <c r="I71" s="34"/>
+      <c r="A71" s="39"/>
+      <c r="B71" s="39"/>
+      <c r="C71" s="39"/>
+      <c r="D71" s="39"/>
+      <c r="E71" s="39"/>
+      <c r="F71" s="39"/>
+      <c r="G71" s="39"/>
+      <c r="H71" s="39"/>
+      <c r="I71" s="39"/>
     </row>
     <row r="72" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A72" s="1"/>
@@ -20623,15 +20623,15 @@
       <c r="I73" s="21"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A76" s="35"/>
-      <c r="B76" s="35"/>
-      <c r="C76" s="35"/>
-      <c r="D76" s="35"/>
-      <c r="E76" s="35"/>
-      <c r="F76" s="35"/>
-      <c r="G76" s="35"/>
-      <c r="H76" s="35"/>
-      <c r="I76" s="35"/>
+      <c r="A76" s="40"/>
+      <c r="B76" s="40"/>
+      <c r="C76" s="40"/>
+      <c r="D76" s="40"/>
+      <c r="E76" s="40"/>
+      <c r="F76" s="40"/>
+      <c r="G76" s="40"/>
+      <c r="H76" s="40"/>
+      <c r="I76" s="40"/>
     </row>
     <row r="77" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="1"/>
@@ -20667,15 +20667,15 @@
       <c r="I79" s="23"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A80" s="36"/>
-      <c r="B80" s="36"/>
-      <c r="C80" s="36"/>
-      <c r="D80" s="36"/>
-      <c r="E80" s="36"/>
-      <c r="F80" s="36"/>
-      <c r="G80" s="36"/>
-      <c r="H80" s="36"/>
-      <c r="I80" s="36"/>
+      <c r="A80" s="41"/>
+      <c r="B80" s="41"/>
+      <c r="C80" s="41"/>
+      <c r="D80" s="41"/>
+      <c r="E80" s="41"/>
+      <c r="F80" s="41"/>
+      <c r="G80" s="41"/>
+      <c r="H80" s="41"/>
+      <c r="I80" s="41"/>
     </row>
     <row r="81" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="1"/>
@@ -20711,15 +20711,15 @@
       <c r="B86" s="21"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A88" s="35"/>
-      <c r="B88" s="35"/>
-      <c r="C88" s="35"/>
-      <c r="D88" s="35"/>
-      <c r="E88" s="35"/>
-      <c r="F88" s="35"/>
-      <c r="G88" s="35"/>
-      <c r="H88" s="35"/>
-      <c r="I88" s="35"/>
+      <c r="A88" s="40"/>
+      <c r="B88" s="40"/>
+      <c r="C88" s="40"/>
+      <c r="D88" s="40"/>
+      <c r="E88" s="40"/>
+      <c r="F88" s="40"/>
+      <c r="G88" s="40"/>
+      <c r="H88" s="40"/>
+      <c r="I88" s="40"/>
     </row>
     <row r="89" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="1"/>
@@ -20822,15 +20822,15 @@
       <c r="B99" s="24"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A101" s="34"/>
-      <c r="B101" s="34"/>
-      <c r="C101" s="34"/>
-      <c r="D101" s="34"/>
-      <c r="E101" s="34"/>
-      <c r="F101" s="34"/>
-      <c r="G101" s="34"/>
-      <c r="H101" s="34"/>
-      <c r="I101" s="34"/>
+      <c r="A101" s="39"/>
+      <c r="B101" s="39"/>
+      <c r="C101" s="39"/>
+      <c r="D101" s="39"/>
+      <c r="E101" s="39"/>
+      <c r="F101" s="39"/>
+      <c r="G101" s="39"/>
+      <c r="H101" s="39"/>
+      <c r="I101" s="39"/>
     </row>
     <row r="102" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A102" s="1"/>
@@ -23461,14 +23461,14 @@
     </row>
     <row r="34" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A34" s="1"/>
-      <c r="B34" s="34"/>
-      <c r="C34" s="34"/>
-      <c r="D34" s="34"/>
-      <c r="E34" s="34"/>
-      <c r="F34" s="34"/>
-      <c r="G34" s="34"/>
-      <c r="H34" s="34"/>
-      <c r="I34" s="34"/>
+      <c r="B34" s="39"/>
+      <c r="C34" s="39"/>
+      <c r="D34" s="39"/>
+      <c r="E34" s="39"/>
+      <c r="F34" s="39"/>
+      <c r="G34" s="39"/>
+      <c r="H34" s="39"/>
+      <c r="I34" s="39"/>
     </row>
     <row r="35" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="1"/>
@@ -23846,15 +23846,15 @@
       <c r="I68" s="1"/>
     </row>
     <row r="69" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A69" s="34"/>
-      <c r="B69" s="34"/>
-      <c r="C69" s="34"/>
-      <c r="D69" s="34"/>
-      <c r="E69" s="34"/>
-      <c r="F69" s="34"/>
-      <c r="G69" s="34"/>
-      <c r="H69" s="34"/>
-      <c r="I69" s="34"/>
+      <c r="A69" s="39"/>
+      <c r="B69" s="39"/>
+      <c r="C69" s="39"/>
+      <c r="D69" s="39"/>
+      <c r="E69" s="39"/>
+      <c r="F69" s="39"/>
+      <c r="G69" s="39"/>
+      <c r="H69" s="39"/>
+      <c r="I69" s="39"/>
     </row>
     <row r="70" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A70" s="1"/>
@@ -23879,15 +23879,15 @@
       <c r="I71" s="21"/>
     </row>
     <row r="74" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A74" s="35"/>
-      <c r="B74" s="35"/>
-      <c r="C74" s="35"/>
-      <c r="D74" s="35"/>
-      <c r="E74" s="35"/>
-      <c r="F74" s="35"/>
-      <c r="G74" s="35"/>
-      <c r="H74" s="35"/>
-      <c r="I74" s="35"/>
+      <c r="A74" s="40"/>
+      <c r="B74" s="40"/>
+      <c r="C74" s="40"/>
+      <c r="D74" s="40"/>
+      <c r="E74" s="40"/>
+      <c r="F74" s="40"/>
+      <c r="G74" s="40"/>
+      <c r="H74" s="40"/>
+      <c r="I74" s="40"/>
     </row>
     <row r="75" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A75" s="1"/>
@@ -23923,15 +23923,15 @@
       <c r="I77" s="23"/>
     </row>
     <row r="78" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A78" s="36"/>
-      <c r="B78" s="36"/>
-      <c r="C78" s="36"/>
-      <c r="D78" s="36"/>
-      <c r="E78" s="36"/>
-      <c r="F78" s="36"/>
-      <c r="G78" s="36"/>
-      <c r="H78" s="36"/>
-      <c r="I78" s="36"/>
+      <c r="A78" s="41"/>
+      <c r="B78" s="41"/>
+      <c r="C78" s="41"/>
+      <c r="D78" s="41"/>
+      <c r="E78" s="41"/>
+      <c r="F78" s="41"/>
+      <c r="G78" s="41"/>
+      <c r="H78" s="41"/>
+      <c r="I78" s="41"/>
     </row>
     <row r="79" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A79" s="1"/>
@@ -23967,15 +23967,15 @@
       <c r="B84" s="21"/>
     </row>
     <row r="86" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A86" s="35"/>
-      <c r="B86" s="35"/>
-      <c r="C86" s="35"/>
-      <c r="D86" s="35"/>
-      <c r="E86" s="35"/>
-      <c r="F86" s="35"/>
-      <c r="G86" s="35"/>
-      <c r="H86" s="35"/>
-      <c r="I86" s="35"/>
+      <c r="A86" s="40"/>
+      <c r="B86" s="40"/>
+      <c r="C86" s="40"/>
+      <c r="D86" s="40"/>
+      <c r="E86" s="40"/>
+      <c r="F86" s="40"/>
+      <c r="G86" s="40"/>
+      <c r="H86" s="40"/>
+      <c r="I86" s="40"/>
     </row>
     <row r="87" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A87" s="1"/>
@@ -24078,15 +24078,15 @@
       <c r="B97" s="24"/>
     </row>
     <row r="99" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A99" s="34"/>
-      <c r="B99" s="34"/>
-      <c r="C99" s="34"/>
-      <c r="D99" s="34"/>
-      <c r="E99" s="34"/>
-      <c r="F99" s="34"/>
-      <c r="G99" s="34"/>
-      <c r="H99" s="34"/>
-      <c r="I99" s="34"/>
+      <c r="A99" s="39"/>
+      <c r="B99" s="39"/>
+      <c r="C99" s="39"/>
+      <c r="D99" s="39"/>
+      <c r="E99" s="39"/>
+      <c r="F99" s="39"/>
+      <c r="G99" s="39"/>
+      <c r="H99" s="39"/>
+      <c r="I99" s="39"/>
     </row>
     <row r="100" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A100" s="1"/>
@@ -26784,14 +26784,14 @@
     </row>
     <row r="35" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="1"/>
-      <c r="B35" s="34"/>
-      <c r="C35" s="34"/>
-      <c r="D35" s="34"/>
-      <c r="E35" s="34"/>
-      <c r="F35" s="34"/>
-      <c r="G35" s="34"/>
-      <c r="H35" s="34"/>
-      <c r="I35" s="34"/>
+      <c r="B35" s="39"/>
+      <c r="C35" s="39"/>
+      <c r="D35" s="39"/>
+      <c r="E35" s="39"/>
+      <c r="F35" s="39"/>
+      <c r="G35" s="39"/>
+      <c r="H35" s="39"/>
+      <c r="I35" s="39"/>
     </row>
     <row r="36" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
@@ -27169,15 +27169,15 @@
       <c r="I69" s="1"/>
     </row>
     <row r="70" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A70" s="34"/>
-      <c r="B70" s="34"/>
-      <c r="C70" s="34"/>
-      <c r="D70" s="34"/>
-      <c r="E70" s="34"/>
-      <c r="F70" s="34"/>
-      <c r="G70" s="34"/>
-      <c r="H70" s="34"/>
-      <c r="I70" s="34"/>
+      <c r="A70" s="39"/>
+      <c r="B70" s="39"/>
+      <c r="C70" s="39"/>
+      <c r="D70" s="39"/>
+      <c r="E70" s="39"/>
+      <c r="F70" s="39"/>
+      <c r="G70" s="39"/>
+      <c r="H70" s="39"/>
+      <c r="I70" s="39"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="1"/>
@@ -27202,15 +27202,15 @@
       <c r="I72" s="21"/>
     </row>
     <row r="75" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A75" s="35"/>
-      <c r="B75" s="35"/>
-      <c r="C75" s="35"/>
-      <c r="D75" s="35"/>
-      <c r="E75" s="35"/>
-      <c r="F75" s="35"/>
-      <c r="G75" s="35"/>
-      <c r="H75" s="35"/>
-      <c r="I75" s="35"/>
+      <c r="A75" s="40"/>
+      <c r="B75" s="40"/>
+      <c r="C75" s="40"/>
+      <c r="D75" s="40"/>
+      <c r="E75" s="40"/>
+      <c r="F75" s="40"/>
+      <c r="G75" s="40"/>
+      <c r="H75" s="40"/>
+      <c r="I75" s="40"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="1"/>
@@ -27246,15 +27246,15 @@
       <c r="I78" s="23"/>
     </row>
     <row r="79" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A79" s="36"/>
-      <c r="B79" s="36"/>
-      <c r="C79" s="36"/>
-      <c r="D79" s="36"/>
-      <c r="E79" s="36"/>
-      <c r="F79" s="36"/>
-      <c r="G79" s="36"/>
-      <c r="H79" s="36"/>
-      <c r="I79" s="36"/>
+      <c r="A79" s="41"/>
+      <c r="B79" s="41"/>
+      <c r="C79" s="41"/>
+      <c r="D79" s="41"/>
+      <c r="E79" s="41"/>
+      <c r="F79" s="41"/>
+      <c r="G79" s="41"/>
+      <c r="H79" s="41"/>
+      <c r="I79" s="41"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="1"/>
@@ -27290,15 +27290,15 @@
       <c r="B85" s="21"/>
     </row>
     <row r="87" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A87" s="35"/>
-      <c r="B87" s="35"/>
-      <c r="C87" s="35"/>
-      <c r="D87" s="35"/>
-      <c r="E87" s="35"/>
-      <c r="F87" s="35"/>
-      <c r="G87" s="35"/>
-      <c r="H87" s="35"/>
-      <c r="I87" s="35"/>
+      <c r="A87" s="40"/>
+      <c r="B87" s="40"/>
+      <c r="C87" s="40"/>
+      <c r="D87" s="40"/>
+      <c r="E87" s="40"/>
+      <c r="F87" s="40"/>
+      <c r="G87" s="40"/>
+      <c r="H87" s="40"/>
+      <c r="I87" s="40"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="1"/>
@@ -27401,15 +27401,15 @@
       <c r="B98" s="24"/>
     </row>
     <row r="100" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A100" s="34"/>
-      <c r="B100" s="34"/>
-      <c r="C100" s="34"/>
-      <c r="D100" s="34"/>
-      <c r="E100" s="34"/>
-      <c r="F100" s="34"/>
-      <c r="G100" s="34"/>
-      <c r="H100" s="34"/>
-      <c r="I100" s="34"/>
+      <c r="A100" s="39"/>
+      <c r="B100" s="39"/>
+      <c r="C100" s="39"/>
+      <c r="D100" s="39"/>
+      <c r="E100" s="39"/>
+      <c r="F100" s="39"/>
+      <c r="G100" s="39"/>
+      <c r="H100" s="39"/>
+      <c r="I100" s="39"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="1"/>
@@ -30107,14 +30107,14 @@
     </row>
     <row r="36" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
-      <c r="B36" s="34"/>
-      <c r="C36" s="34"/>
-      <c r="D36" s="34"/>
-      <c r="E36" s="34"/>
-      <c r="F36" s="34"/>
-      <c r="G36" s="34"/>
-      <c r="H36" s="34"/>
-      <c r="I36" s="34"/>
+      <c r="B36" s="39"/>
+      <c r="C36" s="39"/>
+      <c r="D36" s="39"/>
+      <c r="E36" s="39"/>
+      <c r="F36" s="39"/>
+      <c r="G36" s="39"/>
+      <c r="H36" s="39"/>
+      <c r="I36" s="39"/>
     </row>
     <row r="37" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="1"/>
@@ -30492,15 +30492,15 @@
       <c r="I70" s="1"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A71" s="34"/>
-      <c r="B71" s="34"/>
-      <c r="C71" s="34"/>
-      <c r="D71" s="34"/>
-      <c r="E71" s="34"/>
-      <c r="F71" s="34"/>
-      <c r="G71" s="34"/>
-      <c r="H71" s="34"/>
-      <c r="I71" s="34"/>
+      <c r="A71" s="39"/>
+      <c r="B71" s="39"/>
+      <c r="C71" s="39"/>
+      <c r="D71" s="39"/>
+      <c r="E71" s="39"/>
+      <c r="F71" s="39"/>
+      <c r="G71" s="39"/>
+      <c r="H71" s="39"/>
+      <c r="I71" s="39"/>
     </row>
     <row r="72" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A72" s="1"/>
@@ -30525,15 +30525,15 @@
       <c r="I73" s="21"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A76" s="35"/>
-      <c r="B76" s="35"/>
-      <c r="C76" s="35"/>
-      <c r="D76" s="35"/>
-      <c r="E76" s="35"/>
-      <c r="F76" s="35"/>
-      <c r="G76" s="35"/>
-      <c r="H76" s="35"/>
-      <c r="I76" s="35"/>
+      <c r="A76" s="40"/>
+      <c r="B76" s="40"/>
+      <c r="C76" s="40"/>
+      <c r="D76" s="40"/>
+      <c r="E76" s="40"/>
+      <c r="F76" s="40"/>
+      <c r="G76" s="40"/>
+      <c r="H76" s="40"/>
+      <c r="I76" s="40"/>
     </row>
     <row r="77" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="1"/>
@@ -30569,15 +30569,15 @@
       <c r="I79" s="23"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A80" s="36"/>
-      <c r="B80" s="36"/>
-      <c r="C80" s="36"/>
-      <c r="D80" s="36"/>
-      <c r="E80" s="36"/>
-      <c r="F80" s="36"/>
-      <c r="G80" s="36"/>
-      <c r="H80" s="36"/>
-      <c r="I80" s="36"/>
+      <c r="A80" s="41"/>
+      <c r="B80" s="41"/>
+      <c r="C80" s="41"/>
+      <c r="D80" s="41"/>
+      <c r="E80" s="41"/>
+      <c r="F80" s="41"/>
+      <c r="G80" s="41"/>
+      <c r="H80" s="41"/>
+      <c r="I80" s="41"/>
     </row>
     <row r="81" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="1"/>
@@ -30613,15 +30613,15 @@
       <c r="B86" s="21"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A88" s="35"/>
-      <c r="B88" s="35"/>
-      <c r="C88" s="35"/>
-      <c r="D88" s="35"/>
-      <c r="E88" s="35"/>
-      <c r="F88" s="35"/>
-      <c r="G88" s="35"/>
-      <c r="H88" s="35"/>
-      <c r="I88" s="35"/>
+      <c r="A88" s="40"/>
+      <c r="B88" s="40"/>
+      <c r="C88" s="40"/>
+      <c r="D88" s="40"/>
+      <c r="E88" s="40"/>
+      <c r="F88" s="40"/>
+      <c r="G88" s="40"/>
+      <c r="H88" s="40"/>
+      <c r="I88" s="40"/>
     </row>
     <row r="89" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="1"/>
@@ -30724,15 +30724,15 @@
       <c r="B99" s="24"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A101" s="34"/>
-      <c r="B101" s="34"/>
-      <c r="C101" s="34"/>
-      <c r="D101" s="34"/>
-      <c r="E101" s="34"/>
-      <c r="F101" s="34"/>
-      <c r="G101" s="34"/>
-      <c r="H101" s="34"/>
-      <c r="I101" s="34"/>
+      <c r="A101" s="39"/>
+      <c r="B101" s="39"/>
+      <c r="C101" s="39"/>
+      <c r="D101" s="39"/>
+      <c r="E101" s="39"/>
+      <c r="F101" s="39"/>
+      <c r="G101" s="39"/>
+      <c r="H101" s="39"/>
+      <c r="I101" s="39"/>
     </row>
     <row r="102" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A102" s="1"/>
@@ -30909,7 +30909,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="25">
-        <v>1009.5539995399999</v>
+        <v>1003.1699995399999</v>
       </c>
       <c r="C2" s="25">
         <v>183.79199990000001</v>
@@ -30949,52 +30949,51 @@
       <c r="M2" s="12">
         <v>0</v>
       </c>
-      <c r="N2" s="6">
-        <f t="shared" ref="N2:N14" si="4">AA3-AA2</f>
+      <c r="N2" s="25">
+        <v>276.91199938999995</v>
+      </c>
+      <c r="O2" s="30">
+        <v>58.7279999</v>
+      </c>
+      <c r="P2" s="6">
+        <f t="shared" ref="P2:P14" si="4">AB3-AB2</f>
+        <v>1</v>
+      </c>
+      <c r="Q2" s="12">
+        <v>0</v>
+      </c>
+      <c r="R2" s="12">
+        <v>0</v>
+      </c>
+      <c r="S2" s="6">
+        <f t="shared" ref="S2:S14" si="5">AC3-AC2</f>
         <v>7</v>
       </c>
-      <c r="O2" s="12">
-        <v>0</v>
-      </c>
-      <c r="P2" s="6">
-        <f t="shared" ref="P2:P14" si="5">AB3-AB2</f>
-        <v>1</v>
-      </c>
-      <c r="Q2" s="12">
-        <v>0</v>
-      </c>
-      <c r="R2" s="12">
-        <v>0</v>
-      </c>
-      <c r="S2" s="6">
-        <f t="shared" ref="S2:S14" si="6">AC3-AC2</f>
-        <v>7</v>
-      </c>
       <c r="U2" s="7">
         <v>0</v>
       </c>
-      <c r="V2" s="39">
+      <c r="V2" s="36">
         <v>6375</v>
       </c>
-      <c r="W2" s="39">
+      <c r="W2" s="36">
         <v>8136</v>
       </c>
-      <c r="X2" s="39">
+      <c r="X2" s="36">
         <v>9263</v>
       </c>
-      <c r="Y2" s="39">
+      <c r="Y2" s="36">
         <v>10802</v>
       </c>
-      <c r="Z2" s="39">
+      <c r="Z2" s="36">
         <v>1270</v>
       </c>
-      <c r="AA2" s="39">
+      <c r="AA2" s="36">
         <v>3687</v>
       </c>
-      <c r="AB2" s="39">
+      <c r="AB2" s="36">
         <v>368</v>
       </c>
-      <c r="AC2" s="39">
+      <c r="AC2" s="36">
         <v>3318</v>
       </c>
       <c r="AE2" s="9" t="s">
@@ -31007,7 +31006,7 @@
     </row>
     <row r="3" spans="1:32" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A3" s="11">
-        <f t="shared" ref="A3:A31" si="7">A2+1</f>
+        <f t="shared" ref="A3:A31" si="6">A2+1</f>
         <v>2</v>
       </c>
       <c r="B3" s="26">
@@ -31017,7 +31016,7 @@
         <v>179.08799991000001</v>
       </c>
       <c r="D3" s="6">
-        <f t="shared" ref="D3:D14" si="8">V4-V3</f>
+        <f t="shared" ref="D3:D14" si="7">V4-V3</f>
         <v>32</v>
       </c>
       <c r="E3" s="12">
@@ -31051,60 +31050,59 @@
       <c r="M3" s="12">
         <v>0</v>
       </c>
-      <c r="N3" s="6">
+      <c r="N3" s="25">
+        <v>218.73599947999992</v>
+      </c>
+      <c r="O3" s="30">
+        <v>50.159999910000003</v>
+      </c>
+      <c r="P3" s="6">
         <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q3" s="12">
+        <v>0</v>
+      </c>
+      <c r="R3" s="12">
+        <v>0</v>
+      </c>
+      <c r="S3" s="6">
+        <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="O3" s="12">
-        <v>0</v>
-      </c>
-      <c r="P3" s="6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Q3" s="12">
-        <v>0</v>
-      </c>
-      <c r="R3" s="12">
-        <v>0</v>
-      </c>
-      <c r="S3" s="6">
+      <c r="U3" s="5">
+        <v>1</v>
+      </c>
+      <c r="V3" s="34">
+        <v>6429</v>
+      </c>
+      <c r="W3" s="34">
+        <v>8198</v>
+      </c>
+      <c r="X3" s="34">
+        <v>9269</v>
+      </c>
+      <c r="Y3" s="34">
+        <v>10803</v>
+      </c>
+      <c r="Z3" s="34">
+        <v>1271</v>
+      </c>
+      <c r="AA3" s="34">
+        <v>3694</v>
+      </c>
+      <c r="AB3" s="34">
+        <v>369</v>
+      </c>
+      <c r="AC3" s="34">
+        <v>3325</v>
+      </c>
+    </row>
+    <row r="4" spans="1:32" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A4" s="11">
         <f t="shared" si="6"/>
         <v>3</v>
       </c>
-      <c r="U3" s="5">
-        <v>1</v>
-      </c>
-      <c r="V3" s="37">
-        <v>6429</v>
-      </c>
-      <c r="W3" s="37">
-        <v>8198</v>
-      </c>
-      <c r="X3" s="37">
-        <v>9269</v>
-      </c>
-      <c r="Y3" s="37">
-        <v>10803</v>
-      </c>
-      <c r="Z3" s="37">
-        <v>1271</v>
-      </c>
-      <c r="AA3" s="37">
-        <v>3694</v>
-      </c>
-      <c r="AB3" s="37">
-        <v>369</v>
-      </c>
-      <c r="AC3" s="37">
-        <v>3325</v>
-      </c>
-    </row>
-    <row r="4" spans="1:32" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A4" s="11">
-        <f t="shared" si="7"/>
-        <v>3</v>
-      </c>
       <c r="B4" s="26">
         <v>1343.327999449999</v>
       </c>
@@ -31112,7 +31110,7 @@
         <v>184.42199996000002</v>
       </c>
       <c r="D4" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>63</v>
       </c>
       <c r="E4" s="12">
@@ -31146,59 +31144,58 @@
       <c r="M4" s="12">
         <v>0</v>
       </c>
-      <c r="N4" s="6">
+      <c r="N4" s="25">
+        <v>294.69599936000009</v>
+      </c>
+      <c r="O4" s="30">
+        <v>62.087999889999992</v>
+      </c>
+      <c r="P4" s="6">
         <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q4" s="12">
+        <v>0</v>
+      </c>
+      <c r="R4" s="12">
+        <v>0</v>
+      </c>
+      <c r="S4" s="6">
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="O4" s="12">
-        <v>0</v>
-      </c>
-      <c r="P4" s="6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Q4" s="12">
-        <v>0</v>
-      </c>
-      <c r="R4" s="12">
-        <v>0</v>
-      </c>
-      <c r="S4" s="6">
-        <f t="shared" si="6"/>
-        <v>5</v>
-      </c>
       <c r="U4" s="11">
-        <f t="shared" ref="U4:U32" si="9">U3+1</f>
+        <f t="shared" ref="U4:U32" si="8">U3+1</f>
         <v>2</v>
       </c>
-      <c r="V4" s="37">
+      <c r="V4" s="34">
         <v>6461</v>
       </c>
-      <c r="W4" s="37">
+      <c r="W4" s="34">
         <v>8283</v>
       </c>
-      <c r="X4" s="37">
+      <c r="X4" s="34">
         <v>9272</v>
       </c>
-      <c r="Y4" s="37">
+      <c r="Y4" s="34">
         <v>10804</v>
       </c>
-      <c r="Z4" s="37">
+      <c r="Z4" s="34">
         <v>1271</v>
       </c>
-      <c r="AA4" s="37">
+      <c r="AA4" s="34">
         <v>3697</v>
       </c>
-      <c r="AB4" s="37">
+      <c r="AB4" s="34">
         <v>369</v>
       </c>
-      <c r="AC4" s="37">
+      <c r="AC4" s="34">
         <v>3328</v>
       </c>
     </row>
     <row r="5" spans="1:32" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A5" s="11">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>4</v>
       </c>
       <c r="B5" s="26">
@@ -31208,7 +31205,7 @@
         <v>209.83199991000004</v>
       </c>
       <c r="D5" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>95</v>
       </c>
       <c r="E5" s="12">
@@ -31242,59 +31239,58 @@
       <c r="M5" s="12">
         <v>0</v>
       </c>
-      <c r="N5" s="6">
+      <c r="N5" s="25">
+        <v>270.38399930999987</v>
+      </c>
+      <c r="O5" s="30">
+        <v>59.231999910000006</v>
+      </c>
+      <c r="P5" s="6">
         <f t="shared" si="4"/>
-        <v>5</v>
-      </c>
-      <c r="O5" s="12">
-        <v>0</v>
-      </c>
-      <c r="P5" s="6">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="12">
+        <v>0</v>
+      </c>
+      <c r="R5" s="12">
+        <v>0</v>
+      </c>
+      <c r="S5" s="6">
         <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="Q5" s="12">
-        <v>0</v>
-      </c>
-      <c r="R5" s="12">
-        <v>0</v>
-      </c>
-      <c r="S5" s="6">
-        <f t="shared" si="6"/>
         <v>3</v>
       </c>
       <c r="U5" s="11">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
-      <c r="V5" s="37">
+      <c r="V5" s="34">
         <v>6524</v>
       </c>
-      <c r="W5" s="37">
+      <c r="W5" s="34">
         <v>8298</v>
       </c>
-      <c r="X5" s="37">
+      <c r="X5" s="34">
         <v>9275</v>
       </c>
-      <c r="Y5" s="37">
+      <c r="Y5" s="34">
         <v>10804</v>
       </c>
-      <c r="Z5" s="37">
+      <c r="Z5" s="34">
         <v>1271</v>
       </c>
-      <c r="AA5" s="37">
+      <c r="AA5" s="34">
         <v>3702</v>
       </c>
-      <c r="AB5" s="37">
+      <c r="AB5" s="34">
         <v>369</v>
       </c>
-      <c r="AC5" s="37">
+      <c r="AC5" s="34">
         <v>3333</v>
       </c>
     </row>
     <row r="6" spans="1:32" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A6" s="11">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="B6" s="26">
@@ -31304,7 +31300,7 @@
         <v>198.70199993</v>
       </c>
       <c r="D6" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>57</v>
       </c>
       <c r="E6" s="12">
@@ -31338,59 +31334,58 @@
       <c r="M6" s="12">
         <v>0</v>
       </c>
-      <c r="N6" s="6">
+      <c r="N6" s="25">
+        <v>271.94399931000004</v>
+      </c>
+      <c r="O6" s="30">
+        <v>60.383999889999991</v>
+      </c>
+      <c r="P6" s="6">
         <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="Q6" s="12">
+        <v>0</v>
+      </c>
+      <c r="R6" s="12">
+        <v>0</v>
+      </c>
+      <c r="S6" s="6">
+        <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="O6" s="12">
-        <v>0</v>
-      </c>
-      <c r="P6" s="6">
-        <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="Q6" s="12">
-        <v>0</v>
-      </c>
-      <c r="R6" s="12">
-        <v>0</v>
-      </c>
-      <c r="S6" s="6">
-        <f t="shared" si="6"/>
+      <c r="U6" s="11">
+        <f t="shared" si="8"/>
         <v>4</v>
       </c>
-      <c r="U6" s="11">
-        <f t="shared" si="9"/>
-        <v>4</v>
-      </c>
-      <c r="V6" s="37">
+      <c r="V6" s="34">
         <v>6619</v>
       </c>
-      <c r="W6" s="37">
+      <c r="W6" s="34">
         <v>8371</v>
       </c>
-      <c r="X6" s="37">
+      <c r="X6" s="34">
         <v>9279</v>
       </c>
-      <c r="Y6" s="37">
+      <c r="Y6" s="34">
         <v>10805</v>
       </c>
-      <c r="Z6" s="37">
+      <c r="Z6" s="34">
         <v>1271</v>
       </c>
-      <c r="AA6" s="37">
+      <c r="AA6" s="34">
         <v>3707</v>
       </c>
-      <c r="AB6" s="37">
+      <c r="AB6" s="34">
         <v>370</v>
       </c>
-      <c r="AC6" s="37">
+      <c r="AC6" s="34">
         <v>3336</v>
       </c>
     </row>
     <row r="7" spans="1:32" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A7" s="11">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>6</v>
       </c>
       <c r="B7" s="26">
@@ -31400,7 +31395,7 @@
         <v>181.98599990999998</v>
       </c>
       <c r="D7" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>83</v>
       </c>
       <c r="E7" s="12">
@@ -31434,59 +31429,58 @@
       <c r="M7" s="12">
         <v>0</v>
       </c>
-      <c r="N7" s="6">
+      <c r="N7" s="25">
+        <v>270.07199934000005</v>
+      </c>
+      <c r="O7" s="30">
+        <v>50.903999910000003</v>
+      </c>
+      <c r="P7" s="6">
         <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="O7" s="12">
-        <v>0</v>
-      </c>
-      <c r="P7" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="12">
+        <v>0</v>
+      </c>
+      <c r="R7" s="12">
+        <v>0</v>
+      </c>
+      <c r="S7" s="6">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Q7" s="12">
-        <v>0</v>
-      </c>
-      <c r="R7" s="12">
-        <v>0</v>
-      </c>
-      <c r="S7" s="6">
-        <f t="shared" si="6"/>
         <v>3</v>
       </c>
       <c r="U7" s="11">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>5</v>
       </c>
-      <c r="V7" s="37">
+      <c r="V7" s="34">
         <v>6676</v>
       </c>
-      <c r="W7" s="37">
+      <c r="W7" s="34">
         <v>8399</v>
       </c>
-      <c r="X7" s="37">
+      <c r="X7" s="34">
         <v>9281</v>
       </c>
-      <c r="Y7" s="37">
+      <c r="Y7" s="34">
         <v>10806</v>
       </c>
-      <c r="Z7" s="37">
+      <c r="Z7" s="34">
         <v>1271</v>
       </c>
-      <c r="AA7" s="37">
+      <c r="AA7" s="34">
         <v>3711</v>
       </c>
-      <c r="AB7" s="37">
+      <c r="AB7" s="34">
         <v>371</v>
       </c>
-      <c r="AC7" s="37">
+      <c r="AC7" s="34">
         <v>3340</v>
       </c>
     </row>
     <row r="8" spans="1:32" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A8" s="11">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>7</v>
       </c>
       <c r="B8" s="26">
@@ -31496,7 +31490,7 @@
         <v>171.31799996000004</v>
       </c>
       <c r="D8" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>34</v>
       </c>
       <c r="E8" s="12">
@@ -31530,59 +31524,58 @@
       <c r="M8" s="12">
         <v>0</v>
       </c>
-      <c r="N8" s="6">
+      <c r="N8" s="25">
+        <v>307.19999936999983</v>
+      </c>
+      <c r="O8" s="30">
+        <v>58.775999880000015</v>
+      </c>
+      <c r="P8" s="6">
         <f t="shared" si="4"/>
-        <v>7</v>
-      </c>
-      <c r="O8" s="12">
-        <v>0</v>
-      </c>
-      <c r="P8" s="6">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="12">
+        <v>0</v>
+      </c>
+      <c r="R8" s="12">
+        <v>0</v>
+      </c>
+      <c r="S8" s="6">
         <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="Q8" s="12">
-        <v>0</v>
-      </c>
-      <c r="R8" s="12">
-        <v>0</v>
-      </c>
-      <c r="S8" s="6">
-        <f t="shared" si="6"/>
         <v>4</v>
       </c>
       <c r="U8" s="11">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>6</v>
       </c>
-      <c r="V8" s="37">
+      <c r="V8" s="34">
         <v>6759</v>
       </c>
-      <c r="W8" s="37">
+      <c r="W8" s="34">
         <v>8479</v>
       </c>
-      <c r="X8" s="37">
+      <c r="X8" s="34">
         <v>9287</v>
       </c>
-      <c r="Y8" s="37">
+      <c r="Y8" s="34">
         <v>10807</v>
       </c>
-      <c r="Z8" s="37">
+      <c r="Z8" s="34">
         <v>1272</v>
       </c>
-      <c r="AA8" s="37">
+      <c r="AA8" s="34">
         <v>3712</v>
       </c>
-      <c r="AB8" s="37">
+      <c r="AB8" s="34">
         <v>371</v>
       </c>
-      <c r="AC8" s="37">
+      <c r="AC8" s="34">
         <v>3343</v>
       </c>
     </row>
     <row r="9" spans="1:32" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A9" s="11">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>8</v>
       </c>
       <c r="B9" s="26">
@@ -31592,7 +31585,7 @@
         <v>175.55999992</v>
       </c>
       <c r="D9" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>47</v>
       </c>
       <c r="E9" s="12">
@@ -31626,59 +31619,58 @@
       <c r="M9" s="12">
         <v>0</v>
       </c>
-      <c r="N9" s="6">
+      <c r="N9" s="25">
+        <v>298.75199937999969</v>
+      </c>
+      <c r="O9" s="30">
+        <v>51.5999999</v>
+      </c>
+      <c r="P9" s="6">
         <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q9" s="12">
+        <v>0</v>
+      </c>
+      <c r="R9" s="12">
+        <v>0</v>
+      </c>
+      <c r="S9" s="6">
+        <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="O9" s="12">
-        <v>0</v>
-      </c>
-      <c r="P9" s="6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Q9" s="12">
-        <v>0</v>
-      </c>
-      <c r="R9" s="12">
-        <v>0</v>
-      </c>
-      <c r="S9" s="6">
-        <f t="shared" si="6"/>
-        <v>4</v>
-      </c>
       <c r="U9" s="11">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>7</v>
       </c>
-      <c r="V9" s="37">
+      <c r="V9" s="34">
         <v>6793</v>
       </c>
-      <c r="W9" s="37">
+      <c r="W9" s="34">
         <v>8509</v>
       </c>
-      <c r="X9" s="37">
+      <c r="X9" s="34">
         <v>9291</v>
       </c>
-      <c r="Y9" s="37">
+      <c r="Y9" s="34">
         <v>10808</v>
       </c>
-      <c r="Z9" s="37">
+      <c r="Z9" s="34">
         <v>1273</v>
       </c>
-      <c r="AA9" s="37">
+      <c r="AA9" s="34">
         <v>3719</v>
       </c>
-      <c r="AB9" s="37">
+      <c r="AB9" s="34">
         <v>372</v>
       </c>
-      <c r="AC9" s="37">
+      <c r="AC9" s="34">
         <v>3347</v>
       </c>
     </row>
     <row r="10" spans="1:32" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A10" s="11">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>9</v>
       </c>
       <c r="B10" s="29">
@@ -31688,7 +31680,7 @@
         <v>200.04599990999998</v>
       </c>
       <c r="D10" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="E10" s="12">
@@ -31722,59 +31714,58 @@
       <c r="M10" s="12">
         <v>0</v>
       </c>
-      <c r="N10" s="6">
+      <c r="N10" s="25">
+        <v>284.18399930999988</v>
+      </c>
+      <c r="O10" s="30">
+        <v>61.7279999</v>
+      </c>
+      <c r="P10" s="6">
         <f t="shared" si="4"/>
-        <v>3</v>
-      </c>
-      <c r="O10" s="12">
-        <v>0</v>
-      </c>
-      <c r="P10" s="6">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="12">
+        <v>0</v>
+      </c>
+      <c r="R10" s="12">
+        <v>0</v>
+      </c>
+      <c r="S10" s="6">
         <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="Q10" s="12">
-        <v>0</v>
-      </c>
-      <c r="R10" s="12">
-        <v>0</v>
-      </c>
-      <c r="S10" s="6">
-        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="U10" s="11">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>8</v>
       </c>
-      <c r="V10" s="37">
+      <c r="V10" s="34">
         <v>6840</v>
       </c>
-      <c r="W10" s="37">
+      <c r="W10" s="34">
         <v>8572</v>
       </c>
-      <c r="X10" s="37">
+      <c r="X10" s="34">
         <v>9291</v>
       </c>
-      <c r="Y10" s="37">
+      <c r="Y10" s="34">
         <v>10808</v>
       </c>
-      <c r="Z10" s="37">
+      <c r="Z10" s="34">
         <v>1273</v>
       </c>
-      <c r="AA10" s="37">
+      <c r="AA10" s="34">
         <v>3723</v>
       </c>
-      <c r="AB10" s="37">
+      <c r="AB10" s="34">
         <v>372</v>
       </c>
-      <c r="AC10" s="37">
+      <c r="AC10" s="34">
         <v>3351</v>
       </c>
     </row>
     <row r="11" spans="1:32" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A11" s="11">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>10</v>
       </c>
       <c r="B11" s="29">
@@ -31784,7 +31775,7 @@
         <v>218.48399992999998</v>
       </c>
       <c r="D11" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>57</v>
       </c>
       <c r="E11" s="12">
@@ -31818,59 +31809,58 @@
       <c r="M11" s="12">
         <v>0</v>
       </c>
-      <c r="N11" s="6">
+      <c r="N11" s="25">
+        <v>257.42399933000002</v>
+      </c>
+      <c r="O11" s="30">
+        <v>57.263999889999994</v>
+      </c>
+      <c r="P11" s="6">
         <f t="shared" si="4"/>
-        <v>7</v>
-      </c>
-      <c r="O11" s="12">
-        <v>0</v>
-      </c>
-      <c r="P11" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="12">
+        <v>0</v>
+      </c>
+      <c r="R11" s="12">
+        <v>0</v>
+      </c>
+      <c r="S11" s="6">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Q11" s="12">
-        <v>0</v>
-      </c>
-      <c r="R11" s="12">
-        <v>0</v>
-      </c>
-      <c r="S11" s="6">
-        <f t="shared" si="6"/>
         <v>8</v>
       </c>
       <c r="U11" s="11">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>9</v>
       </c>
-      <c r="V11" s="37">
+      <c r="V11" s="34">
         <v>6845</v>
       </c>
-      <c r="W11" s="37">
+      <c r="W11" s="34">
         <v>8607</v>
       </c>
-      <c r="X11" s="37">
+      <c r="X11" s="34">
         <v>9299</v>
       </c>
-      <c r="Y11" s="37">
+      <c r="Y11" s="34">
         <v>10809</v>
       </c>
-      <c r="Z11" s="37">
+      <c r="Z11" s="34">
         <v>1273</v>
       </c>
-      <c r="AA11" s="37">
+      <c r="AA11" s="34">
         <v>3726</v>
       </c>
-      <c r="AB11" s="37">
+      <c r="AB11" s="34">
         <v>373</v>
       </c>
-      <c r="AC11" s="37">
+      <c r="AC11" s="34">
         <v>3351</v>
       </c>
     </row>
     <row r="12" spans="1:32" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A12" s="11">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>11</v>
       </c>
       <c r="B12" s="29">
@@ -31880,7 +31870,7 @@
         <v>196.81199991</v>
       </c>
       <c r="D12" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>15</v>
       </c>
       <c r="E12" s="12">
@@ -31914,69 +31904,68 @@
       <c r="M12" s="12">
         <v>0</v>
       </c>
-      <c r="N12" s="6">
+      <c r="N12" s="25">
+        <v>234.59999937999976</v>
+      </c>
+      <c r="O12" s="30">
+        <v>53.855999909999987</v>
+      </c>
+      <c r="P12" s="6">
         <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q12" s="12">
+        <v>0</v>
+      </c>
+      <c r="R12" s="12">
+        <v>0</v>
+      </c>
+      <c r="S12" s="6">
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="O12" s="12">
-        <v>0</v>
-      </c>
-      <c r="P12" s="6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Q12" s="12">
-        <v>0</v>
-      </c>
-      <c r="R12" s="12">
-        <v>0</v>
-      </c>
-      <c r="S12" s="6">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
       <c r="U12" s="11">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
-      <c r="V12" s="37">
+      <c r="V12" s="34">
         <v>6902</v>
       </c>
-      <c r="W12" s="37">
+      <c r="W12" s="34">
         <v>8690</v>
       </c>
-      <c r="X12" s="37">
+      <c r="X12" s="34">
         <v>9302</v>
       </c>
-      <c r="Y12" s="37">
+      <c r="Y12" s="34">
         <v>10810</v>
       </c>
-      <c r="Z12" s="37">
+      <c r="Z12" s="34">
         <v>1273</v>
       </c>
-      <c r="AA12" s="37">
+      <c r="AA12" s="34">
         <v>3733</v>
       </c>
-      <c r="AB12" s="37">
+      <c r="AB12" s="34">
         <v>373</v>
       </c>
-      <c r="AC12" s="37">
+      <c r="AC12" s="34">
         <v>3359</v>
       </c>
     </row>
     <row r="13" spans="1:32" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A13" s="11">
+        <f t="shared" si="6"/>
+        <v>12</v>
+      </c>
+      <c r="B13" s="30">
+        <v>1172.72399954</v>
+      </c>
+      <c r="C13" s="30">
+        <v>182.99399991000001</v>
+      </c>
+      <c r="D13" s="6">
         <f t="shared" si="7"/>
-        <v>12</v>
-      </c>
-      <c r="B13" s="12">
-        <v>0</v>
-      </c>
-      <c r="C13" s="12">
-        <v>0</v>
-      </c>
-      <c r="D13" s="6">
-        <f t="shared" si="8"/>
         <v>112</v>
       </c>
       <c r="E13" s="12">
@@ -32010,69 +31999,68 @@
       <c r="M13" s="12">
         <v>0</v>
       </c>
-      <c r="N13" s="6">
+      <c r="N13" s="25">
+        <v>218.42399931000006</v>
+      </c>
+      <c r="O13" s="30">
+        <v>59.23199988999999</v>
+      </c>
+      <c r="P13" s="6">
         <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="Q13" s="12">
+        <v>0</v>
+      </c>
+      <c r="R13" s="12">
+        <v>0</v>
+      </c>
+      <c r="S13" s="6">
+        <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="O13" s="12">
-        <v>0</v>
-      </c>
-      <c r="P13" s="6">
-        <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="Q13" s="12">
-        <v>0</v>
-      </c>
-      <c r="R13" s="12">
-        <v>0</v>
-      </c>
-      <c r="S13" s="6">
-        <f t="shared" si="6"/>
-        <v>4</v>
-      </c>
       <c r="U13" s="11">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>11</v>
       </c>
-      <c r="V13" s="37">
+      <c r="V13" s="34">
         <v>6917</v>
       </c>
-      <c r="W13" s="37">
+      <c r="W13" s="34">
         <v>8710</v>
       </c>
-      <c r="X13" s="37">
+      <c r="X13" s="34">
         <v>9309</v>
       </c>
-      <c r="Y13" s="37">
+      <c r="Y13" s="34">
         <v>10811</v>
       </c>
-      <c r="Z13" s="37">
+      <c r="Z13" s="34">
         <v>1274</v>
       </c>
-      <c r="AA13" s="37">
+      <c r="AA13" s="34">
         <v>3734</v>
       </c>
-      <c r="AB13" s="37">
+      <c r="AB13" s="34">
         <v>373</v>
       </c>
-      <c r="AC13" s="37">
+      <c r="AC13" s="34">
         <v>3360</v>
       </c>
     </row>
     <row r="14" spans="1:32" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A14" s="11">
+        <f t="shared" si="6"/>
+        <v>13</v>
+      </c>
+      <c r="B14" s="30">
+        <v>1072.5959995599997</v>
+      </c>
+      <c r="C14" s="30">
+        <v>179.17199994999999</v>
+      </c>
+      <c r="D14" s="6">
         <f t="shared" si="7"/>
-        <v>13</v>
-      </c>
-      <c r="B14" s="12">
-        <v>0</v>
-      </c>
-      <c r="C14" s="12">
-        <v>0</v>
-      </c>
-      <c r="D14" s="6">
-        <f t="shared" si="8"/>
         <v>65</v>
       </c>
       <c r="E14" s="12">
@@ -32106,83 +32094,82 @@
       <c r="M14" s="12">
         <v>0</v>
       </c>
-      <c r="N14" s="6">
+      <c r="N14" s="25">
+        <v>236.87999939999992</v>
+      </c>
+      <c r="O14" s="30">
+        <v>49.919999920000002</v>
+      </c>
+      <c r="P14" s="6">
         <f t="shared" si="4"/>
-        <v>9</v>
-      </c>
-      <c r="O14" s="12">
-        <v>0</v>
-      </c>
-      <c r="P14" s="6">
+        <v>2</v>
+      </c>
+      <c r="Q14" s="12">
+        <v>0</v>
+      </c>
+      <c r="R14" s="12">
+        <v>0</v>
+      </c>
+      <c r="S14" s="6">
         <f t="shared" si="5"/>
-        <v>2</v>
-      </c>
-      <c r="Q14" s="12">
-        <v>0</v>
-      </c>
-      <c r="R14" s="12">
-        <v>0</v>
-      </c>
-      <c r="S14" s="6">
-        <f t="shared" si="6"/>
         <v>7</v>
       </c>
       <c r="U14" s="11">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>12</v>
       </c>
-      <c r="V14" s="37">
+      <c r="V14" s="34">
         <v>7029</v>
       </c>
-      <c r="W14" s="37">
+      <c r="W14" s="34">
         <v>8819</v>
       </c>
-      <c r="X14" s="37">
+      <c r="X14" s="34">
         <v>9312</v>
       </c>
-      <c r="Y14" s="37">
+      <c r="Y14" s="34">
         <v>10811</v>
       </c>
-      <c r="Z14" s="37">
+      <c r="Z14" s="34">
         <v>1274</v>
       </c>
-      <c r="AA14" s="37">
+      <c r="AA14" s="34">
         <v>3738</v>
       </c>
-      <c r="AB14" s="37">
+      <c r="AB14" s="34">
         <v>374</v>
       </c>
-      <c r="AC14" s="37">
+      <c r="AC14" s="34">
         <v>3364</v>
       </c>
     </row>
     <row r="15" spans="1:32" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A15" s="11">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>14</v>
       </c>
-      <c r="B15" s="12">
-        <v>0</v>
-      </c>
-      <c r="C15" s="12">
-        <v>0</v>
+      <c r="B15" s="30">
+        <v>954.02999946999989</v>
+      </c>
+      <c r="C15" s="30">
+        <v>150.77999991000002</v>
       </c>
       <c r="D15" s="6">
-        <f t="shared" ref="D15:D31" si="10">V16-V15</f>
+        <f t="shared" ref="D15:D31" si="9">V16-V15</f>
         <v>0</v>
       </c>
       <c r="E15" s="12">
         <v>0</v>
       </c>
       <c r="F15" s="6">
-        <f t="shared" ref="F15:F31" si="11">W16-W15</f>
+        <f t="shared" ref="F15:F31" si="10">W16-W15</f>
         <v>0</v>
       </c>
       <c r="G15" s="12">
         <v>0</v>
       </c>
       <c r="H15" s="6">
-        <f t="shared" ref="H15:H31" si="12">X16-X15</f>
+        <f t="shared" ref="H15:H31" si="11">X16-X15</f>
         <v>0</v>
       </c>
       <c r="I15" s="12">
@@ -32195,21 +32182,20 @@
         <v>0</v>
       </c>
       <c r="L15" s="6">
-        <f t="shared" ref="L15:L31" si="13">Z16-Z15</f>
+        <f t="shared" ref="L15:L31" si="12">Z16-Z15</f>
         <v>0</v>
       </c>
       <c r="M15" s="12">
         <v>0</v>
       </c>
-      <c r="N15" s="6">
-        <f t="shared" ref="N15:N31" si="14">AA16-AA15</f>
-        <v>0</v>
-      </c>
-      <c r="O15" s="12">
-        <v>0</v>
+      <c r="N15" s="25">
+        <v>249.3839993399998</v>
+      </c>
+      <c r="O15" s="30">
+        <v>56.927999889999995</v>
       </c>
       <c r="P15" s="6">
-        <f t="shared" ref="P15:P31" si="15">AB16-AB15</f>
+        <f t="shared" ref="P15:P31" si="13">AB16-AB15</f>
         <v>0</v>
       </c>
       <c r="Q15" s="12">
@@ -32219,1148 +32205,1136 @@
         <v>0</v>
       </c>
       <c r="S15" s="6">
-        <f t="shared" ref="S15:S31" si="16">AC16-AC15</f>
+        <f t="shared" ref="S15:S31" si="14">AC16-AC15</f>
         <v>0</v>
       </c>
       <c r="U15" s="11">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>13</v>
       </c>
-      <c r="V15" s="37">
+      <c r="V15" s="34">
         <v>7094</v>
       </c>
-      <c r="W15" s="37">
+      <c r="W15" s="34">
         <v>8914</v>
       </c>
-      <c r="X15" s="37">
+      <c r="X15" s="34">
         <v>9318</v>
       </c>
-      <c r="Y15" s="37">
+      <c r="Y15" s="34">
         <v>10812</v>
       </c>
-      <c r="Z15" s="37">
+      <c r="Z15" s="34">
         <v>1275</v>
       </c>
-      <c r="AA15" s="37">
+      <c r="AA15" s="34">
         <v>3747</v>
       </c>
-      <c r="AB15" s="37">
+      <c r="AB15" s="34">
         <v>376</v>
       </c>
-      <c r="AC15" s="37">
+      <c r="AC15" s="34">
         <v>3371</v>
       </c>
     </row>
     <row r="16" spans="1:32" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A16" s="11">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>15</v>
       </c>
-      <c r="B16" s="12">
-        <v>0</v>
-      </c>
-      <c r="C16" s="12">
-        <v>0</v>
+      <c r="B16" s="30">
+        <v>836.55599950999988</v>
+      </c>
+      <c r="C16" s="30">
+        <v>164.80799992999997</v>
       </c>
       <c r="D16" s="6">
+        <f t="shared" si="9"/>
+        <v>43</v>
+      </c>
+      <c r="E16" s="12">
+        <v>0</v>
+      </c>
+      <c r="F16" s="6">
         <f t="shared" si="10"/>
-        <v>43</v>
-      </c>
-      <c r="E16" s="12">
-        <v>0</v>
-      </c>
-      <c r="F16" s="6">
+        <v>44</v>
+      </c>
+      <c r="G16" s="12">
+        <v>0</v>
+      </c>
+      <c r="H16" s="6">
         <f t="shared" si="11"/>
-        <v>44</v>
-      </c>
-      <c r="G16" s="12">
-        <v>0</v>
-      </c>
-      <c r="H16" s="6">
+        <v>4</v>
+      </c>
+      <c r="I16" s="12">
+        <v>0</v>
+      </c>
+      <c r="J16" s="6">
+        <f t="shared" ref="J16:J31" si="15">Y17-Y16</f>
+        <v>1</v>
+      </c>
+      <c r="K16" s="12">
+        <v>0</v>
+      </c>
+      <c r="L16" s="6">
         <f t="shared" si="12"/>
-        <v>4</v>
-      </c>
-      <c r="I16" s="12">
-        <v>0</v>
-      </c>
-      <c r="J16" s="6">
-        <f t="shared" ref="J16:J31" si="17">Y17-Y16</f>
-        <v>1</v>
-      </c>
-      <c r="K16" s="12">
-        <v>0</v>
-      </c>
-      <c r="L16" s="6">
+        <v>0</v>
+      </c>
+      <c r="M16" s="12">
+        <v>0</v>
+      </c>
+      <c r="N16" s="25">
+        <v>245.54399935999982</v>
+      </c>
+      <c r="O16" s="30">
+        <v>48.695999909999998</v>
+      </c>
+      <c r="P16" s="6">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="M16" s="12">
-        <v>0</v>
-      </c>
-      <c r="N16" s="6">
+      <c r="Q16" s="12">
+        <v>0</v>
+      </c>
+      <c r="R16" s="12">
+        <v>0</v>
+      </c>
+      <c r="S16" s="6">
         <f t="shared" si="14"/>
         <v>4</v>
       </c>
-      <c r="O16" s="12">
-        <v>0</v>
-      </c>
-      <c r="P16" s="6">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="Q16" s="12">
-        <v>0</v>
-      </c>
-      <c r="R16" s="12">
-        <v>0</v>
-      </c>
-      <c r="S16" s="6">
-        <f t="shared" si="16"/>
-        <v>4</v>
-      </c>
       <c r="U16" s="11">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>14</v>
       </c>
-      <c r="V16" s="37">
+      <c r="V16" s="34">
         <v>7094</v>
       </c>
-      <c r="W16" s="37">
+      <c r="W16" s="34">
         <v>8914</v>
       </c>
-      <c r="X16" s="37">
+      <c r="X16" s="34">
         <v>9318</v>
       </c>
-      <c r="Y16" s="37">
+      <c r="Y16" s="34">
         <v>10812</v>
       </c>
-      <c r="Z16" s="37">
+      <c r="Z16" s="34">
         <v>1275</v>
       </c>
-      <c r="AA16" s="37">
+      <c r="AA16" s="34">
         <v>3747</v>
       </c>
-      <c r="AB16" s="37">
+      <c r="AB16" s="34">
         <v>376</v>
       </c>
-      <c r="AC16" s="37">
+      <c r="AC16" s="34">
         <v>3371</v>
       </c>
     </row>
     <row r="17" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A17" s="11">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>16</v>
       </c>
-      <c r="B17" s="12">
-        <v>0</v>
-      </c>
-      <c r="C17" s="12">
-        <v>0</v>
+      <c r="B17" s="30">
+        <v>1224.4259995499992</v>
+      </c>
+      <c r="C17" s="30">
+        <v>204.11999993999996</v>
       </c>
       <c r="D17" s="6">
+        <f t="shared" si="9"/>
+        <v>5</v>
+      </c>
+      <c r="E17" s="12">
+        <v>0</v>
+      </c>
+      <c r="F17" s="6">
         <f t="shared" si="10"/>
-        <v>5</v>
-      </c>
-      <c r="E17" s="12">
-        <v>0</v>
-      </c>
-      <c r="F17" s="6">
+        <v>20</v>
+      </c>
+      <c r="G17" s="12">
+        <v>0</v>
+      </c>
+      <c r="H17" s="6">
         <f t="shared" si="11"/>
-        <v>20</v>
-      </c>
-      <c r="G17" s="12">
-        <v>0</v>
-      </c>
-      <c r="H17" s="6">
+        <v>1</v>
+      </c>
+      <c r="I17" s="12">
+        <v>0</v>
+      </c>
+      <c r="J17" s="6">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="K17" s="12">
+        <v>0</v>
+      </c>
+      <c r="L17" s="6">
         <f t="shared" si="12"/>
-        <v>1</v>
-      </c>
-      <c r="I17" s="12">
-        <v>0</v>
-      </c>
-      <c r="J17" s="6">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="K17" s="12">
-        <v>0</v>
-      </c>
-      <c r="L17" s="6">
+        <v>0</v>
+      </c>
+      <c r="M17" s="12">
+        <v>0</v>
+      </c>
+      <c r="N17" s="25">
+        <v>238.60799944999999</v>
+      </c>
+      <c r="O17" s="30">
+        <v>61.103999920000007</v>
+      </c>
+      <c r="P17" s="6">
         <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="M17" s="12">
-        <v>0</v>
-      </c>
-      <c r="N17" s="6">
+        <v>3</v>
+      </c>
+      <c r="Q17" s="12">
+        <v>0</v>
+      </c>
+      <c r="R17" s="12">
+        <v>0</v>
+      </c>
+      <c r="S17" s="6">
         <f t="shared" si="14"/>
         <v>4</v>
       </c>
-      <c r="O17" s="12">
-        <v>0</v>
-      </c>
-      <c r="P17" s="6">
-        <f t="shared" si="15"/>
-        <v>3</v>
-      </c>
-      <c r="Q17" s="12">
-        <v>0</v>
-      </c>
-      <c r="R17" s="12">
-        <v>0</v>
-      </c>
-      <c r="S17" s="6">
-        <f t="shared" si="16"/>
-        <v>4</v>
-      </c>
       <c r="U17" s="11">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>15</v>
       </c>
-      <c r="V17" s="37">
+      <c r="V17" s="34">
         <v>7137</v>
       </c>
-      <c r="W17" s="37">
+      <c r="W17" s="34">
         <v>8958</v>
       </c>
-      <c r="X17" s="37">
+      <c r="X17" s="34">
         <v>9322</v>
       </c>
-      <c r="Y17" s="37">
+      <c r="Y17" s="34">
         <v>10813</v>
       </c>
-      <c r="Z17" s="37">
+      <c r="Z17" s="34">
         <v>1275</v>
       </c>
-      <c r="AA17" s="37">
+      <c r="AA17" s="34">
         <v>3751</v>
       </c>
-      <c r="AB17" s="37">
+      <c r="AB17" s="34">
         <v>376</v>
       </c>
-      <c r="AC17" s="37">
+      <c r="AC17" s="34">
         <v>3375</v>
       </c>
     </row>
     <row r="18" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A18" s="15">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>17</v>
       </c>
-      <c r="B18" s="12">
-        <v>0</v>
-      </c>
-      <c r="C18" s="12">
-        <v>0</v>
+      <c r="B18" s="30">
+        <v>1213.6739995099997</v>
+      </c>
+      <c r="C18" s="30">
+        <v>181.48199990000003</v>
       </c>
       <c r="D18" s="6">
+        <f t="shared" si="9"/>
+        <v>50</v>
+      </c>
+      <c r="E18" s="12">
+        <v>0</v>
+      </c>
+      <c r="F18" s="6">
         <f t="shared" si="10"/>
-        <v>50</v>
-      </c>
-      <c r="E18" s="12">
-        <v>0</v>
-      </c>
-      <c r="F18" s="6">
+        <v>32</v>
+      </c>
+      <c r="G18" s="12">
+        <v>0</v>
+      </c>
+      <c r="H18" s="6">
         <f t="shared" si="11"/>
-        <v>32</v>
-      </c>
-      <c r="G18" s="12">
-        <v>0</v>
-      </c>
-      <c r="H18" s="6">
+        <v>5</v>
+      </c>
+      <c r="I18" s="12">
+        <v>0</v>
+      </c>
+      <c r="J18" s="6">
+        <f t="shared" si="15"/>
+        <v>2</v>
+      </c>
+      <c r="K18" s="12">
+        <v>0</v>
+      </c>
+      <c r="L18" s="6">
         <f t="shared" si="12"/>
-        <v>5</v>
-      </c>
-      <c r="I18" s="12">
-        <v>0</v>
-      </c>
-      <c r="J18" s="6">
-        <f t="shared" si="17"/>
-        <v>2</v>
-      </c>
-      <c r="K18" s="12">
-        <v>0</v>
-      </c>
-      <c r="L18" s="6">
+        <v>0</v>
+      </c>
+      <c r="M18" s="12">
+        <v>0</v>
+      </c>
+      <c r="N18" s="25">
+        <v>280.77599930999969</v>
+      </c>
+      <c r="O18" s="30">
+        <v>58.439999899999997</v>
+      </c>
+      <c r="P18" s="6">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="M18" s="12">
-        <v>0</v>
-      </c>
-      <c r="N18" s="6">
+      <c r="Q18" s="12">
+        <v>0</v>
+      </c>
+      <c r="R18" s="12">
+        <v>0</v>
+      </c>
+      <c r="S18" s="6">
         <f t="shared" si="14"/>
         <v>2</v>
       </c>
-      <c r="O18" s="12">
-        <v>0</v>
-      </c>
-      <c r="P18" s="6">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="Q18" s="12">
-        <v>0</v>
-      </c>
-      <c r="R18" s="12">
-        <v>0</v>
-      </c>
-      <c r="S18" s="6">
-        <f t="shared" si="16"/>
-        <v>2</v>
-      </c>
       <c r="U18" s="11">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>16</v>
       </c>
-      <c r="V18" s="37">
+      <c r="V18" s="34">
         <v>7142</v>
       </c>
-      <c r="W18" s="37">
+      <c r="W18" s="34">
         <v>8978</v>
       </c>
-      <c r="X18" s="37">
+      <c r="X18" s="34">
         <v>9323</v>
       </c>
-      <c r="Y18" s="37">
+      <c r="Y18" s="34">
         <v>10813</v>
       </c>
-      <c r="Z18" s="37">
+      <c r="Z18" s="34">
         <v>1275</v>
       </c>
-      <c r="AA18" s="37">
+      <c r="AA18" s="34">
         <v>3755</v>
       </c>
-      <c r="AB18" s="37">
+      <c r="AB18" s="34">
         <v>379</v>
       </c>
-      <c r="AC18" s="37">
+      <c r="AC18" s="34">
         <v>3379</v>
       </c>
     </row>
     <row r="19" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A19" s="15">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>18</v>
       </c>
-      <c r="B19" s="12">
-        <v>0</v>
-      </c>
-      <c r="C19" s="12">
-        <v>0</v>
+      <c r="B19" s="30">
+        <v>1310.2739995399993</v>
+      </c>
+      <c r="C19" s="30">
+        <v>180.97799992</v>
       </c>
       <c r="D19" s="6">
+        <f t="shared" si="9"/>
+        <v>134</v>
+      </c>
+      <c r="E19" s="12">
+        <v>0</v>
+      </c>
+      <c r="F19" s="6">
         <f t="shared" si="10"/>
-        <v>134</v>
-      </c>
-      <c r="E19" s="12">
-        <v>0</v>
-      </c>
-      <c r="F19" s="6">
+        <v>110</v>
+      </c>
+      <c r="G19" s="12">
+        <v>0</v>
+      </c>
+      <c r="H19" s="6">
         <f t="shared" si="11"/>
-        <v>110</v>
-      </c>
-      <c r="G19" s="12">
-        <v>0</v>
-      </c>
-      <c r="H19" s="6">
+        <v>11</v>
+      </c>
+      <c r="I19" s="12">
+        <v>0</v>
+      </c>
+      <c r="J19" s="6">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="K19" s="12">
+        <v>0</v>
+      </c>
+      <c r="L19" s="6">
         <f t="shared" si="12"/>
-        <v>11</v>
-      </c>
-      <c r="I19" s="12">
-        <v>0</v>
-      </c>
-      <c r="J19" s="6">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="K19" s="12">
-        <v>0</v>
-      </c>
-      <c r="L19" s="6">
+        <v>0</v>
+      </c>
+      <c r="M19" s="12">
+        <v>0</v>
+      </c>
+      <c r="N19" s="25">
+        <v>266.35199933999979</v>
+      </c>
+      <c r="O19" s="30">
+        <v>61.583999880000007</v>
+      </c>
+      <c r="P19" s="6">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="M19" s="12">
-        <v>0</v>
-      </c>
-      <c r="N19" s="6">
+      <c r="Q19" s="12">
+        <v>0</v>
+      </c>
+      <c r="R19" s="12">
+        <v>0</v>
+      </c>
+      <c r="S19" s="6">
         <f t="shared" si="14"/>
-        <v>14</v>
-      </c>
-      <c r="O19" s="12">
-        <v>0</v>
-      </c>
-      <c r="P19" s="6">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="Q19" s="12">
-        <v>0</v>
-      </c>
-      <c r="R19" s="12">
-        <v>0</v>
-      </c>
-      <c r="S19" s="6">
-        <f t="shared" si="16"/>
         <v>12</v>
       </c>
       <c r="T19" s="16"/>
       <c r="U19" s="11">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>17</v>
       </c>
-      <c r="V19" s="37">
+      <c r="V19" s="34">
         <v>7192</v>
       </c>
-      <c r="W19" s="37">
+      <c r="W19" s="34">
         <v>9010</v>
       </c>
-      <c r="X19" s="37">
+      <c r="X19" s="34">
         <v>9328</v>
       </c>
-      <c r="Y19" s="37">
+      <c r="Y19" s="34">
         <v>10815</v>
       </c>
-      <c r="Z19" s="37">
+      <c r="Z19" s="34">
         <v>1275</v>
       </c>
-      <c r="AA19" s="37">
+      <c r="AA19" s="34">
         <v>3757</v>
       </c>
-      <c r="AB19" s="37">
+      <c r="AB19" s="34">
         <v>379</v>
       </c>
-      <c r="AC19" s="37">
+      <c r="AC19" s="34">
         <v>3381</v>
       </c>
     </row>
     <row r="20" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A20" s="15">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>19</v>
       </c>
-      <c r="B20" s="12">
-        <v>0</v>
-      </c>
-      <c r="C20" s="12">
-        <v>0</v>
+      <c r="B20" s="30">
+        <v>911.56799946999968</v>
+      </c>
+      <c r="C20" s="30">
+        <v>168.5039999</v>
       </c>
       <c r="D20" s="6">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="E20" s="12">
+        <v>0</v>
+      </c>
+      <c r="F20" s="6">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="E20" s="12">
-        <v>0</v>
-      </c>
-      <c r="F20" s="6">
+      <c r="G20" s="12">
+        <v>0</v>
+      </c>
+      <c r="H20" s="6">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="G20" s="12">
-        <v>0</v>
-      </c>
-      <c r="H20" s="6">
+      <c r="I20" s="12">
+        <v>0</v>
+      </c>
+      <c r="J20" s="6">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="K20" s="12">
+        <v>0</v>
+      </c>
+      <c r="L20" s="6">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="I20" s="12">
-        <v>0</v>
-      </c>
-      <c r="J20" s="6">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="K20" s="12">
-        <v>0</v>
-      </c>
-      <c r="L20" s="6">
+      <c r="M20" s="12">
+        <v>0</v>
+      </c>
+      <c r="N20" s="25">
+        <v>306.4799993999996</v>
+      </c>
+      <c r="O20" s="30">
+        <v>57.959999910000008</v>
+      </c>
+      <c r="P20" s="6">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="M20" s="12">
-        <v>0</v>
-      </c>
-      <c r="N20" s="6">
+      <c r="Q20" s="12">
+        <v>0</v>
+      </c>
+      <c r="R20" s="12">
+        <v>0</v>
+      </c>
+      <c r="S20" s="6">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="O20" s="12">
-        <v>0</v>
-      </c>
-      <c r="P20" s="6">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="Q20" s="12">
-        <v>0</v>
-      </c>
-      <c r="R20" s="12">
-        <v>0</v>
-      </c>
-      <c r="S20" s="6">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
       <c r="U20" s="11">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>18</v>
       </c>
-      <c r="V20" s="37">
+      <c r="V20" s="34">
         <v>7326</v>
       </c>
-      <c r="W20" s="37">
+      <c r="W20" s="34">
         <v>9120</v>
       </c>
-      <c r="X20" s="37">
+      <c r="X20" s="34">
         <v>9339</v>
       </c>
-      <c r="Y20" s="37">
+      <c r="Y20" s="34">
         <v>10815</v>
       </c>
-      <c r="Z20" s="37">
+      <c r="Z20" s="34">
         <v>1275</v>
       </c>
-      <c r="AA20" s="37">
+      <c r="AA20" s="34">
         <v>3771</v>
       </c>
-      <c r="AB20" s="37">
+      <c r="AB20" s="34">
         <v>379</v>
       </c>
-      <c r="AC20" s="37">
+      <c r="AC20" s="34">
         <v>3393</v>
       </c>
     </row>
     <row r="21" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A21" s="15">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>20</v>
       </c>
-      <c r="B21" s="12">
-        <v>0</v>
-      </c>
-      <c r="C21" s="12">
-        <v>0</v>
+      <c r="B21" s="30">
+        <v>996.32399944999884</v>
+      </c>
+      <c r="C21" s="30">
+        <v>166.10999993000001</v>
       </c>
       <c r="D21" s="6">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="E21" s="12">
+        <v>0</v>
+      </c>
+      <c r="F21" s="6">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="E21" s="12">
-        <v>0</v>
-      </c>
-      <c r="F21" s="6">
+      <c r="G21" s="12">
+        <v>0</v>
+      </c>
+      <c r="H21" s="6">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="G21" s="12">
-        <v>0</v>
-      </c>
-      <c r="H21" s="6">
+      <c r="I21" s="12">
+        <v>0</v>
+      </c>
+      <c r="J21" s="6">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="K21" s="12">
+        <v>0</v>
+      </c>
+      <c r="L21" s="6">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="I21" s="12">
-        <v>0</v>
-      </c>
-      <c r="J21" s="6">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="K21" s="12">
-        <v>0</v>
-      </c>
-      <c r="L21" s="6">
+      <c r="M21" s="12">
+        <v>0</v>
+      </c>
+      <c r="N21" s="25">
+        <v>307.53599938999997</v>
+      </c>
+      <c r="O21" s="30">
+        <v>62.831999879999998</v>
+      </c>
+      <c r="P21" s="6">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="M21" s="12">
-        <v>0</v>
-      </c>
-      <c r="N21" s="6">
+      <c r="Q21" s="12">
+        <v>0</v>
+      </c>
+      <c r="R21" s="12">
+        <v>0</v>
+      </c>
+      <c r="S21" s="6">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="O21" s="12">
-        <v>0</v>
-      </c>
-      <c r="P21" s="6">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="Q21" s="12">
-        <v>0</v>
-      </c>
-      <c r="R21" s="12">
-        <v>0</v>
-      </c>
-      <c r="S21" s="6">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
       <c r="U21" s="11">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>19</v>
       </c>
-      <c r="V21" s="37">
+      <c r="V21" s="34">
         <v>7326</v>
       </c>
-      <c r="W21" s="37">
+      <c r="W21" s="34">
         <v>9120</v>
       </c>
-      <c r="X21" s="37">
+      <c r="X21" s="34">
         <v>9339</v>
       </c>
-      <c r="Y21" s="37">
+      <c r="Y21" s="34">
         <v>10815</v>
       </c>
-      <c r="Z21" s="37">
+      <c r="Z21" s="34">
         <v>1275</v>
       </c>
-      <c r="AA21" s="37">
+      <c r="AA21" s="34">
         <v>3771</v>
       </c>
-      <c r="AB21" s="37">
+      <c r="AB21" s="34">
         <v>379</v>
       </c>
-      <c r="AC21" s="37">
+      <c r="AC21" s="34">
         <v>3393</v>
       </c>
     </row>
     <row r="22" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A22" s="15">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>21</v>
       </c>
-      <c r="B22" s="12">
-        <v>0</v>
-      </c>
-      <c r="C22" s="12">
-        <v>0</v>
+      <c r="B22" s="30">
+        <v>1084.3979994999995</v>
+      </c>
+      <c r="C22" s="30">
+        <v>182.44799993000001</v>
       </c>
       <c r="D22" s="6">
+        <f t="shared" si="9"/>
+        <v>20</v>
+      </c>
+      <c r="E22" s="12">
+        <v>0</v>
+      </c>
+      <c r="F22" s="6">
         <f t="shared" si="10"/>
+        <v>29</v>
+      </c>
+      <c r="G22" s="12">
+        <v>0</v>
+      </c>
+      <c r="H22" s="6">
+        <f t="shared" si="11"/>
+        <v>3</v>
+      </c>
+      <c r="I22" s="12">
+        <v>0</v>
+      </c>
+      <c r="J22" s="6">
+        <f t="shared" si="15"/>
+        <v>1</v>
+      </c>
+      <c r="K22" s="12">
+        <v>0</v>
+      </c>
+      <c r="L22" s="6">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="M22" s="12">
+        <v>0</v>
+      </c>
+      <c r="N22" s="25">
+        <v>310.70399932999993</v>
+      </c>
+      <c r="O22" s="30">
+        <v>61.223999889999995</v>
+      </c>
+      <c r="P22" s="6">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="Q22" s="12">
+        <v>0</v>
+      </c>
+      <c r="R22" s="12">
+        <v>0</v>
+      </c>
+      <c r="S22" s="6">
+        <f t="shared" si="14"/>
+        <v>4</v>
+      </c>
+      <c r="U22" s="11">
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
-      <c r="E22" s="12">
-        <v>0</v>
-      </c>
-      <c r="F22" s="6">
+      <c r="V22" s="34">
+        <v>7326</v>
+      </c>
+      <c r="W22" s="34">
+        <v>9120</v>
+      </c>
+      <c r="X22" s="34">
+        <v>9339</v>
+      </c>
+      <c r="Y22" s="34">
+        <v>10815</v>
+      </c>
+      <c r="Z22" s="34">
+        <v>1275</v>
+      </c>
+      <c r="AA22" s="34">
+        <v>3771</v>
+      </c>
+      <c r="AB22" s="34">
+        <v>379</v>
+      </c>
+      <c r="AC22" s="34">
+        <v>3393</v>
+      </c>
+    </row>
+    <row r="23" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A23" s="15">
+        <f t="shared" si="6"/>
+        <v>22</v>
+      </c>
+      <c r="B23" s="30">
+        <v>909.04799958000001</v>
+      </c>
+      <c r="C23" s="30">
+        <v>152.54399995999998</v>
+      </c>
+      <c r="D23" s="6">
+        <f t="shared" si="9"/>
+        <v>28</v>
+      </c>
+      <c r="E23" s="12">
+        <v>0</v>
+      </c>
+      <c r="F23" s="6">
+        <f t="shared" si="10"/>
+        <v>55</v>
+      </c>
+      <c r="G23" s="12">
+        <v>0</v>
+      </c>
+      <c r="H23" s="6">
         <f t="shared" si="11"/>
-        <v>29</v>
-      </c>
-      <c r="G22" s="12">
-        <v>0</v>
-      </c>
-      <c r="H22" s="6">
+        <v>3</v>
+      </c>
+      <c r="I23" s="12">
+        <v>0</v>
+      </c>
+      <c r="J23" s="6">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="K23" s="12">
+        <v>0</v>
+      </c>
+      <c r="L23" s="6">
         <f t="shared" si="12"/>
-        <v>3</v>
-      </c>
-      <c r="I22" s="12">
-        <v>0</v>
-      </c>
-      <c r="J22" s="6">
-        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="M23" s="12">
+        <v>0</v>
+      </c>
+      <c r="N23" s="25">
+        <v>306.8159992799998</v>
+      </c>
+      <c r="O23" s="30">
+        <v>57.695999899999997</v>
+      </c>
+      <c r="P23" s="6">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="Q23" s="12">
+        <v>0</v>
+      </c>
+      <c r="R23" s="12">
+        <v>0</v>
+      </c>
+      <c r="S23" s="6">
+        <f t="shared" si="14"/>
+        <v>4</v>
+      </c>
+      <c r="U23" s="11">
+        <f t="shared" si="8"/>
+        <v>21</v>
+      </c>
+      <c r="V23" s="38">
+        <v>7346</v>
+      </c>
+      <c r="W23" s="38">
+        <v>9149</v>
+      </c>
+      <c r="X23" s="38">
+        <v>9342</v>
+      </c>
+      <c r="Y23" s="38">
+        <v>10816</v>
+      </c>
+      <c r="Z23" s="38">
+        <v>1275</v>
+      </c>
+      <c r="AA23" s="38">
+        <v>3776</v>
+      </c>
+      <c r="AB23" s="38">
+        <v>379</v>
+      </c>
+      <c r="AC23" s="38">
+        <v>3397</v>
+      </c>
+    </row>
+    <row r="24" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A24" s="15">
+        <f t="shared" si="6"/>
+        <v>23</v>
+      </c>
+      <c r="B24" s="30">
+        <v>1544.9279994999988</v>
+      </c>
+      <c r="C24" s="30">
+        <v>240.32399992000001</v>
+      </c>
+      <c r="D24" s="6">
+        <f t="shared" si="9"/>
+        <v>34</v>
+      </c>
+      <c r="E24" s="12">
+        <v>0</v>
+      </c>
+      <c r="F24" s="6">
+        <f t="shared" si="10"/>
+        <v>56</v>
+      </c>
+      <c r="G24" s="12">
+        <v>0</v>
+      </c>
+      <c r="H24" s="6">
+        <f t="shared" si="11"/>
+        <v>4</v>
+      </c>
+      <c r="I24" s="12">
+        <v>0</v>
+      </c>
+      <c r="J24" s="6">
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
-      <c r="K22" s="12">
-        <v>0</v>
-      </c>
-      <c r="L22" s="6">
+      <c r="K24" s="12">
+        <v>0</v>
+      </c>
+      <c r="L24" s="6">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="M24" s="12">
+        <v>0</v>
+      </c>
+      <c r="N24" s="25">
+        <v>275.3279993499998</v>
+      </c>
+      <c r="O24" s="30">
+        <v>66.887999909999991</v>
+      </c>
+      <c r="P24" s="6">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="M22" s="12">
-        <v>0</v>
-      </c>
-      <c r="N22" s="6">
+      <c r="Q24" s="12">
+        <v>0</v>
+      </c>
+      <c r="R24" s="12">
+        <v>0</v>
+      </c>
+      <c r="S24" s="6">
         <f t="shared" si="14"/>
         <v>5</v>
       </c>
-      <c r="O22" s="12">
-        <v>0</v>
-      </c>
-      <c r="P22" s="6">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="Q22" s="12">
-        <v>0</v>
-      </c>
-      <c r="R22" s="12">
-        <v>0</v>
-      </c>
-      <c r="S22" s="6">
-        <f t="shared" si="16"/>
-        <v>4</v>
-      </c>
-      <c r="U22" s="11">
-        <f t="shared" si="9"/>
-        <v>20</v>
-      </c>
-      <c r="V22" s="37">
-        <v>7326</v>
-      </c>
-      <c r="W22" s="37">
-        <v>9120</v>
-      </c>
-      <c r="X22" s="37">
-        <v>9339</v>
-      </c>
-      <c r="Y22" s="37">
-        <v>10815</v>
-      </c>
-      <c r="Z22" s="37">
+      <c r="U24" s="11">
+        <f t="shared" si="8"/>
+        <v>22</v>
+      </c>
+      <c r="V24" s="38">
+        <v>7374</v>
+      </c>
+      <c r="W24" s="38">
+        <v>9204</v>
+      </c>
+      <c r="X24" s="38">
+        <v>9345</v>
+      </c>
+      <c r="Y24" s="38">
+        <v>10816</v>
+      </c>
+      <c r="Z24" s="38">
         <v>1275</v>
       </c>
-      <c r="AA22" s="37">
-        <v>3771</v>
-      </c>
-      <c r="AB22" s="37">
+      <c r="AA24" s="38">
+        <v>3780</v>
+      </c>
+      <c r="AB24" s="38">
         <v>379</v>
       </c>
-      <c r="AC22" s="37">
-        <v>3393</v>
-      </c>
-    </row>
-    <row r="23" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A23" s="15">
-        <f t="shared" si="7"/>
-        <v>22</v>
-      </c>
-      <c r="B23" s="12">
-        <v>0</v>
-      </c>
-      <c r="C23" s="12">
-        <v>0</v>
-      </c>
-      <c r="D23" s="6">
-        <f t="shared" si="10"/>
-        <v>28</v>
-      </c>
-      <c r="E23" s="12">
-        <v>0</v>
-      </c>
-      <c r="F23" s="6">
-        <f t="shared" si="11"/>
-        <v>55</v>
-      </c>
-      <c r="G23" s="12">
-        <v>0</v>
-      </c>
-      <c r="H23" s="6">
-        <f t="shared" si="12"/>
-        <v>3</v>
-      </c>
-      <c r="I23" s="12">
-        <v>0</v>
-      </c>
-      <c r="J23" s="6">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="K23" s="12">
-        <v>0</v>
-      </c>
-      <c r="L23" s="6">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="M23" s="12">
-        <v>0</v>
-      </c>
-      <c r="N23" s="6">
-        <f t="shared" si="14"/>
-        <v>4</v>
-      </c>
-      <c r="O23" s="12">
-        <v>0</v>
-      </c>
-      <c r="P23" s="6">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="Q23" s="12">
-        <v>0</v>
-      </c>
-      <c r="R23" s="12">
-        <v>0</v>
-      </c>
-      <c r="S23" s="6">
-        <f t="shared" si="16"/>
-        <v>4</v>
-      </c>
-      <c r="U23" s="11">
-        <f t="shared" si="9"/>
-        <v>21</v>
-      </c>
-      <c r="V23" s="41">
-        <v>7346</v>
-      </c>
-      <c r="W23" s="41">
-        <v>9149</v>
-      </c>
-      <c r="X23" s="41">
-        <v>9342</v>
-      </c>
-      <c r="Y23" s="41">
-        <v>10816</v>
-      </c>
-      <c r="Z23" s="41">
-        <v>1275</v>
-      </c>
-      <c r="AA23" s="41">
-        <v>3776</v>
-      </c>
-      <c r="AB23" s="41">
-        <v>379</v>
-      </c>
-      <c r="AC23" s="41">
-        <v>3397</v>
-      </c>
-    </row>
-    <row r="24" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A24" s="15">
-        <f t="shared" si="7"/>
-        <v>23</v>
-      </c>
-      <c r="B24" s="12">
-        <v>0</v>
-      </c>
-      <c r="C24" s="12">
-        <v>0</v>
-      </c>
-      <c r="D24" s="6">
-        <f t="shared" si="10"/>
-        <v>34</v>
-      </c>
-      <c r="E24" s="12">
-        <v>0</v>
-      </c>
-      <c r="F24" s="6">
-        <f t="shared" si="11"/>
-        <v>56</v>
-      </c>
-      <c r="G24" s="12">
-        <v>0</v>
-      </c>
-      <c r="H24" s="6">
-        <f t="shared" si="12"/>
-        <v>4</v>
-      </c>
-      <c r="I24" s="12">
-        <v>0</v>
-      </c>
-      <c r="J24" s="6">
-        <f t="shared" si="17"/>
-        <v>1</v>
-      </c>
-      <c r="K24" s="12">
-        <v>0</v>
-      </c>
-      <c r="L24" s="6">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="M24" s="12">
-        <v>0</v>
-      </c>
-      <c r="N24" s="6">
-        <f t="shared" si="14"/>
-        <v>5</v>
-      </c>
-      <c r="O24" s="12">
-        <v>0</v>
-      </c>
-      <c r="P24" s="6">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="Q24" s="12">
-        <v>0</v>
-      </c>
-      <c r="R24" s="12">
-        <v>0</v>
-      </c>
-      <c r="S24" s="6">
-        <f t="shared" si="16"/>
-        <v>5</v>
-      </c>
-      <c r="U24" s="11">
-        <f t="shared" si="9"/>
-        <v>22</v>
-      </c>
-      <c r="V24" s="41">
-        <v>7374</v>
-      </c>
-      <c r="W24" s="41">
-        <v>9204</v>
-      </c>
-      <c r="X24" s="41">
-        <v>9345</v>
-      </c>
-      <c r="Y24" s="41">
-        <v>10816</v>
-      </c>
-      <c r="Z24" s="41">
-        <v>1275</v>
-      </c>
-      <c r="AA24" s="41">
-        <v>3780</v>
-      </c>
-      <c r="AB24" s="41">
-        <v>379</v>
-      </c>
-      <c r="AC24" s="41">
+      <c r="AC24" s="38">
         <v>3401</v>
       </c>
     </row>
     <row r="25" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A25" s="18">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>24</v>
       </c>
-      <c r="B25" s="12">
-        <v>0</v>
-      </c>
-      <c r="C25" s="12">
-        <v>0</v>
+      <c r="B25" s="30">
+        <v>1439.96999949</v>
+      </c>
+      <c r="C25" s="30">
+        <v>219.99599992999998</v>
       </c>
       <c r="D25" s="6">
+        <f t="shared" si="9"/>
+        <v>-7408</v>
+      </c>
+      <c r="E25" s="12">
+        <v>0</v>
+      </c>
+      <c r="F25" s="6">
         <f t="shared" si="10"/>
-        <v>-7408</v>
-      </c>
-      <c r="E25" s="12">
-        <v>0</v>
-      </c>
-      <c r="F25" s="6">
+        <v>-9260</v>
+      </c>
+      <c r="G25" s="12">
+        <v>0</v>
+      </c>
+      <c r="H25" s="6">
         <f t="shared" si="11"/>
-        <v>-9260</v>
-      </c>
-      <c r="G25" s="12">
-        <v>0</v>
-      </c>
-      <c r="H25" s="6">
+        <v>-9349</v>
+      </c>
+      <c r="I25" s="12">
+        <v>0</v>
+      </c>
+      <c r="J25" s="6">
+        <f t="shared" si="15"/>
+        <v>-10817</v>
+      </c>
+      <c r="K25" s="12">
+        <v>0</v>
+      </c>
+      <c r="L25" s="6">
         <f t="shared" si="12"/>
-        <v>-9349</v>
-      </c>
-      <c r="I25" s="12">
-        <v>0</v>
-      </c>
-      <c r="J25" s="6">
-        <f t="shared" si="17"/>
-        <v>-10817</v>
-      </c>
-      <c r="K25" s="12">
-        <v>0</v>
-      </c>
-      <c r="L25" s="6">
+        <v>-1275</v>
+      </c>
+      <c r="M25" s="12">
+        <v>0</v>
+      </c>
+      <c r="N25" s="25">
+        <v>248.49599941999989</v>
+      </c>
+      <c r="O25" s="30">
+        <v>61.775999880000001</v>
+      </c>
+      <c r="P25" s="6">
         <f t="shared" si="13"/>
-        <v>-1275</v>
-      </c>
-      <c r="M25" s="12">
-        <v>0</v>
-      </c>
-      <c r="N25" s="6">
+        <v>-379</v>
+      </c>
+      <c r="Q25" s="12">
+        <v>0</v>
+      </c>
+      <c r="R25" s="12">
+        <v>0</v>
+      </c>
+      <c r="S25" s="6">
         <f t="shared" si="14"/>
-        <v>-3785</v>
-      </c>
-      <c r="O25" s="12">
-        <v>0</v>
-      </c>
-      <c r="P25" s="6">
-        <f t="shared" si="15"/>
-        <v>-379</v>
-      </c>
-      <c r="Q25" s="12">
-        <v>0</v>
-      </c>
-      <c r="R25" s="12">
-        <v>0</v>
-      </c>
-      <c r="S25" s="6">
-        <f t="shared" si="16"/>
         <v>-3406</v>
       </c>
       <c r="U25" s="11">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>23</v>
       </c>
-      <c r="V25" s="41">
+      <c r="V25" s="38">
         <v>7408</v>
       </c>
-      <c r="W25" s="41">
+      <c r="W25" s="38">
         <v>9260</v>
       </c>
-      <c r="X25" s="41">
+      <c r="X25" s="38">
         <v>9349</v>
       </c>
-      <c r="Y25" s="41">
+      <c r="Y25" s="38">
         <v>10817</v>
       </c>
-      <c r="Z25" s="41">
+      <c r="Z25" s="38">
         <v>1275</v>
       </c>
-      <c r="AA25" s="41">
+      <c r="AA25" s="38">
         <v>3785</v>
       </c>
-      <c r="AB25" s="41">
+      <c r="AB25" s="38">
         <v>379</v>
       </c>
-      <c r="AC25" s="41">
+      <c r="AC25" s="38">
         <v>3406</v>
       </c>
     </row>
     <row r="26" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A26" s="15">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>25</v>
       </c>
-      <c r="B26" s="12">
-        <v>0</v>
-      </c>
-      <c r="C26" s="12">
-        <v>0</v>
+      <c r="B26" s="30">
+        <v>1284.7379994599999</v>
+      </c>
+      <c r="C26" s="30">
+        <v>211.63799988999997</v>
       </c>
       <c r="D26" s="6">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="E26" s="12">
+        <v>0</v>
+      </c>
+      <c r="F26" s="6">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="E26" s="12">
-        <v>0</v>
-      </c>
-      <c r="F26" s="6">
+      <c r="G26" s="12">
+        <v>0</v>
+      </c>
+      <c r="H26" s="6">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="G26" s="12">
-        <v>0</v>
-      </c>
-      <c r="H26" s="6">
+      <c r="I26" s="12">
+        <v>0</v>
+      </c>
+      <c r="J26" s="6">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="K26" s="12">
+        <v>0</v>
+      </c>
+      <c r="L26" s="6">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="I26" s="12">
-        <v>0</v>
-      </c>
-      <c r="J26" s="6">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="K26" s="12">
-        <v>0</v>
-      </c>
-      <c r="L26" s="6">
+      <c r="M26" s="12">
+        <v>0</v>
+      </c>
+      <c r="N26" s="25">
+        <v>265.36799933999993</v>
+      </c>
+      <c r="O26" s="30">
+        <v>55.703999900000007</v>
+      </c>
+      <c r="P26" s="6">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="M26" s="12">
-        <v>0</v>
-      </c>
-      <c r="N26" s="6">
+      <c r="Q26" s="12">
+        <v>0</v>
+      </c>
+      <c r="R26" s="12">
+        <v>0</v>
+      </c>
+      <c r="S26" s="6">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="O26" s="12">
-        <v>0</v>
-      </c>
-      <c r="P26" s="6">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="Q26" s="12">
-        <v>0</v>
-      </c>
-      <c r="R26" s="12">
-        <v>0</v>
-      </c>
-      <c r="S26" s="6">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
       <c r="U26" s="18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>24</v>
       </c>
-      <c r="V26" s="40"/>
-      <c r="W26" s="40"/>
-      <c r="X26" s="40"/>
-      <c r="Y26" s="40"/>
-      <c r="Z26" s="40"/>
-      <c r="AA26" s="40"/>
-      <c r="AB26" s="40"/>
-      <c r="AC26" s="40"/>
+      <c r="V26" s="37"/>
+      <c r="W26" s="37"/>
+      <c r="X26" s="37"/>
+      <c r="Y26" s="37"/>
+      <c r="Z26" s="37"/>
+      <c r="AA26" s="37"/>
+      <c r="AB26" s="37"/>
+      <c r="AC26" s="37"/>
     </row>
     <row r="27" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A27" s="15">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>26</v>
       </c>
-      <c r="B27" s="12">
-        <v>0</v>
-      </c>
-      <c r="C27" s="12">
-        <v>0</v>
+      <c r="B27" s="30">
+        <v>1338.5819995099987</v>
+      </c>
+      <c r="C27" s="30">
+        <v>190.34399994999998</v>
       </c>
       <c r="D27" s="6">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="E27" s="12">
+        <v>0</v>
+      </c>
+      <c r="F27" s="6">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="E27" s="12">
-        <v>0</v>
-      </c>
-      <c r="F27" s="6">
+      <c r="G27" s="12">
+        <v>0</v>
+      </c>
+      <c r="H27" s="6">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="G27" s="12">
-        <v>0</v>
-      </c>
-      <c r="H27" s="6">
+      <c r="I27" s="12">
+        <v>0</v>
+      </c>
+      <c r="J27" s="6">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="K27" s="12">
+        <v>0</v>
+      </c>
+      <c r="L27" s="6">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="I27" s="12">
-        <v>0</v>
-      </c>
-      <c r="J27" s="6">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="K27" s="12">
-        <v>0</v>
-      </c>
-      <c r="L27" s="6">
+      <c r="M27" s="12">
+        <v>0</v>
+      </c>
+      <c r="N27" s="25">
+        <v>246.43199937999987</v>
+      </c>
+      <c r="O27" s="30">
+        <v>60.263999900000002</v>
+      </c>
+      <c r="P27" s="6">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="M27" s="12">
-        <v>0</v>
-      </c>
-      <c r="N27" s="6">
+      <c r="Q27" s="12">
+        <v>0</v>
+      </c>
+      <c r="R27" s="12">
+        <v>0</v>
+      </c>
+      <c r="S27" s="6">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="O27" s="12">
-        <v>0</v>
-      </c>
-      <c r="P27" s="6">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="Q27" s="12">
-        <v>0</v>
-      </c>
-      <c r="R27" s="12">
-        <v>0</v>
-      </c>
-      <c r="S27" s="6">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
       <c r="U27" s="15">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>25</v>
       </c>
       <c r="V27" s="13"/>
@@ -33374,14 +33348,14 @@
     </row>
     <row r="28" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A28" s="15">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>27</v>
       </c>
-      <c r="B28" s="12">
-        <v>0</v>
-      </c>
-      <c r="C28" s="12">
-        <v>0</v>
+      <c r="B28" s="30">
+        <v>1159.1999995100002</v>
+      </c>
+      <c r="C28" s="30">
+        <v>183.91799988999998</v>
       </c>
       <c r="D28" s="6">
         <f>V29-V28</f>
@@ -33391,56 +33365,55 @@
         <v>0</v>
       </c>
       <c r="F28" s="6">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="G28" s="12">
+        <v>0</v>
+      </c>
+      <c r="H28" s="6">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="G28" s="12">
-        <v>0</v>
-      </c>
-      <c r="H28" s="6">
+      <c r="I28" s="12">
+        <v>0</v>
+      </c>
+      <c r="J28" s="6">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="K28" s="12">
+        <v>0</v>
+      </c>
+      <c r="L28" s="6">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="I28" s="12">
-        <v>0</v>
-      </c>
-      <c r="J28" s="6">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="K28" s="12">
-        <v>0</v>
-      </c>
-      <c r="L28" s="6">
+      <c r="M28" s="12">
+        <v>0</v>
+      </c>
+      <c r="N28" s="25">
+        <v>249.74399931999994</v>
+      </c>
+      <c r="O28" s="30">
+        <v>54.815999890000001</v>
+      </c>
+      <c r="P28" s="6">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="M28" s="12">
-        <v>0</v>
-      </c>
-      <c r="N28" s="6">
+      <c r="Q28" s="12">
+        <v>0</v>
+      </c>
+      <c r="R28" s="12">
+        <v>0</v>
+      </c>
+      <c r="S28" s="6">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="O28" s="12">
-        <v>0</v>
-      </c>
-      <c r="P28" s="6">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="Q28" s="12">
-        <v>0</v>
-      </c>
-      <c r="R28" s="12">
-        <v>0</v>
-      </c>
-      <c r="S28" s="6">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
       <c r="U28" s="15">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>26</v>
       </c>
       <c r="V28" s="13"/>
@@ -33454,73 +33427,72 @@
     </row>
     <row r="29" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A29" s="15">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>28</v>
       </c>
-      <c r="B29" s="12">
-        <v>0</v>
-      </c>
-      <c r="C29" s="12">
-        <v>0</v>
+      <c r="B29" s="30">
+        <v>937.5659994600004</v>
+      </c>
+      <c r="C29" s="30">
+        <v>152.66999990999997</v>
       </c>
       <c r="D29" s="6">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="E29" s="12">
+        <v>0</v>
+      </c>
+      <c r="F29" s="6">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="E29" s="12">
-        <v>0</v>
-      </c>
-      <c r="F29" s="6">
+      <c r="G29" s="12">
+        <v>0</v>
+      </c>
+      <c r="H29" s="6">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="G29" s="12">
-        <v>0</v>
-      </c>
-      <c r="H29" s="6">
+      <c r="I29" s="12">
+        <v>0</v>
+      </c>
+      <c r="J29" s="6">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="K29" s="12">
+        <v>0</v>
+      </c>
+      <c r="L29" s="6">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="I29" s="12">
-        <v>0</v>
-      </c>
-      <c r="J29" s="6">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="K29" s="12">
-        <v>0</v>
-      </c>
-      <c r="L29" s="6">
+      <c r="M29" s="12">
+        <v>0</v>
+      </c>
+      <c r="N29" s="25">
+        <v>273.47999938999976</v>
+      </c>
+      <c r="O29" s="30">
+        <v>64.199999910000003</v>
+      </c>
+      <c r="P29" s="6">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="M29" s="12">
-        <v>0</v>
-      </c>
-      <c r="N29" s="6">
+      <c r="Q29" s="12">
+        <v>0</v>
+      </c>
+      <c r="R29" s="12">
+        <v>0</v>
+      </c>
+      <c r="S29" s="6">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="O29" s="12">
-        <v>0</v>
-      </c>
-      <c r="P29" s="6">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="Q29" s="12">
-        <v>0</v>
-      </c>
-      <c r="R29" s="12">
-        <v>0</v>
-      </c>
-      <c r="S29" s="6">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
       <c r="U29" s="15">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>27</v>
       </c>
       <c r="V29" s="13"/>
@@ -33534,73 +33506,72 @@
     </row>
     <row r="30" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A30" s="15">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>29</v>
       </c>
-      <c r="B30" s="12">
-        <v>0</v>
-      </c>
-      <c r="C30" s="12">
-        <v>0</v>
+      <c r="B30" s="30">
+        <v>928.78799944999992</v>
+      </c>
+      <c r="C30" s="30">
+        <v>166.78199988999998</v>
       </c>
       <c r="D30" s="6">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="E30" s="12">
+        <v>0</v>
+      </c>
+      <c r="F30" s="6">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="E30" s="12">
-        <v>0</v>
-      </c>
-      <c r="F30" s="6">
+      <c r="G30" s="12">
+        <v>0</v>
+      </c>
+      <c r="H30" s="6">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="G30" s="12">
-        <v>0</v>
-      </c>
-      <c r="H30" s="6">
+      <c r="I30" s="12">
+        <v>0</v>
+      </c>
+      <c r="J30" s="6">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="K30" s="12">
+        <v>0</v>
+      </c>
+      <c r="L30" s="6">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="I30" s="12">
-        <v>0</v>
-      </c>
-      <c r="J30" s="6">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="K30" s="12">
-        <v>0</v>
-      </c>
-      <c r="L30" s="6">
+      <c r="M30" s="12">
+        <v>0</v>
+      </c>
+      <c r="N30" s="25">
+        <v>291.28799944999969</v>
+      </c>
+      <c r="O30" s="30">
+        <v>59.903999889999994</v>
+      </c>
+      <c r="P30" s="6">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="M30" s="12">
-        <v>0</v>
-      </c>
-      <c r="N30" s="6">
+      <c r="Q30" s="12">
+        <v>0</v>
+      </c>
+      <c r="R30" s="12">
+        <v>0</v>
+      </c>
+      <c r="S30" s="6">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="O30" s="12">
-        <v>0</v>
-      </c>
-      <c r="P30" s="6">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="Q30" s="12">
-        <v>0</v>
-      </c>
-      <c r="R30" s="12">
-        <v>0</v>
-      </c>
-      <c r="S30" s="6">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
       <c r="U30" s="15">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>28</v>
       </c>
       <c r="V30" s="13"/>
@@ -33614,73 +33585,72 @@
     </row>
     <row r="31" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A31" s="15">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>30</v>
       </c>
-      <c r="B31" s="12">
-        <v>0</v>
-      </c>
-      <c r="C31" s="12">
-        <v>0</v>
+      <c r="B31" s="30">
+        <v>1388.7299995399999</v>
+      </c>
+      <c r="C31" s="30">
+        <v>196.76999993000001</v>
       </c>
       <c r="D31" s="6">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="E31" s="12">
+        <v>0</v>
+      </c>
+      <c r="F31" s="6">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="E31" s="12">
-        <v>0</v>
-      </c>
-      <c r="F31" s="6">
+      <c r="G31" s="12">
+        <v>0</v>
+      </c>
+      <c r="H31" s="6">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="G31" s="12">
-        <v>0</v>
-      </c>
-      <c r="H31" s="6">
+      <c r="I31" s="12">
+        <v>0</v>
+      </c>
+      <c r="J31" s="6">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="K31" s="12">
+        <v>0</v>
+      </c>
+      <c r="L31" s="6">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="I31" s="12">
-        <v>0</v>
-      </c>
-      <c r="J31" s="6">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="K31" s="12">
-        <v>0</v>
-      </c>
-      <c r="L31" s="6">
+      <c r="M31" s="12">
+        <v>0</v>
+      </c>
+      <c r="N31" s="25">
+        <v>236.15999938999974</v>
+      </c>
+      <c r="O31" s="30">
+        <v>52.031999909999996</v>
+      </c>
+      <c r="P31" s="6">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="M31" s="12">
-        <v>0</v>
-      </c>
-      <c r="N31" s="6">
+      <c r="Q31" s="12">
+        <v>0</v>
+      </c>
+      <c r="R31" s="12">
+        <v>0</v>
+      </c>
+      <c r="S31" s="6">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="O31" s="12">
-        <v>0</v>
-      </c>
-      <c r="P31" s="6">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="Q31" s="12">
-        <v>0</v>
-      </c>
-      <c r="R31" s="12">
-        <v>0</v>
-      </c>
-      <c r="S31" s="6">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
       <c r="U31" s="15">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>29</v>
       </c>
       <c r="V31" s="13"/>
@@ -33694,7 +33664,7 @@
     </row>
     <row r="32" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="U32" s="15">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>30</v>
       </c>
       <c r="V32" s="13"/>
@@ -33723,22 +33693,22 @@
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
-      <c r="D35" s="34"/>
-      <c r="E35" s="34"/>
-      <c r="F35" s="34"/>
-      <c r="G35" s="34"/>
-      <c r="H35" s="34"/>
-      <c r="I35" s="34"/>
-      <c r="J35" s="34"/>
-      <c r="K35" s="34"/>
-      <c r="L35" s="34"/>
-      <c r="M35" s="34"/>
-      <c r="N35" s="34"/>
-      <c r="O35" s="34"/>
-      <c r="P35" s="34"/>
-      <c r="Q35" s="34"/>
-      <c r="R35" s="34"/>
-      <c r="S35" s="34"/>
+      <c r="D35" s="39"/>
+      <c r="E35" s="39"/>
+      <c r="F35" s="39"/>
+      <c r="G35" s="39"/>
+      <c r="H35" s="39"/>
+      <c r="I35" s="39"/>
+      <c r="J35" s="39"/>
+      <c r="K35" s="39"/>
+      <c r="L35" s="39"/>
+      <c r="M35" s="39"/>
+      <c r="N35" s="39"/>
+      <c r="O35" s="39"/>
+      <c r="P35" s="39"/>
+      <c r="Q35" s="39"/>
+      <c r="R35" s="39"/>
+      <c r="S35" s="39"/>
       <c r="T35"/>
     </row>
     <row r="36" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
@@ -34457,25 +34427,25 @@
       <c r="S69" s="1"/>
     </row>
     <row r="70" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A70" s="34"/>
-      <c r="B70" s="34"/>
-      <c r="C70" s="34"/>
-      <c r="D70" s="34"/>
-      <c r="E70" s="34"/>
-      <c r="F70" s="34"/>
-      <c r="G70" s="34"/>
-      <c r="H70" s="34"/>
-      <c r="I70" s="34"/>
-      <c r="J70" s="34"/>
-      <c r="K70" s="34"/>
-      <c r="L70" s="34"/>
-      <c r="M70" s="34"/>
-      <c r="N70" s="34"/>
-      <c r="O70" s="34"/>
-      <c r="P70" s="34"/>
-      <c r="Q70" s="34"/>
-      <c r="R70" s="34"/>
-      <c r="S70" s="34"/>
+      <c r="A70" s="39"/>
+      <c r="B70" s="39"/>
+      <c r="C70" s="39"/>
+      <c r="D70" s="39"/>
+      <c r="E70" s="39"/>
+      <c r="F70" s="39"/>
+      <c r="G70" s="39"/>
+      <c r="H70" s="39"/>
+      <c r="I70" s="39"/>
+      <c r="J70" s="39"/>
+      <c r="K70" s="39"/>
+      <c r="L70" s="39"/>
+      <c r="M70" s="39"/>
+      <c r="N70" s="39"/>
+      <c r="O70" s="39"/>
+      <c r="P70" s="39"/>
+      <c r="Q70" s="39"/>
+      <c r="R70" s="39"/>
+      <c r="S70" s="39"/>
     </row>
     <row r="71" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="1"/>
@@ -34520,25 +34490,25 @@
       <c r="S72" s="21"/>
     </row>
     <row r="75" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A75" s="35"/>
-      <c r="B75" s="35"/>
-      <c r="C75" s="35"/>
-      <c r="D75" s="35"/>
-      <c r="E75" s="35"/>
-      <c r="F75" s="35"/>
-      <c r="G75" s="35"/>
-      <c r="H75" s="35"/>
-      <c r="I75" s="35"/>
-      <c r="J75" s="35"/>
-      <c r="K75" s="35"/>
-      <c r="L75" s="35"/>
-      <c r="M75" s="35"/>
-      <c r="N75" s="35"/>
-      <c r="O75" s="35"/>
-      <c r="P75" s="35"/>
-      <c r="Q75" s="35"/>
-      <c r="R75" s="35"/>
-      <c r="S75" s="35"/>
+      <c r="A75" s="40"/>
+      <c r="B75" s="40"/>
+      <c r="C75" s="40"/>
+      <c r="D75" s="40"/>
+      <c r="E75" s="40"/>
+      <c r="F75" s="40"/>
+      <c r="G75" s="40"/>
+      <c r="H75" s="40"/>
+      <c r="I75" s="40"/>
+      <c r="J75" s="40"/>
+      <c r="K75" s="40"/>
+      <c r="L75" s="40"/>
+      <c r="M75" s="40"/>
+      <c r="N75" s="40"/>
+      <c r="O75" s="40"/>
+      <c r="P75" s="40"/>
+      <c r="Q75" s="40"/>
+      <c r="R75" s="40"/>
+      <c r="S75" s="40"/>
     </row>
     <row r="76" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="1"/>
@@ -34604,25 +34574,25 @@
       <c r="S78" s="23"/>
     </row>
     <row r="79" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A79" s="36"/>
-      <c r="B79" s="36"/>
-      <c r="C79" s="36"/>
-      <c r="D79" s="36"/>
-      <c r="E79" s="36"/>
-      <c r="F79" s="36"/>
-      <c r="G79" s="36"/>
-      <c r="H79" s="36"/>
-      <c r="I79" s="36"/>
-      <c r="J79" s="36"/>
-      <c r="K79" s="36"/>
-      <c r="L79" s="36"/>
-      <c r="M79" s="36"/>
-      <c r="N79" s="36"/>
-      <c r="O79" s="36"/>
-      <c r="P79" s="36"/>
-      <c r="Q79" s="36"/>
-      <c r="R79" s="36"/>
-      <c r="S79" s="36"/>
+      <c r="A79" s="41"/>
+      <c r="B79" s="41"/>
+      <c r="C79" s="41"/>
+      <c r="D79" s="41"/>
+      <c r="E79" s="41"/>
+      <c r="F79" s="41"/>
+      <c r="G79" s="41"/>
+      <c r="H79" s="41"/>
+      <c r="I79" s="41"/>
+      <c r="J79" s="41"/>
+      <c r="K79" s="41"/>
+      <c r="L79" s="41"/>
+      <c r="M79" s="41"/>
+      <c r="N79" s="41"/>
+      <c r="O79" s="41"/>
+      <c r="P79" s="41"/>
+      <c r="Q79" s="41"/>
+      <c r="R79" s="41"/>
+      <c r="S79" s="41"/>
     </row>
     <row r="80" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="1"/>
@@ -34686,25 +34656,25 @@
       <c r="E85" s="21"/>
     </row>
     <row r="87" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A87" s="35"/>
-      <c r="B87" s="35"/>
-      <c r="C87" s="35"/>
-      <c r="D87" s="35"/>
-      <c r="E87" s="35"/>
-      <c r="F87" s="35"/>
-      <c r="G87" s="35"/>
-      <c r="H87" s="35"/>
-      <c r="I87" s="35"/>
-      <c r="J87" s="35"/>
-      <c r="K87" s="35"/>
-      <c r="L87" s="35"/>
-      <c r="M87" s="35"/>
-      <c r="N87" s="35"/>
-      <c r="O87" s="35"/>
-      <c r="P87" s="35"/>
-      <c r="Q87" s="35"/>
-      <c r="R87" s="35"/>
-      <c r="S87" s="35"/>
+      <c r="A87" s="40"/>
+      <c r="B87" s="40"/>
+      <c r="C87" s="40"/>
+      <c r="D87" s="40"/>
+      <c r="E87" s="40"/>
+      <c r="F87" s="40"/>
+      <c r="G87" s="40"/>
+      <c r="H87" s="40"/>
+      <c r="I87" s="40"/>
+      <c r="J87" s="40"/>
+      <c r="K87" s="40"/>
+      <c r="L87" s="40"/>
+      <c r="M87" s="40"/>
+      <c r="N87" s="40"/>
+      <c r="O87" s="40"/>
+      <c r="P87" s="40"/>
+      <c r="Q87" s="40"/>
+      <c r="R87" s="40"/>
+      <c r="S87" s="40"/>
     </row>
     <row r="88" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="1"/>
@@ -34896,25 +34866,25 @@
       <c r="E98" s="24"/>
     </row>
     <row r="100" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A100" s="34"/>
-      <c r="B100" s="34"/>
-      <c r="C100" s="34"/>
-      <c r="D100" s="34"/>
-      <c r="E100" s="34"/>
-      <c r="F100" s="34"/>
-      <c r="G100" s="34"/>
-      <c r="H100" s="34"/>
-      <c r="I100" s="34"/>
-      <c r="J100" s="34"/>
-      <c r="K100" s="34"/>
-      <c r="L100" s="34"/>
-      <c r="M100" s="34"/>
-      <c r="N100" s="34"/>
-      <c r="O100" s="34"/>
-      <c r="P100" s="34"/>
-      <c r="Q100" s="34"/>
-      <c r="R100" s="34"/>
-      <c r="S100" s="34"/>
+      <c r="A100" s="39"/>
+      <c r="B100" s="39"/>
+      <c r="C100" s="39"/>
+      <c r="D100" s="39"/>
+      <c r="E100" s="39"/>
+      <c r="F100" s="39"/>
+      <c r="G100" s="39"/>
+      <c r="H100" s="39"/>
+      <c r="I100" s="39"/>
+      <c r="J100" s="39"/>
+      <c r="K100" s="39"/>
+      <c r="L100" s="39"/>
+      <c r="M100" s="39"/>
+      <c r="N100" s="39"/>
+      <c r="O100" s="39"/>
+      <c r="P100" s="39"/>
+      <c r="Q100" s="39"/>
+      <c r="R100" s="39"/>
+      <c r="S100" s="39"/>
     </row>
     <row r="101" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="1"/>
@@ -35175,28 +35145,28 @@
       <c r="U2" s="7">
         <v>0</v>
       </c>
-      <c r="V2" s="39">
+      <c r="V2" s="36">
         <v>4765</v>
       </c>
-      <c r="W2" s="39">
+      <c r="W2" s="36">
         <v>6659</v>
       </c>
-      <c r="X2" s="39">
+      <c r="X2" s="36">
         <v>9140</v>
       </c>
-      <c r="Y2" s="39">
+      <c r="Y2" s="36">
         <v>10780</v>
       </c>
-      <c r="Z2" s="39">
+      <c r="Z2" s="36">
         <v>1266</v>
       </c>
-      <c r="AA2" s="39">
+      <c r="AA2" s="36">
         <v>3556</v>
       </c>
-      <c r="AB2" s="39">
+      <c r="AB2" s="36">
         <v>353</v>
       </c>
-      <c r="AC2" s="39">
+      <c r="AC2" s="36">
         <v>3203</v>
       </c>
       <c r="AE2" s="9" t="s">
@@ -35277,28 +35247,28 @@
       <c r="U3" s="5">
         <v>1</v>
       </c>
-      <c r="V3" s="37">
+      <c r="V3" s="34">
         <v>4909</v>
       </c>
-      <c r="W3" s="37">
+      <c r="W3" s="34">
         <v>6810</v>
       </c>
-      <c r="X3" s="37">
+      <c r="X3" s="34">
         <v>9145</v>
       </c>
-      <c r="Y3" s="37">
+      <c r="Y3" s="34">
         <v>10783</v>
       </c>
-      <c r="Z3" s="37">
+      <c r="Z3" s="34">
         <v>1266</v>
       </c>
-      <c r="AA3" s="37">
+      <c r="AA3" s="34">
         <v>3565</v>
       </c>
-      <c r="AB3" s="37">
+      <c r="AB3" s="34">
         <v>354</v>
       </c>
-      <c r="AC3" s="37">
+      <c r="AC3" s="34">
         <v>3210</v>
       </c>
     </row>
@@ -35373,28 +35343,28 @@
         <f t="shared" ref="U4:U33" si="8">U3+1</f>
         <v>2</v>
       </c>
-      <c r="V4" s="37">
+      <c r="V4" s="34">
         <v>4909</v>
       </c>
-      <c r="W4" s="37">
+      <c r="W4" s="34">
         <v>6810</v>
       </c>
-      <c r="X4" s="37">
+      <c r="X4" s="34">
         <v>9145</v>
       </c>
-      <c r="Y4" s="37">
+      <c r="Y4" s="34">
         <v>10783</v>
       </c>
-      <c r="Z4" s="37">
+      <c r="Z4" s="34">
         <v>1266</v>
       </c>
-      <c r="AA4" s="37">
+      <c r="AA4" s="34">
         <v>3565</v>
       </c>
-      <c r="AB4" s="37">
+      <c r="AB4" s="34">
         <v>354</v>
       </c>
-      <c r="AC4" s="37">
+      <c r="AC4" s="34">
         <v>3210</v>
       </c>
     </row>
@@ -35469,28 +35439,28 @@
         <f t="shared" si="8"/>
         <v>3</v>
       </c>
-      <c r="V5" s="37">
+      <c r="V5" s="34">
         <v>5009</v>
       </c>
-      <c r="W5" s="37">
+      <c r="W5" s="34">
         <v>6932</v>
       </c>
-      <c r="X5" s="37">
+      <c r="X5" s="34">
         <v>9157</v>
       </c>
-      <c r="Y5" s="37">
+      <c r="Y5" s="34">
         <v>10784</v>
       </c>
-      <c r="Z5" s="37">
+      <c r="Z5" s="34">
         <v>1267</v>
       </c>
-      <c r="AA5" s="37">
+      <c r="AA5" s="34">
         <v>3574</v>
       </c>
-      <c r="AB5" s="37">
+      <c r="AB5" s="34">
         <v>355</v>
       </c>
-      <c r="AC5" s="37">
+      <c r="AC5" s="34">
         <v>3218</v>
       </c>
     </row>
@@ -35565,28 +35535,28 @@
         <f t="shared" si="8"/>
         <v>4</v>
       </c>
-      <c r="V6" s="37">
+      <c r="V6" s="34">
         <v>5025</v>
       </c>
-      <c r="W6" s="37">
+      <c r="W6" s="34">
         <v>6932</v>
       </c>
-      <c r="X6" s="37">
+      <c r="X6" s="34">
         <v>9158</v>
       </c>
-      <c r="Y6" s="37">
+      <c r="Y6" s="34">
         <v>10784</v>
       </c>
-      <c r="Z6" s="37">
+      <c r="Z6" s="34">
         <v>1267</v>
       </c>
-      <c r="AA6" s="37">
+      <c r="AA6" s="34">
         <v>3578</v>
       </c>
-      <c r="AB6" s="37">
+      <c r="AB6" s="34">
         <v>355</v>
       </c>
-      <c r="AC6" s="37">
+      <c r="AC6" s="34">
         <v>3223</v>
       </c>
     </row>
@@ -35661,28 +35631,28 @@
         <f t="shared" si="8"/>
         <v>5</v>
       </c>
-      <c r="V7" s="37">
+      <c r="V7" s="34">
         <v>5069</v>
       </c>
-      <c r="W7" s="37">
+      <c r="W7" s="34">
         <v>6997</v>
       </c>
-      <c r="X7" s="37">
+      <c r="X7" s="34">
         <v>9168</v>
       </c>
-      <c r="Y7" s="37">
+      <c r="Y7" s="34">
         <v>10784</v>
       </c>
-      <c r="Z7" s="37">
+      <c r="Z7" s="34">
         <v>1267</v>
       </c>
-      <c r="AA7" s="37">
+      <c r="AA7" s="34">
         <v>3583</v>
       </c>
-      <c r="AB7" s="37">
+      <c r="AB7" s="34">
         <v>355</v>
       </c>
-      <c r="AC7" s="37">
+      <c r="AC7" s="34">
         <v>3227</v>
       </c>
     </row>
@@ -35757,28 +35727,28 @@
         <f t="shared" si="8"/>
         <v>6</v>
       </c>
-      <c r="V8" s="37">
+      <c r="V8" s="34">
         <v>5127</v>
       </c>
-      <c r="W8" s="37">
+      <c r="W8" s="34">
         <v>7107</v>
       </c>
-      <c r="X8" s="37">
+      <c r="X8" s="34">
         <v>9172</v>
       </c>
-      <c r="Y8" s="37">
+      <c r="Y8" s="34">
         <v>10785</v>
       </c>
-      <c r="Z8" s="37">
+      <c r="Z8" s="34">
         <v>1267</v>
       </c>
-      <c r="AA8" s="37">
+      <c r="AA8" s="34">
         <v>3584</v>
       </c>
-      <c r="AB8" s="37">
+      <c r="AB8" s="34">
         <v>355</v>
       </c>
-      <c r="AC8" s="37">
+      <c r="AC8" s="34">
         <v>3228</v>
       </c>
     </row>
@@ -35853,28 +35823,28 @@
         <f t="shared" si="8"/>
         <v>7</v>
       </c>
-      <c r="V9" s="37">
+      <c r="V9" s="34">
         <v>5130</v>
       </c>
-      <c r="W9" s="37">
+      <c r="W9" s="34">
         <v>7110</v>
       </c>
-      <c r="X9" s="37">
+      <c r="X9" s="34">
         <v>9176</v>
       </c>
-      <c r="Y9" s="37">
+      <c r="Y9" s="34">
         <v>10787</v>
       </c>
-      <c r="Z9" s="37">
+      <c r="Z9" s="34">
         <v>1268</v>
       </c>
-      <c r="AA9" s="37">
+      <c r="AA9" s="34">
         <v>3590</v>
       </c>
-      <c r="AB9" s="37">
+      <c r="AB9" s="34">
         <v>356</v>
       </c>
-      <c r="AC9" s="37">
+      <c r="AC9" s="34">
         <v>3233</v>
       </c>
     </row>
@@ -35949,28 +35919,28 @@
         <f t="shared" si="8"/>
         <v>8</v>
       </c>
-      <c r="V10" s="37">
+      <c r="V10" s="34">
         <v>5130</v>
       </c>
-      <c r="W10" s="37">
+      <c r="W10" s="34">
         <v>7110</v>
       </c>
-      <c r="X10" s="37">
+      <c r="X10" s="34">
         <v>9176</v>
       </c>
-      <c r="Y10" s="37">
+      <c r="Y10" s="34">
         <v>10787</v>
       </c>
-      <c r="Z10" s="37">
+      <c r="Z10" s="34">
         <v>1268</v>
       </c>
-      <c r="AA10" s="37">
+      <c r="AA10" s="34">
         <v>3590</v>
       </c>
-      <c r="AB10" s="37">
+      <c r="AB10" s="34">
         <v>356</v>
       </c>
-      <c r="AC10" s="37">
+      <c r="AC10" s="34">
         <v>3233</v>
       </c>
     </row>
@@ -36045,28 +36015,28 @@
         <f t="shared" si="8"/>
         <v>9</v>
       </c>
-      <c r="V11" s="37">
+      <c r="V11" s="34">
         <v>5130</v>
       </c>
-      <c r="W11" s="37">
+      <c r="W11" s="34">
         <v>7110</v>
       </c>
-      <c r="X11" s="37">
+      <c r="X11" s="34">
         <v>9176</v>
       </c>
-      <c r="Y11" s="37">
+      <c r="Y11" s="34">
         <v>10787</v>
       </c>
-      <c r="Z11" s="37">
+      <c r="Z11" s="34">
         <v>1268</v>
       </c>
-      <c r="AA11" s="37">
+      <c r="AA11" s="34">
         <v>3590</v>
       </c>
-      <c r="AB11" s="37">
+      <c r="AB11" s="34">
         <v>356</v>
       </c>
-      <c r="AC11" s="37">
+      <c r="AC11" s="34">
         <v>3233</v>
       </c>
     </row>
@@ -36141,28 +36111,28 @@
         <f t="shared" si="8"/>
         <v>10</v>
       </c>
-      <c r="V12" s="37">
+      <c r="V12" s="34">
         <v>5416</v>
       </c>
-      <c r="W12" s="37">
+      <c r="W12" s="34">
         <v>7409</v>
       </c>
-      <c r="X12" s="37">
+      <c r="X12" s="34">
         <v>9192</v>
       </c>
-      <c r="Y12" s="37">
+      <c r="Y12" s="34">
         <v>10787</v>
       </c>
-      <c r="Z12" s="37">
+      <c r="Z12" s="34">
         <v>1269</v>
       </c>
-      <c r="AA12" s="37">
+      <c r="AA12" s="34">
         <v>3604</v>
       </c>
-      <c r="AB12" s="37">
+      <c r="AB12" s="34">
         <v>358</v>
       </c>
-      <c r="AC12" s="37">
+      <c r="AC12" s="34">
         <v>3245</v>
       </c>
     </row>
@@ -36237,28 +36207,28 @@
         <f t="shared" si="8"/>
         <v>11</v>
       </c>
-      <c r="V13" s="37">
+      <c r="V13" s="34">
         <v>5429</v>
       </c>
-      <c r="W13" s="37">
+      <c r="W13" s="34">
         <v>7435</v>
       </c>
-      <c r="X13" s="37">
+      <c r="X13" s="34">
         <v>9195</v>
       </c>
-      <c r="Y13" s="37">
+      <c r="Y13" s="34">
         <v>10788</v>
       </c>
-      <c r="Z13" s="37">
+      <c r="Z13" s="34">
         <v>1269</v>
       </c>
-      <c r="AA13" s="37">
+      <c r="AA13" s="34">
         <v>3609</v>
       </c>
-      <c r="AB13" s="37">
+      <c r="AB13" s="34">
         <v>358</v>
       </c>
-      <c r="AC13" s="37">
+      <c r="AC13" s="34">
         <v>3250</v>
       </c>
     </row>
@@ -36333,28 +36303,28 @@
         <f t="shared" si="8"/>
         <v>12</v>
       </c>
-      <c r="V14" s="37">
+      <c r="V14" s="34">
         <v>5458</v>
       </c>
-      <c r="W14" s="37">
+      <c r="W14" s="34">
         <v>7553</v>
       </c>
-      <c r="X14" s="37">
+      <c r="X14" s="34">
         <v>9200</v>
       </c>
-      <c r="Y14" s="37">
+      <c r="Y14" s="34">
         <v>10789</v>
       </c>
-      <c r="Z14" s="37">
+      <c r="Z14" s="34">
         <v>1269</v>
       </c>
-      <c r="AA14" s="37">
+      <c r="AA14" s="34">
         <v>3614</v>
       </c>
-      <c r="AB14" s="37">
+      <c r="AB14" s="34">
         <v>358</v>
       </c>
-      <c r="AC14" s="37">
+      <c r="AC14" s="34">
         <v>3255</v>
       </c>
     </row>
@@ -36428,28 +36398,28 @@
         <f t="shared" si="8"/>
         <v>13</v>
       </c>
-      <c r="V15" s="37">
+      <c r="V15" s="34">
         <v>5458</v>
       </c>
-      <c r="W15" s="37">
+      <c r="W15" s="34">
         <v>7553</v>
       </c>
-      <c r="X15" s="37">
+      <c r="X15" s="34">
         <v>9200</v>
       </c>
-      <c r="Y15" s="37">
+      <c r="Y15" s="34">
         <v>10789</v>
       </c>
-      <c r="Z15" s="37">
+      <c r="Z15" s="34">
         <v>1269</v>
       </c>
-      <c r="AA15" s="37">
+      <c r="AA15" s="34">
         <v>3614</v>
       </c>
-      <c r="AB15" s="37">
+      <c r="AB15" s="34">
         <v>358</v>
       </c>
-      <c r="AC15" s="37">
+      <c r="AC15" s="34">
         <v>3255</v>
       </c>
     </row>
@@ -36524,28 +36494,28 @@
         <f t="shared" si="8"/>
         <v>14</v>
       </c>
-      <c r="V16" s="37">
+      <c r="V16" s="34">
         <v>5458</v>
       </c>
-      <c r="W16" s="37">
+      <c r="W16" s="34">
         <v>7553</v>
       </c>
-      <c r="X16" s="37">
+      <c r="X16" s="34">
         <v>9200</v>
       </c>
-      <c r="Y16" s="37">
+      <c r="Y16" s="34">
         <v>10789</v>
       </c>
-      <c r="Z16" s="37">
+      <c r="Z16" s="34">
         <v>1269</v>
       </c>
-      <c r="AA16" s="37">
+      <c r="AA16" s="34">
         <v>3614</v>
       </c>
-      <c r="AB16" s="37">
+      <c r="AB16" s="34">
         <v>358</v>
       </c>
-      <c r="AC16" s="37">
+      <c r="AC16" s="34">
         <v>3255</v>
       </c>
     </row>
@@ -36620,28 +36590,28 @@
         <f t="shared" si="8"/>
         <v>15</v>
       </c>
-      <c r="V17" s="37">
+      <c r="V17" s="34">
         <v>5695</v>
       </c>
-      <c r="W17" s="37">
+      <c r="W17" s="34">
         <v>7647</v>
       </c>
-      <c r="X17" s="37">
+      <c r="X17" s="34">
         <v>9209</v>
       </c>
-      <c r="Y17" s="37">
+      <c r="Y17" s="34">
         <v>10791</v>
       </c>
-      <c r="Z17" s="37">
+      <c r="Z17" s="34">
         <v>1269</v>
       </c>
-      <c r="AA17" s="37">
+      <c r="AA17" s="34">
         <v>3627</v>
       </c>
-      <c r="AB17" s="37">
+      <c r="AB17" s="34">
         <v>360</v>
       </c>
-      <c r="AC17" s="37">
+      <c r="AC17" s="34">
         <v>3266</v>
       </c>
     </row>
@@ -36716,28 +36686,28 @@
         <f t="shared" si="8"/>
         <v>16</v>
       </c>
-      <c r="V18" s="37">
+      <c r="V18" s="34">
         <v>5695</v>
       </c>
-      <c r="W18" s="37">
+      <c r="W18" s="34">
         <v>7647</v>
       </c>
-      <c r="X18" s="37">
+      <c r="X18" s="34">
         <v>9209</v>
       </c>
-      <c r="Y18" s="37">
+      <c r="Y18" s="34">
         <v>10791</v>
       </c>
-      <c r="Z18" s="37">
+      <c r="Z18" s="34">
         <v>1269</v>
       </c>
-      <c r="AA18" s="37">
+      <c r="AA18" s="34">
         <v>3627</v>
       </c>
-      <c r="AB18" s="37">
+      <c r="AB18" s="34">
         <v>360</v>
       </c>
-      <c r="AC18" s="37">
+      <c r="AC18" s="34">
         <v>3266</v>
       </c>
     </row>
@@ -36812,28 +36782,28 @@
         <f t="shared" si="8"/>
         <v>17</v>
       </c>
-      <c r="V19" s="37">
+      <c r="V19" s="34">
         <v>5695</v>
       </c>
-      <c r="W19" s="37">
+      <c r="W19" s="34">
         <v>7647</v>
       </c>
-      <c r="X19" s="37">
+      <c r="X19" s="34">
         <v>9209</v>
       </c>
-      <c r="Y19" s="37">
+      <c r="Y19" s="34">
         <v>10791</v>
       </c>
-      <c r="Z19" s="37">
+      <c r="Z19" s="34">
         <v>1269</v>
       </c>
-      <c r="AA19" s="37">
+      <c r="AA19" s="34">
         <v>3627</v>
       </c>
-      <c r="AB19" s="37">
+      <c r="AB19" s="34">
         <v>360</v>
       </c>
-      <c r="AC19" s="37">
+      <c r="AC19" s="34">
         <v>3266</v>
       </c>
     </row>
@@ -36908,28 +36878,28 @@
         <f t="shared" si="8"/>
         <v>18</v>
       </c>
-      <c r="V20" s="37">
+      <c r="V20" s="34">
         <v>5695</v>
       </c>
-      <c r="W20" s="37">
+      <c r="W20" s="34">
         <v>7647</v>
       </c>
-      <c r="X20" s="37">
+      <c r="X20" s="34">
         <v>9209</v>
       </c>
-      <c r="Y20" s="37">
+      <c r="Y20" s="34">
         <v>10791</v>
       </c>
-      <c r="Z20" s="37">
+      <c r="Z20" s="34">
         <v>1269</v>
       </c>
-      <c r="AA20" s="37">
+      <c r="AA20" s="34">
         <v>3627</v>
       </c>
-      <c r="AB20" s="37">
+      <c r="AB20" s="34">
         <v>360</v>
       </c>
-      <c r="AC20" s="37">
+      <c r="AC20" s="34">
         <v>3266</v>
       </c>
     </row>
@@ -37004,28 +36974,28 @@
         <f t="shared" si="8"/>
         <v>19</v>
       </c>
-      <c r="V21" s="37">
+      <c r="V21" s="34">
         <v>5695</v>
       </c>
-      <c r="W21" s="37">
+      <c r="W21" s="34">
         <v>7647</v>
       </c>
-      <c r="X21" s="37">
+      <c r="X21" s="34">
         <v>9209</v>
       </c>
-      <c r="Y21" s="37">
+      <c r="Y21" s="34">
         <v>10791</v>
       </c>
-      <c r="Z21" s="37">
+      <c r="Z21" s="34">
         <v>1269</v>
       </c>
-      <c r="AA21" s="37">
+      <c r="AA21" s="34">
         <v>3627</v>
       </c>
-      <c r="AB21" s="37">
+      <c r="AB21" s="34">
         <v>360</v>
       </c>
-      <c r="AC21" s="37">
+      <c r="AC21" s="34">
         <v>3266</v>
       </c>
     </row>
@@ -37100,28 +37070,28 @@
         <f t="shared" si="8"/>
         <v>20</v>
       </c>
-      <c r="V22" s="37">
+      <c r="V22" s="34">
         <v>5695</v>
       </c>
-      <c r="W22" s="37">
+      <c r="W22" s="34">
         <v>7647</v>
       </c>
-      <c r="X22" s="37">
+      <c r="X22" s="34">
         <v>9209</v>
       </c>
-      <c r="Y22" s="37">
+      <c r="Y22" s="34">
         <v>10791</v>
       </c>
-      <c r="Z22" s="37">
+      <c r="Z22" s="34">
         <v>1269</v>
       </c>
-      <c r="AA22" s="37">
+      <c r="AA22" s="34">
         <v>3627</v>
       </c>
-      <c r="AB22" s="37">
+      <c r="AB22" s="34">
         <v>360</v>
       </c>
-      <c r="AC22" s="37">
+      <c r="AC22" s="34">
         <v>3266</v>
       </c>
     </row>
@@ -37196,28 +37166,28 @@
         <f t="shared" si="8"/>
         <v>21</v>
       </c>
-      <c r="V23" s="37">
+      <c r="V23" s="34">
         <v>5695</v>
       </c>
-      <c r="W23" s="37">
+      <c r="W23" s="34">
         <v>7647</v>
       </c>
-      <c r="X23" s="37">
+      <c r="X23" s="34">
         <v>9209</v>
       </c>
-      <c r="Y23" s="37">
+      <c r="Y23" s="34">
         <v>10791</v>
       </c>
-      <c r="Z23" s="37">
+      <c r="Z23" s="34">
         <v>1269</v>
       </c>
-      <c r="AA23" s="37">
+      <c r="AA23" s="34">
         <v>3627</v>
       </c>
-      <c r="AB23" s="37">
+      <c r="AB23" s="34">
         <v>360</v>
       </c>
-      <c r="AC23" s="37">
+      <c r="AC23" s="34">
         <v>3266</v>
       </c>
     </row>
@@ -37292,28 +37262,28 @@
         <f t="shared" si="8"/>
         <v>22</v>
       </c>
-      <c r="V24" s="37">
+      <c r="V24" s="34">
         <v>5695</v>
       </c>
-      <c r="W24" s="37">
+      <c r="W24" s="34">
         <v>7647</v>
       </c>
-      <c r="X24" s="37">
+      <c r="X24" s="34">
         <v>9209</v>
       </c>
-      <c r="Y24" s="37">
+      <c r="Y24" s="34">
         <v>10791</v>
       </c>
-      <c r="Z24" s="37">
+      <c r="Z24" s="34">
         <v>1269</v>
       </c>
-      <c r="AA24" s="37">
+      <c r="AA24" s="34">
         <v>3627</v>
       </c>
-      <c r="AB24" s="37">
+      <c r="AB24" s="34">
         <v>360</v>
       </c>
-      <c r="AC24" s="37">
+      <c r="AC24" s="34">
         <v>3266</v>
       </c>
     </row>
@@ -37388,28 +37358,28 @@
         <f t="shared" si="8"/>
         <v>23</v>
       </c>
-      <c r="V25" s="37">
+      <c r="V25" s="34">
         <v>5695</v>
       </c>
-      <c r="W25" s="37">
+      <c r="W25" s="34">
         <v>7647</v>
       </c>
-      <c r="X25" s="37">
+      <c r="X25" s="34">
         <v>9209</v>
       </c>
-      <c r="Y25" s="37">
+      <c r="Y25" s="34">
         <v>10791</v>
       </c>
-      <c r="Z25" s="37">
+      <c r="Z25" s="34">
         <v>1269</v>
       </c>
-      <c r="AA25" s="37">
+      <c r="AA25" s="34">
         <v>3627</v>
       </c>
-      <c r="AB25" s="37">
+      <c r="AB25" s="34">
         <v>360</v>
       </c>
-      <c r="AC25" s="37">
+      <c r="AC25" s="34">
         <v>3266</v>
       </c>
     </row>
@@ -37480,32 +37450,32 @@
         <v>0</v>
       </c>
       <c r="T26" s="4"/>
-      <c r="U26" s="38">
+      <c r="U26" s="35">
         <f t="shared" si="8"/>
         <v>24</v>
       </c>
-      <c r="V26" s="37">
+      <c r="V26" s="34">
         <v>5695</v>
       </c>
-      <c r="W26" s="37">
+      <c r="W26" s="34">
         <v>7647</v>
       </c>
-      <c r="X26" s="37">
+      <c r="X26" s="34">
         <v>9209</v>
       </c>
-      <c r="Y26" s="37">
+      <c r="Y26" s="34">
         <v>10791</v>
       </c>
-      <c r="Z26" s="37">
+      <c r="Z26" s="34">
         <v>1269</v>
       </c>
-      <c r="AA26" s="37">
+      <c r="AA26" s="34">
         <v>3627</v>
       </c>
-      <c r="AB26" s="37">
+      <c r="AB26" s="34">
         <v>360</v>
       </c>
-      <c r="AC26" s="37">
+      <c r="AC26" s="34">
         <v>3266</v>
       </c>
     </row>
@@ -37580,28 +37550,28 @@
         <f t="shared" si="8"/>
         <v>25</v>
       </c>
-      <c r="V27" s="37">
+      <c r="V27" s="34">
         <v>5695</v>
       </c>
-      <c r="W27" s="37">
+      <c r="W27" s="34">
         <v>7647</v>
       </c>
-      <c r="X27" s="37">
+      <c r="X27" s="34">
         <v>9209</v>
       </c>
-      <c r="Y27" s="37">
+      <c r="Y27" s="34">
         <v>10791</v>
       </c>
-      <c r="Z27" s="37">
+      <c r="Z27" s="34">
         <v>1269</v>
       </c>
-      <c r="AA27" s="37">
+      <c r="AA27" s="34">
         <v>3627</v>
       </c>
-      <c r="AB27" s="37">
+      <c r="AB27" s="34">
         <v>360</v>
       </c>
-      <c r="AC27" s="37">
+      <c r="AC27" s="34">
         <v>3266</v>
       </c>
     </row>
@@ -37676,28 +37646,28 @@
         <f t="shared" si="8"/>
         <v>26</v>
       </c>
-      <c r="V28" s="37">
+      <c r="V28" s="34">
         <v>5695</v>
       </c>
-      <c r="W28" s="37">
+      <c r="W28" s="34">
         <v>7647</v>
       </c>
-      <c r="X28" s="37">
+      <c r="X28" s="34">
         <v>9209</v>
       </c>
-      <c r="Y28" s="37">
+      <c r="Y28" s="34">
         <v>10791</v>
       </c>
-      <c r="Z28" s="37">
+      <c r="Z28" s="34">
         <v>1269</v>
       </c>
-      <c r="AA28" s="37">
+      <c r="AA28" s="34">
         <v>3627</v>
       </c>
-      <c r="AB28" s="37">
+      <c r="AB28" s="34">
         <v>360</v>
       </c>
-      <c r="AC28" s="37">
+      <c r="AC28" s="34">
         <v>3266</v>
       </c>
     </row>
@@ -37772,28 +37742,28 @@
         <f t="shared" si="8"/>
         <v>27</v>
       </c>
-      <c r="V29" s="37">
+      <c r="V29" s="34">
         <v>5695</v>
       </c>
-      <c r="W29" s="37">
+      <c r="W29" s="34">
         <v>7647</v>
       </c>
-      <c r="X29" s="37">
+      <c r="X29" s="34">
         <v>9209</v>
       </c>
-      <c r="Y29" s="37">
+      <c r="Y29" s="34">
         <v>10791</v>
       </c>
-      <c r="Z29" s="37">
+      <c r="Z29" s="34">
         <v>1269</v>
       </c>
-      <c r="AA29" s="37">
+      <c r="AA29" s="34">
         <v>3627</v>
       </c>
-      <c r="AB29" s="37">
+      <c r="AB29" s="34">
         <v>360</v>
       </c>
-      <c r="AC29" s="37">
+      <c r="AC29" s="34">
         <v>3266</v>
       </c>
     </row>
@@ -37868,28 +37838,28 @@
         <f t="shared" si="8"/>
         <v>28</v>
       </c>
-      <c r="V30" s="37">
+      <c r="V30" s="34">
         <v>5695</v>
       </c>
-      <c r="W30" s="37">
+      <c r="W30" s="34">
         <v>7647</v>
       </c>
-      <c r="X30" s="37">
+      <c r="X30" s="34">
         <v>9209</v>
       </c>
-      <c r="Y30" s="37">
+      <c r="Y30" s="34">
         <v>10791</v>
       </c>
-      <c r="Z30" s="37">
+      <c r="Z30" s="34">
         <v>1269</v>
       </c>
-      <c r="AA30" s="37">
+      <c r="AA30" s="34">
         <v>3627</v>
       </c>
-      <c r="AB30" s="37">
+      <c r="AB30" s="34">
         <v>360</v>
       </c>
-      <c r="AC30" s="37">
+      <c r="AC30" s="34">
         <v>3266</v>
       </c>
     </row>
@@ -37964,28 +37934,28 @@
         <f t="shared" si="8"/>
         <v>29</v>
       </c>
-      <c r="V31" s="37">
+      <c r="V31" s="34">
         <v>6351</v>
       </c>
-      <c r="W31" s="37">
+      <c r="W31" s="34">
         <v>8113</v>
       </c>
-      <c r="X31" s="37">
+      <c r="X31" s="34">
         <v>9260</v>
       </c>
-      <c r="Y31" s="37">
+      <c r="Y31" s="34">
         <v>11801</v>
       </c>
-      <c r="Z31" s="37">
+      <c r="Z31" s="34">
         <v>1270</v>
       </c>
-      <c r="AA31" s="37">
+      <c r="AA31" s="34">
         <v>3684</v>
       </c>
-      <c r="AB31" s="37">
+      <c r="AB31" s="34">
         <v>367</v>
       </c>
-      <c r="AC31" s="37">
+      <c r="AC31" s="34">
         <v>3316</v>
       </c>
     </row>
@@ -38060,28 +38030,28 @@
         <f t="shared" si="8"/>
         <v>30</v>
       </c>
-      <c r="V32" s="37">
+      <c r="V32" s="34">
         <v>6375</v>
       </c>
-      <c r="W32" s="37">
+      <c r="W32" s="34">
         <v>8136</v>
       </c>
-      <c r="X32" s="37">
+      <c r="X32" s="34">
         <v>9263</v>
       </c>
-      <c r="Y32" s="37">
+      <c r="Y32" s="34">
         <v>11802</v>
       </c>
-      <c r="Z32" s="37">
+      <c r="Z32" s="34">
         <v>1270</v>
       </c>
-      <c r="AA32" s="37">
+      <c r="AA32" s="34">
         <v>3687</v>
       </c>
-      <c r="AB32" s="37">
+      <c r="AB32" s="34">
         <v>368</v>
       </c>
-      <c r="AC32" s="37">
+      <c r="AC32" s="34">
         <v>3318</v>
       </c>
     </row>
@@ -38091,42 +38061,42 @@
         <f t="shared" si="8"/>
         <v>31</v>
       </c>
-      <c r="V33" s="37">
+      <c r="V33" s="34">
         <v>6375</v>
       </c>
-      <c r="W33" s="37">
+      <c r="W33" s="34">
         <v>8136</v>
       </c>
-      <c r="X33" s="37">
+      <c r="X33" s="34">
         <v>9263</v>
       </c>
-      <c r="Y33" s="37">
+      <c r="Y33" s="34">
         <v>11802</v>
       </c>
-      <c r="Z33" s="37">
+      <c r="Z33" s="34">
         <v>1270</v>
       </c>
-      <c r="AA33" s="37">
+      <c r="AA33" s="34">
         <v>3687</v>
       </c>
-      <c r="AB33" s="37">
+      <c r="AB33" s="34">
         <v>368</v>
       </c>
-      <c r="AC33" s="37">
+      <c r="AC33" s="34">
         <v>3318</v>
       </c>
     </row>
     <row r="34" spans="1:29" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="36" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
-      <c r="B36" s="34"/>
-      <c r="C36" s="34"/>
-      <c r="D36" s="34"/>
-      <c r="E36" s="34"/>
-      <c r="F36" s="34"/>
-      <c r="G36" s="34"/>
-      <c r="H36" s="34"/>
-      <c r="I36" s="34"/>
+      <c r="B36" s="39"/>
+      <c r="C36" s="39"/>
+      <c r="D36" s="39"/>
+      <c r="E36" s="39"/>
+      <c r="F36" s="39"/>
+      <c r="G36" s="39"/>
+      <c r="H36" s="39"/>
+      <c r="I36" s="39"/>
     </row>
     <row r="37" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="1"/>
@@ -38504,15 +38474,15 @@
       <c r="I70" s="1"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A71" s="34"/>
-      <c r="B71" s="34"/>
-      <c r="C71" s="34"/>
-      <c r="D71" s="34"/>
-      <c r="E71" s="34"/>
-      <c r="F71" s="34"/>
-      <c r="G71" s="34"/>
-      <c r="H71" s="34"/>
-      <c r="I71" s="34"/>
+      <c r="A71" s="39"/>
+      <c r="B71" s="39"/>
+      <c r="C71" s="39"/>
+      <c r="D71" s="39"/>
+      <c r="E71" s="39"/>
+      <c r="F71" s="39"/>
+      <c r="G71" s="39"/>
+      <c r="H71" s="39"/>
+      <c r="I71" s="39"/>
     </row>
     <row r="72" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A72" s="1"/>
@@ -38537,15 +38507,15 @@
       <c r="I73" s="21"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A76" s="35"/>
-      <c r="B76" s="35"/>
-      <c r="C76" s="35"/>
-      <c r="D76" s="35"/>
-      <c r="E76" s="35"/>
-      <c r="F76" s="35"/>
-      <c r="G76" s="35"/>
-      <c r="H76" s="35"/>
-      <c r="I76" s="35"/>
+      <c r="A76" s="40"/>
+      <c r="B76" s="40"/>
+      <c r="C76" s="40"/>
+      <c r="D76" s="40"/>
+      <c r="E76" s="40"/>
+      <c r="F76" s="40"/>
+      <c r="G76" s="40"/>
+      <c r="H76" s="40"/>
+      <c r="I76" s="40"/>
     </row>
     <row r="77" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="1"/>
@@ -38581,15 +38551,15 @@
       <c r="I79" s="23"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A80" s="36"/>
-      <c r="B80" s="36"/>
-      <c r="C80" s="36"/>
-      <c r="D80" s="36"/>
-      <c r="E80" s="36"/>
-      <c r="F80" s="36"/>
-      <c r="G80" s="36"/>
-      <c r="H80" s="36"/>
-      <c r="I80" s="36"/>
+      <c r="A80" s="41"/>
+      <c r="B80" s="41"/>
+      <c r="C80" s="41"/>
+      <c r="D80" s="41"/>
+      <c r="E80" s="41"/>
+      <c r="F80" s="41"/>
+      <c r="G80" s="41"/>
+      <c r="H80" s="41"/>
+      <c r="I80" s="41"/>
     </row>
     <row r="81" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="1"/>
@@ -38625,15 +38595,15 @@
       <c r="B86" s="21"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A88" s="35"/>
-      <c r="B88" s="35"/>
-      <c r="C88" s="35"/>
-      <c r="D88" s="35"/>
-      <c r="E88" s="35"/>
-      <c r="F88" s="35"/>
-      <c r="G88" s="35"/>
-      <c r="H88" s="35"/>
-      <c r="I88" s="35"/>
+      <c r="A88" s="40"/>
+      <c r="B88" s="40"/>
+      <c r="C88" s="40"/>
+      <c r="D88" s="40"/>
+      <c r="E88" s="40"/>
+      <c r="F88" s="40"/>
+      <c r="G88" s="40"/>
+      <c r="H88" s="40"/>
+      <c r="I88" s="40"/>
     </row>
     <row r="89" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="1"/>
@@ -38736,15 +38706,15 @@
       <c r="B99" s="24"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A101" s="34"/>
-      <c r="B101" s="34"/>
-      <c r="C101" s="34"/>
-      <c r="D101" s="34"/>
-      <c r="E101" s="34"/>
-      <c r="F101" s="34"/>
-      <c r="G101" s="34"/>
-      <c r="H101" s="34"/>
-      <c r="I101" s="34"/>
+      <c r="A101" s="39"/>
+      <c r="B101" s="39"/>
+      <c r="C101" s="39"/>
+      <c r="D101" s="39"/>
+      <c r="E101" s="39"/>
+      <c r="F101" s="39"/>
+      <c r="G101" s="39"/>
+      <c r="H101" s="39"/>
+      <c r="I101" s="39"/>
     </row>
     <row r="102" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A102" s="1"/>
@@ -38990,28 +38960,28 @@
       <c r="U2" s="7">
         <v>0</v>
       </c>
-      <c r="V2" s="39">
+      <c r="V2" s="36">
         <v>2812</v>
       </c>
-      <c r="W2" s="39">
+      <c r="W2" s="36">
         <v>4489</v>
       </c>
-      <c r="X2" s="39">
+      <c r="X2" s="36">
         <v>9036</v>
       </c>
-      <c r="Y2" s="39">
+      <c r="Y2" s="36">
         <v>10758</v>
       </c>
-      <c r="Z2" s="39">
+      <c r="Z2" s="36">
         <v>1260</v>
       </c>
-      <c r="AA2" s="39">
+      <c r="AA2" s="36">
         <v>3408</v>
       </c>
-      <c r="AB2" s="39">
+      <c r="AB2" s="36">
         <v>338</v>
       </c>
-      <c r="AC2" s="39">
+      <c r="AC2" s="36">
         <v>3069</v>
       </c>
       <c r="AE2" s="9" t="s">
@@ -39092,28 +39062,28 @@
       <c r="U3" s="5">
         <v>1</v>
       </c>
-      <c r="V3" s="37">
+      <c r="V3" s="34">
         <v>2930</v>
       </c>
-      <c r="W3" s="37">
+      <c r="W3" s="34">
         <v>4611</v>
       </c>
-      <c r="X3" s="37">
+      <c r="X3" s="34">
         <v>9038</v>
       </c>
-      <c r="Y3" s="37">
+      <c r="Y3" s="34">
         <v>10758</v>
       </c>
-      <c r="Z3" s="37">
+      <c r="Z3" s="34">
         <v>1260</v>
       </c>
-      <c r="AA3" s="37">
+      <c r="AA3" s="34">
         <v>3413</v>
       </c>
-      <c r="AB3" s="37">
+      <c r="AB3" s="34">
         <v>339</v>
       </c>
-      <c r="AC3" s="37">
+      <c r="AC3" s="34">
         <v>3073</v>
       </c>
     </row>
@@ -39188,28 +39158,28 @@
         <f t="shared" ref="U4:U32" si="8">U3+1</f>
         <v>2</v>
       </c>
-      <c r="V4" s="37">
+      <c r="V4" s="34">
         <v>3025</v>
       </c>
-      <c r="W4" s="37">
+      <c r="W4" s="34">
         <v>4736</v>
       </c>
-      <c r="X4" s="37">
+      <c r="X4" s="34">
         <v>9043</v>
       </c>
-      <c r="Y4" s="37">
+      <c r="Y4" s="34">
         <v>10760</v>
       </c>
-      <c r="Z4" s="37">
+      <c r="Z4" s="34">
         <v>1261</v>
       </c>
-      <c r="AA4" s="37">
+      <c r="AA4" s="34">
         <v>3419</v>
       </c>
-      <c r="AB4" s="37">
+      <c r="AB4" s="34">
         <v>340</v>
       </c>
-      <c r="AC4" s="37">
+      <c r="AC4" s="34">
         <v>3079</v>
       </c>
     </row>
@@ -39284,28 +39254,28 @@
         <f t="shared" si="8"/>
         <v>3</v>
       </c>
-      <c r="V5" s="37">
+      <c r="V5" s="34">
         <v>3146</v>
       </c>
-      <c r="W5" s="37">
+      <c r="W5" s="34">
         <v>4811</v>
       </c>
-      <c r="X5" s="37">
+      <c r="X5" s="34">
         <v>9043</v>
       </c>
-      <c r="Y5" s="37">
+      <c r="Y5" s="34">
         <v>10761</v>
       </c>
-      <c r="Z5" s="37">
+      <c r="Z5" s="34">
         <v>1261</v>
       </c>
-      <c r="AA5" s="37">
+      <c r="AA5" s="34">
         <v>3424</v>
       </c>
-      <c r="AB5" s="37">
+      <c r="AB5" s="34">
         <v>341</v>
       </c>
-      <c r="AC5" s="37">
+      <c r="AC5" s="34">
         <v>3083</v>
       </c>
     </row>
@@ -39380,28 +39350,28 @@
         <f t="shared" si="8"/>
         <v>4</v>
       </c>
-      <c r="V6" s="37">
+      <c r="V6" s="34">
         <v>3240</v>
       </c>
-      <c r="W6" s="37">
+      <c r="W6" s="34">
         <v>4914</v>
       </c>
-      <c r="X6" s="37">
+      <c r="X6" s="34">
         <v>9048</v>
       </c>
-      <c r="Y6" s="37">
+      <c r="Y6" s="34">
         <v>10762</v>
       </c>
-      <c r="Z6" s="37">
+      <c r="Z6" s="34">
         <v>1261</v>
       </c>
-      <c r="AA6" s="37">
+      <c r="AA6" s="34">
         <v>3429</v>
       </c>
-      <c r="AB6" s="37">
+      <c r="AB6" s="34">
         <v>341</v>
       </c>
-      <c r="AC6" s="37">
+      <c r="AC6" s="34">
         <v>3088</v>
       </c>
     </row>
@@ -39476,28 +39446,28 @@
         <f t="shared" si="8"/>
         <v>5</v>
       </c>
-      <c r="V7" s="37">
+      <c r="V7" s="34">
         <v>3301</v>
       </c>
-      <c r="W7" s="37">
+      <c r="W7" s="34">
         <v>4990</v>
       </c>
-      <c r="X7" s="37">
+      <c r="X7" s="34">
         <v>9053</v>
       </c>
-      <c r="Y7" s="37">
+      <c r="Y7" s="34">
         <v>10763</v>
       </c>
-      <c r="Z7" s="37">
+      <c r="Z7" s="34">
         <v>1261</v>
       </c>
-      <c r="AA7" s="37">
+      <c r="AA7" s="34">
         <v>3435</v>
       </c>
-      <c r="AB7" s="37">
+      <c r="AB7" s="34">
         <v>342</v>
       </c>
-      <c r="AC7" s="37">
+      <c r="AC7" s="34">
         <v>3092</v>
       </c>
     </row>
@@ -39572,28 +39542,28 @@
         <f t="shared" si="8"/>
         <v>6</v>
       </c>
-      <c r="V8" s="37">
+      <c r="V8" s="34">
         <v>3332</v>
       </c>
-      <c r="W8" s="37">
+      <c r="W8" s="34">
         <v>5122</v>
       </c>
-      <c r="X8" s="37">
+      <c r="X8" s="34">
         <v>9056</v>
       </c>
-      <c r="Y8" s="37">
+      <c r="Y8" s="34">
         <v>10763</v>
       </c>
-      <c r="Z8" s="37">
+      <c r="Z8" s="34">
         <v>1261</v>
       </c>
-      <c r="AA8" s="37">
+      <c r="AA8" s="34">
         <v>3437</v>
       </c>
-      <c r="AB8" s="37">
+      <c r="AB8" s="34">
         <v>342</v>
       </c>
-      <c r="AC8" s="37">
+      <c r="AC8" s="34">
         <v>3094</v>
       </c>
     </row>
@@ -39668,28 +39638,28 @@
         <f t="shared" si="8"/>
         <v>7</v>
       </c>
-      <c r="V9" s="37">
+      <c r="V9" s="34">
         <v>3369</v>
       </c>
-      <c r="W9" s="37">
+      <c r="W9" s="34">
         <v>5122</v>
       </c>
-      <c r="X9" s="37">
+      <c r="X9" s="34">
         <v>9059</v>
       </c>
-      <c r="Y9" s="37">
+      <c r="Y9" s="34">
         <v>10764</v>
       </c>
-      <c r="Z9" s="37">
+      <c r="Z9" s="34">
         <v>1262</v>
       </c>
-      <c r="AA9" s="37">
+      <c r="AA9" s="34">
         <v>3445</v>
       </c>
-      <c r="AB9" s="37">
+      <c r="AB9" s="34">
         <v>342</v>
       </c>
-      <c r="AC9" s="37">
+      <c r="AC9" s="34">
         <v>3102</v>
       </c>
     </row>
@@ -39764,28 +39734,28 @@
         <f t="shared" si="8"/>
         <v>8</v>
       </c>
-      <c r="V10" s="37">
+      <c r="V10" s="34">
         <v>3461</v>
       </c>
-      <c r="W10" s="37">
+      <c r="W10" s="34">
         <v>5204</v>
       </c>
-      <c r="X10" s="37">
+      <c r="X10" s="34">
         <v>9059</v>
       </c>
-      <c r="Y10" s="37">
+      <c r="Y10" s="34">
         <v>10765</v>
       </c>
-      <c r="Z10" s="37">
+      <c r="Z10" s="34">
         <v>1262</v>
       </c>
-      <c r="AA10" s="37">
+      <c r="AA10" s="34">
         <v>3447</v>
       </c>
-      <c r="AB10" s="37">
+      <c r="AB10" s="34">
         <v>343</v>
       </c>
-      <c r="AC10" s="37">
+      <c r="AC10" s="34">
         <v>3104</v>
       </c>
     </row>
@@ -39860,28 +39830,28 @@
         <f t="shared" si="8"/>
         <v>9</v>
       </c>
-      <c r="V11" s="37">
+      <c r="V11" s="34">
         <v>3541</v>
       </c>
-      <c r="W11" s="37">
+      <c r="W11" s="34">
         <v>5240</v>
       </c>
-      <c r="X11" s="37">
+      <c r="X11" s="34">
         <v>9059</v>
       </c>
-      <c r="Y11" s="37">
+      <c r="Y11" s="34">
         <v>10765</v>
       </c>
-      <c r="Z11" s="37">
+      <c r="Z11" s="34">
         <v>1262</v>
       </c>
-      <c r="AA11" s="37">
+      <c r="AA11" s="34">
         <v>3454</v>
       </c>
-      <c r="AB11" s="37">
+      <c r="AB11" s="34">
         <v>344</v>
       </c>
-      <c r="AC11" s="37">
+      <c r="AC11" s="34">
         <v>3110</v>
       </c>
     </row>
@@ -39956,28 +39926,28 @@
         <f t="shared" si="8"/>
         <v>10</v>
       </c>
-      <c r="V12" s="37">
+      <c r="V12" s="34">
         <v>3647</v>
       </c>
-      <c r="W12" s="37">
+      <c r="W12" s="34">
         <v>5316</v>
       </c>
-      <c r="X12" s="37">
+      <c r="X12" s="34">
         <v>9059</v>
       </c>
-      <c r="Y12" s="37">
+      <c r="Y12" s="34">
         <v>10765</v>
       </c>
-      <c r="Z12" s="37">
+      <c r="Z12" s="34">
         <v>1262</v>
       </c>
-      <c r="AA12" s="37">
+      <c r="AA12" s="34">
         <v>3459</v>
       </c>
-      <c r="AB12" s="37">
+      <c r="AB12" s="34">
         <v>344</v>
       </c>
-      <c r="AC12" s="37">
+      <c r="AC12" s="34">
         <v>3114</v>
       </c>
     </row>
@@ -40052,28 +40022,28 @@
         <f t="shared" si="8"/>
         <v>11</v>
       </c>
-      <c r="V13" s="37">
+      <c r="V13" s="34">
         <v>3717</v>
       </c>
-      <c r="W13" s="37">
+      <c r="W13" s="34">
         <v>5332</v>
       </c>
-      <c r="X13" s="37">
+      <c r="X13" s="34">
         <v>9072</v>
       </c>
-      <c r="Y13" s="37">
+      <c r="Y13" s="34">
         <v>10765</v>
       </c>
-      <c r="Z13" s="37">
+      <c r="Z13" s="34">
         <v>1262</v>
       </c>
-      <c r="AA13" s="37">
+      <c r="AA13" s="34">
         <v>3464</v>
       </c>
-      <c r="AB13" s="37">
+      <c r="AB13" s="34">
         <v>345</v>
       </c>
-      <c r="AC13" s="37">
+      <c r="AC13" s="34">
         <v>3118</v>
       </c>
     </row>
@@ -40148,28 +40118,28 @@
         <f t="shared" si="8"/>
         <v>12</v>
       </c>
-      <c r="V14" s="37">
+      <c r="V14" s="34">
         <v>3819</v>
       </c>
-      <c r="W14" s="37">
+      <c r="W14" s="34">
         <v>5471</v>
       </c>
-      <c r="X14" s="37">
+      <c r="X14" s="34">
         <v>9076</v>
       </c>
-      <c r="Y14" s="37">
+      <c r="Y14" s="34">
         <v>10767</v>
       </c>
-      <c r="Z14" s="37">
+      <c r="Z14" s="34">
         <v>1263</v>
       </c>
-      <c r="AA14" s="37">
+      <c r="AA14" s="34">
         <v>3469</v>
       </c>
-      <c r="AB14" s="37">
+      <c r="AB14" s="34">
         <v>346</v>
       </c>
-      <c r="AC14" s="37">
+      <c r="AC14" s="34">
         <v>3122</v>
       </c>
     </row>
@@ -40243,28 +40213,28 @@
         <f t="shared" si="8"/>
         <v>13</v>
       </c>
-      <c r="V15" s="37">
+      <c r="V15" s="34">
         <v>3835</v>
       </c>
-      <c r="W15" s="37">
+      <c r="W15" s="34">
         <v>5538</v>
       </c>
-      <c r="X15" s="37">
+      <c r="X15" s="34">
         <v>9081</v>
       </c>
-      <c r="Y15" s="37">
+      <c r="Y15" s="34">
         <v>10768</v>
       </c>
-      <c r="Z15" s="37">
+      <c r="Z15" s="34">
         <v>1263</v>
       </c>
-      <c r="AA15" s="37">
+      <c r="AA15" s="34">
         <v>3472</v>
       </c>
-      <c r="AB15" s="37">
+      <c r="AB15" s="34">
         <v>346</v>
       </c>
-      <c r="AC15" s="37">
+      <c r="AC15" s="34">
         <v>3135</v>
       </c>
     </row>
@@ -40339,28 +40309,28 @@
         <f t="shared" si="8"/>
         <v>14</v>
       </c>
-      <c r="V16" s="37">
+      <c r="V16" s="34">
         <v>3879</v>
       </c>
-      <c r="W16" s="37">
+      <c r="W16" s="34">
         <v>5598</v>
       </c>
-      <c r="X16" s="37">
+      <c r="X16" s="34">
         <v>9085</v>
       </c>
-      <c r="Y16" s="37">
+      <c r="Y16" s="34">
         <v>10769</v>
       </c>
-      <c r="Z16" s="37">
+      <c r="Z16" s="34">
         <v>1263</v>
       </c>
-      <c r="AA16" s="37">
+      <c r="AA16" s="34">
         <v>3480</v>
       </c>
-      <c r="AB16" s="37">
+      <c r="AB16" s="34">
         <v>346</v>
       </c>
-      <c r="AC16" s="37">
+      <c r="AC16" s="34">
         <v>3135</v>
       </c>
     </row>
@@ -40435,28 +40405,28 @@
         <f t="shared" si="8"/>
         <v>15</v>
       </c>
-      <c r="V17" s="37">
+      <c r="V17" s="34">
         <v>3959</v>
       </c>
-      <c r="W17" s="37">
+      <c r="W17" s="34">
         <v>5660</v>
       </c>
-      <c r="X17" s="37">
+      <c r="X17" s="34">
         <v>9090</v>
       </c>
-      <c r="Y17" s="37">
+      <c r="Y17" s="34">
         <v>10770</v>
       </c>
-      <c r="Z17" s="37">
+      <c r="Z17" s="34">
         <v>1264</v>
       </c>
-      <c r="AA17" s="37">
+      <c r="AA17" s="34">
         <v>3482</v>
       </c>
-      <c r="AB17" s="37">
+      <c r="AB17" s="34">
         <v>347</v>
       </c>
-      <c r="AC17" s="37">
+      <c r="AC17" s="34">
         <v>3135</v>
       </c>
     </row>
@@ -40531,28 +40501,28 @@
         <f t="shared" si="8"/>
         <v>16</v>
       </c>
-      <c r="V18" s="37">
+      <c r="V18" s="34">
         <v>4062</v>
       </c>
-      <c r="W18" s="37">
+      <c r="W18" s="34">
         <v>5699</v>
       </c>
-      <c r="X18" s="37">
+      <c r="X18" s="34">
         <v>9092</v>
       </c>
-      <c r="Y18" s="37">
+      <c r="Y18" s="34">
         <v>10771</v>
       </c>
-      <c r="Z18" s="37">
+      <c r="Z18" s="34">
         <v>1264</v>
       </c>
-      <c r="AA18" s="37">
+      <c r="AA18" s="34">
         <v>3484</v>
       </c>
-      <c r="AB18" s="37">
+      <c r="AB18" s="34">
         <v>350</v>
       </c>
-      <c r="AC18" s="37">
+      <c r="AC18" s="34">
         <v>3141</v>
       </c>
     </row>
@@ -40627,28 +40597,28 @@
         <f t="shared" si="8"/>
         <v>17</v>
       </c>
-      <c r="V19" s="37">
+      <c r="V19" s="34">
         <v>4205</v>
       </c>
-      <c r="W19" s="37">
+      <c r="W19" s="34">
         <v>5881</v>
       </c>
-      <c r="X19" s="37">
+      <c r="X19" s="34">
         <v>9101</v>
       </c>
-      <c r="Y19" s="37">
+      <c r="Y19" s="34">
         <v>10772</v>
       </c>
-      <c r="Z19" s="37">
+      <c r="Z19" s="34">
         <v>1264</v>
       </c>
-      <c r="AA19" s="37">
+      <c r="AA19" s="34">
         <v>3500</v>
       </c>
-      <c r="AB19" s="37">
+      <c r="AB19" s="34">
         <v>350</v>
       </c>
-      <c r="AC19" s="37">
+      <c r="AC19" s="34">
         <v>3151</v>
       </c>
     </row>
@@ -40723,28 +40693,28 @@
         <f t="shared" si="8"/>
         <v>18</v>
       </c>
-      <c r="V20" s="37">
+      <c r="V20" s="34">
         <v>4205</v>
       </c>
-      <c r="W20" s="37">
+      <c r="W20" s="34">
         <v>5881</v>
       </c>
-      <c r="X20" s="37">
+      <c r="X20" s="34">
         <v>9101</v>
       </c>
-      <c r="Y20" s="37">
+      <c r="Y20" s="34">
         <v>10772</v>
       </c>
-      <c r="Z20" s="37">
+      <c r="Z20" s="34">
         <v>1264</v>
       </c>
-      <c r="AA20" s="37">
+      <c r="AA20" s="34">
         <v>3500</v>
       </c>
-      <c r="AB20" s="37">
+      <c r="AB20" s="34">
         <v>350</v>
       </c>
-      <c r="AC20" s="37">
+      <c r="AC20" s="34">
         <v>3151</v>
       </c>
     </row>
@@ -40819,28 +40789,28 @@
         <f t="shared" si="8"/>
         <v>19</v>
       </c>
-      <c r="V21" s="37">
+      <c r="V21" s="34">
         <v>4216</v>
       </c>
-      <c r="W21" s="37">
+      <c r="W21" s="34">
         <v>5931</v>
       </c>
-      <c r="X21" s="37">
+      <c r="X21" s="34">
         <v>9103</v>
       </c>
-      <c r="Y21" s="37">
+      <c r="Y21" s="34">
         <v>10772</v>
       </c>
-      <c r="Z21" s="37">
+      <c r="Z21" s="34">
         <v>1264</v>
       </c>
-      <c r="AA21" s="37">
+      <c r="AA21" s="34">
         <v>3516</v>
       </c>
-      <c r="AB21" s="37">
+      <c r="AB21" s="34">
         <v>350</v>
       </c>
-      <c r="AC21" s="37">
+      <c r="AC21" s="34">
         <v>3169</v>
       </c>
     </row>
@@ -40915,28 +40885,28 @@
         <f t="shared" si="8"/>
         <v>20</v>
       </c>
-      <c r="V22" s="37">
+      <c r="V22" s="34">
         <v>4216</v>
       </c>
-      <c r="W22" s="37">
+      <c r="W22" s="34">
         <v>5931</v>
       </c>
-      <c r="X22" s="37">
+      <c r="X22" s="34">
         <v>9103</v>
       </c>
-      <c r="Y22" s="37">
+      <c r="Y22" s="34">
         <v>10772</v>
       </c>
-      <c r="Z22" s="37">
+      <c r="Z22" s="34">
         <v>1264</v>
       </c>
-      <c r="AA22" s="37">
+      <c r="AA22" s="34">
         <v>3516</v>
       </c>
-      <c r="AB22" s="37">
+      <c r="AB22" s="34">
         <v>350</v>
       </c>
-      <c r="AC22" s="37">
+      <c r="AC22" s="34">
         <v>3169</v>
       </c>
     </row>
@@ -41011,28 +40981,28 @@
         <f t="shared" si="8"/>
         <v>21</v>
       </c>
-      <c r="V23" s="37">
+      <c r="V23" s="34">
         <v>4276</v>
       </c>
-      <c r="W23" s="37">
+      <c r="W23" s="34">
         <v>6079</v>
       </c>
-      <c r="X23" s="37">
+      <c r="X23" s="34">
         <v>9112</v>
       </c>
-      <c r="Y23" s="37">
+      <c r="Y23" s="34">
         <v>10774</v>
       </c>
-      <c r="Z23" s="37">
+      <c r="Z23" s="34">
         <v>1265</v>
       </c>
-      <c r="AA23" s="37">
+      <c r="AA23" s="34">
         <v>3516</v>
       </c>
-      <c r="AB23" s="37">
+      <c r="AB23" s="34">
         <v>350</v>
       </c>
-      <c r="AC23" s="37">
+      <c r="AC23" s="34">
         <v>3169</v>
       </c>
     </row>
@@ -41107,28 +41077,28 @@
         <f t="shared" si="8"/>
         <v>22</v>
       </c>
-      <c r="V24" s="37">
+      <c r="V24" s="34">
         <v>4310</v>
       </c>
-      <c r="W24" s="37">
+      <c r="W24" s="34">
         <v>6226</v>
       </c>
-      <c r="X24" s="37">
+      <c r="X24" s="34">
         <v>9114</v>
       </c>
-      <c r="Y24" s="37">
+      <c r="Y24" s="34">
         <v>10774</v>
       </c>
-      <c r="Z24" s="37">
+      <c r="Z24" s="34">
         <v>1265</v>
       </c>
-      <c r="AA24" s="37">
+      <c r="AA24" s="34">
         <v>3521</v>
       </c>
-      <c r="AB24" s="37">
+      <c r="AB24" s="34">
         <v>350</v>
       </c>
-      <c r="AC24" s="37">
+      <c r="AC24" s="34">
         <v>3171</v>
       </c>
     </row>
@@ -41203,28 +41173,28 @@
         <f t="shared" si="8"/>
         <v>23</v>
       </c>
-      <c r="V25" s="37">
+      <c r="V25" s="34">
         <v>4401</v>
       </c>
-      <c r="W25" s="37">
+      <c r="W25" s="34">
         <v>6242</v>
       </c>
-      <c r="X25" s="37">
+      <c r="X25" s="34">
         <v>9119</v>
       </c>
-      <c r="Y25" s="37">
+      <c r="Y25" s="34">
         <v>10774</v>
       </c>
-      <c r="Z25" s="37">
+      <c r="Z25" s="34">
         <v>1265</v>
       </c>
-      <c r="AA25" s="37">
+      <c r="AA25" s="34">
         <v>3524</v>
       </c>
-      <c r="AB25" s="37">
+      <c r="AB25" s="34">
         <v>350</v>
       </c>
-      <c r="AC25" s="37">
+      <c r="AC25" s="34">
         <v>3179</v>
       </c>
     </row>
@@ -41295,32 +41265,32 @@
         <v>4</v>
       </c>
       <c r="T26" s="4"/>
-      <c r="U26" s="38">
+      <c r="U26" s="35">
         <f t="shared" si="8"/>
         <v>24</v>
       </c>
-      <c r="V26" s="37">
+      <c r="V26" s="34">
         <v>4494</v>
       </c>
-      <c r="W26" s="37">
+      <c r="W26" s="34">
         <v>6283</v>
       </c>
-      <c r="X26" s="37">
+      <c r="X26" s="34">
         <v>9121</v>
       </c>
-      <c r="Y26" s="37">
+      <c r="Y26" s="34">
         <v>10776</v>
       </c>
-      <c r="Z26" s="37">
+      <c r="Z26" s="34">
         <v>1265</v>
       </c>
-      <c r="AA26" s="37">
+      <c r="AA26" s="34">
         <v>3532</v>
       </c>
-      <c r="AB26" s="37">
+      <c r="AB26" s="34">
         <v>351</v>
       </c>
-      <c r="AC26" s="37">
+      <c r="AC26" s="34">
         <v>3180</v>
       </c>
     </row>
@@ -41395,28 +41365,28 @@
         <f t="shared" si="8"/>
         <v>25</v>
       </c>
-      <c r="V27" s="37">
+      <c r="V27" s="34">
         <v>4569</v>
       </c>
-      <c r="W27" s="37">
+      <c r="W27" s="34">
         <v>6389</v>
       </c>
-      <c r="X27" s="37">
+      <c r="X27" s="34">
         <v>9128</v>
       </c>
-      <c r="Y27" s="37">
+      <c r="Y27" s="34">
         <v>10776</v>
       </c>
-      <c r="Z27" s="37">
+      <c r="Z27" s="34">
         <v>1265</v>
       </c>
-      <c r="AA27" s="37">
+      <c r="AA27" s="34">
         <v>3536</v>
       </c>
-      <c r="AB27" s="37">
+      <c r="AB27" s="34">
         <v>352</v>
       </c>
-      <c r="AC27" s="37">
+      <c r="AC27" s="34">
         <v>3184</v>
       </c>
     </row>
@@ -41491,28 +41461,28 @@
         <f t="shared" si="8"/>
         <v>26</v>
       </c>
-      <c r="V28" s="37">
+      <c r="V28" s="34">
         <v>4603</v>
       </c>
-      <c r="W28" s="37">
+      <c r="W28" s="34">
         <v>6457</v>
       </c>
-      <c r="X28" s="37">
+      <c r="X28" s="34">
         <v>9129</v>
       </c>
-      <c r="Y28" s="37">
+      <c r="Y28" s="34">
         <v>10777</v>
       </c>
-      <c r="Z28" s="37">
+      <c r="Z28" s="34">
         <v>1265</v>
       </c>
-      <c r="AA28" s="37">
+      <c r="AA28" s="34">
         <v>3540</v>
       </c>
-      <c r="AB28" s="37">
+      <c r="AB28" s="34">
         <v>352</v>
       </c>
-      <c r="AC28" s="37">
+      <c r="AC28" s="34">
         <v>3188</v>
       </c>
     </row>
@@ -41587,28 +41557,28 @@
         <f t="shared" si="8"/>
         <v>27</v>
       </c>
-      <c r="V29" s="37">
+      <c r="V29" s="34">
         <v>4660</v>
       </c>
-      <c r="W29" s="37">
+      <c r="W29" s="34">
         <v>6551</v>
       </c>
-      <c r="X29" s="37">
+      <c r="X29" s="34">
         <v>9133</v>
       </c>
-      <c r="Y29" s="37">
+      <c r="Y29" s="34">
         <v>10778</v>
       </c>
-      <c r="Z29" s="37">
+      <c r="Z29" s="34">
         <v>1266</v>
       </c>
-      <c r="AA29" s="37">
+      <c r="AA29" s="34">
         <v>3540</v>
       </c>
-      <c r="AB29" s="37">
+      <c r="AB29" s="34">
         <v>352</v>
       </c>
-      <c r="AC29" s="37">
+      <c r="AC29" s="34">
         <v>3193</v>
       </c>
     </row>
@@ -41683,28 +41653,28 @@
         <f t="shared" si="8"/>
         <v>28</v>
       </c>
-      <c r="V30" s="37">
+      <c r="V30" s="34">
         <v>4672</v>
       </c>
-      <c r="W30" s="37">
+      <c r="W30" s="34">
         <v>6586</v>
       </c>
-      <c r="X30" s="37">
+      <c r="X30" s="34">
         <v>9138</v>
       </c>
-      <c r="Y30" s="37">
+      <c r="Y30" s="34">
         <v>10779</v>
       </c>
-      <c r="Z30" s="37">
+      <c r="Z30" s="34">
         <v>1266</v>
       </c>
-      <c r="AA30" s="37">
+      <c r="AA30" s="34">
         <v>3548</v>
       </c>
-      <c r="AB30" s="37">
+      <c r="AB30" s="34">
         <v>352</v>
       </c>
-      <c r="AC30" s="37">
+      <c r="AC30" s="34">
         <v>3196</v>
       </c>
     </row>
@@ -41779,28 +41749,28 @@
         <f t="shared" si="8"/>
         <v>29</v>
       </c>
-      <c r="V31" s="37">
+      <c r="V31" s="34">
         <v>4765</v>
       </c>
-      <c r="W31" s="37">
+      <c r="W31" s="34">
         <v>6659</v>
       </c>
-      <c r="X31" s="37">
+      <c r="X31" s="34">
         <v>9140</v>
       </c>
-      <c r="Y31" s="37">
+      <c r="Y31" s="34">
         <v>10780</v>
       </c>
-      <c r="Z31" s="37">
+      <c r="Z31" s="34">
         <v>1266</v>
       </c>
-      <c r="AA31" s="37">
+      <c r="AA31" s="34">
         <v>3556</v>
       </c>
-      <c r="AB31" s="37">
+      <c r="AB31" s="34">
         <v>353</v>
       </c>
-      <c r="AC31" s="37">
+      <c r="AC31" s="34">
         <v>3203</v>
       </c>
     </row>
@@ -41810,28 +41780,28 @@
         <f t="shared" si="8"/>
         <v>30</v>
       </c>
-      <c r="V32" s="37">
+      <c r="V32" s="34">
         <v>4765</v>
       </c>
-      <c r="W32" s="37">
+      <c r="W32" s="34">
         <v>6659</v>
       </c>
-      <c r="X32" s="37">
+      <c r="X32" s="34">
         <v>9140</v>
       </c>
-      <c r="Y32" s="37">
+      <c r="Y32" s="34">
         <v>10780</v>
       </c>
-      <c r="Z32" s="37">
+      <c r="Z32" s="34">
         <v>1266</v>
       </c>
-      <c r="AA32" s="37">
+      <c r="AA32" s="34">
         <v>3556</v>
       </c>
-      <c r="AB32" s="37">
+      <c r="AB32" s="34">
         <v>353</v>
       </c>
-      <c r="AC32" s="37">
+      <c r="AC32" s="34">
         <v>3203</v>
       </c>
     </row>
@@ -41916,15 +41886,15 @@
       <c r="I68" s="1"/>
     </row>
     <row r="69" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A69" s="34"/>
-      <c r="B69" s="34"/>
-      <c r="C69" s="34"/>
-      <c r="D69" s="34"/>
-      <c r="E69" s="34"/>
-      <c r="F69" s="34"/>
-      <c r="G69" s="34"/>
-      <c r="H69" s="34"/>
-      <c r="I69" s="34"/>
+      <c r="A69" s="39"/>
+      <c r="B69" s="39"/>
+      <c r="C69" s="39"/>
+      <c r="D69" s="39"/>
+      <c r="E69" s="39"/>
+      <c r="F69" s="39"/>
+      <c r="G69" s="39"/>
+      <c r="H69" s="39"/>
+      <c r="I69" s="39"/>
     </row>
     <row r="70" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A70" s="1"/>
@@ -41949,15 +41919,15 @@
       <c r="I71" s="21"/>
     </row>
     <row r="74" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A74" s="35"/>
-      <c r="B74" s="35"/>
-      <c r="C74" s="35"/>
-      <c r="D74" s="35"/>
-      <c r="E74" s="35"/>
-      <c r="F74" s="35"/>
-      <c r="G74" s="35"/>
-      <c r="H74" s="35"/>
-      <c r="I74" s="35"/>
+      <c r="A74" s="40"/>
+      <c r="B74" s="40"/>
+      <c r="C74" s="40"/>
+      <c r="D74" s="40"/>
+      <c r="E74" s="40"/>
+      <c r="F74" s="40"/>
+      <c r="G74" s="40"/>
+      <c r="H74" s="40"/>
+      <c r="I74" s="40"/>
     </row>
     <row r="75" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A75" s="1"/>
@@ -41993,15 +41963,15 @@
       <c r="I77" s="23"/>
     </row>
     <row r="78" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A78" s="36"/>
-      <c r="B78" s="36"/>
-      <c r="C78" s="36"/>
-      <c r="D78" s="36"/>
-      <c r="E78" s="36"/>
-      <c r="F78" s="36"/>
-      <c r="G78" s="36"/>
-      <c r="H78" s="36"/>
-      <c r="I78" s="36"/>
+      <c r="A78" s="41"/>
+      <c r="B78" s="41"/>
+      <c r="C78" s="41"/>
+      <c r="D78" s="41"/>
+      <c r="E78" s="41"/>
+      <c r="F78" s="41"/>
+      <c r="G78" s="41"/>
+      <c r="H78" s="41"/>
+      <c r="I78" s="41"/>
     </row>
     <row r="79" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A79" s="1"/>
@@ -42037,15 +42007,15 @@
       <c r="B84" s="21"/>
     </row>
     <row r="86" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A86" s="35"/>
-      <c r="B86" s="35"/>
-      <c r="C86" s="35"/>
-      <c r="D86" s="35"/>
-      <c r="E86" s="35"/>
-      <c r="F86" s="35"/>
-      <c r="G86" s="35"/>
-      <c r="H86" s="35"/>
-      <c r="I86" s="35"/>
+      <c r="A86" s="40"/>
+      <c r="B86" s="40"/>
+      <c r="C86" s="40"/>
+      <c r="D86" s="40"/>
+      <c r="E86" s="40"/>
+      <c r="F86" s="40"/>
+      <c r="G86" s="40"/>
+      <c r="H86" s="40"/>
+      <c r="I86" s="40"/>
     </row>
     <row r="87" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A87" s="1"/>
@@ -42148,15 +42118,15 @@
       <c r="B97" s="24"/>
     </row>
     <row r="99" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A99" s="34"/>
-      <c r="B99" s="34"/>
-      <c r="C99" s="34"/>
-      <c r="D99" s="34"/>
-      <c r="E99" s="34"/>
-      <c r="F99" s="34"/>
-      <c r="G99" s="34"/>
-      <c r="H99" s="34"/>
-      <c r="I99" s="34"/>
+      <c r="A99" s="39"/>
+      <c r="B99" s="39"/>
+      <c r="C99" s="39"/>
+      <c r="D99" s="39"/>
+      <c r="E99" s="39"/>
+      <c r="F99" s="39"/>
+      <c r="G99" s="39"/>
+      <c r="H99" s="39"/>
+      <c r="I99" s="39"/>
     </row>
     <row r="100" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A100" s="1"/>
